--- a/files/九龙-启德-Double Coast III.xlsx
+++ b/files/九龙-启德-Double Coast III.xlsx
@@ -8,8 +8,6 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="销控汇总明细" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1A座 销控表" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1B座 销控表" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -21,7 +19,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="$#,##0"/>
   </numFmts>
-  <fonts count="14">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -43,65 +41,8 @@
       <name val="Microsoft YaHei"/>
       <sz val="10"/>
     </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <color rgb="007F7F7F"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="007F7F7F"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00004D00"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00004D00"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <color rgb="00002060"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00002060"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <color rgb="00660000"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00660000"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00000000"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00000000"/>
-      <sz val="11"/>
-    </font>
   </fonts>
-  <fills count="9">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
@@ -112,42 +53,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="00F2F2F2"/>
         <bgColor rgb="00F2F2F2"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFFFFF"/>
-        <bgColor rgb="00FFFFFF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00A9F5A9"/>
-        <bgColor rgb="00A9F5A9"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00A9D0F5"/>
-        <bgColor rgb="00A9D0F5"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00F5A9A9"/>
-        <bgColor rgb="00F5A9A9"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFC000"/>
-        <bgColor rgb="00FFC000"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00E5E5E5"/>
-        <bgColor rgb="00E5E5E5"/>
       </patternFill>
     </fill>
   </fills>
@@ -177,7 +82,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -193,51 +98,6 @@
     </xf>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -26031,4963 +25891,4 @@
   <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:G38"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="40" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Double Coast III - 1A座 销控网格图</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="6" t="inlineStr">
-        <is>
-          <t>总套数</t>
-        </is>
-      </c>
-      <c r="B2" s="7" t="inlineStr">
-        <is>
-          <t>在售 (Sale)</t>
-        </is>
-      </c>
-      <c r="C2" s="8" t="inlineStr">
-        <is>
-          <t>已定价未售</t>
-        </is>
-      </c>
-      <c r="D2" s="9" t="inlineStr">
-        <is>
-          <t>已售 (Sold)</t>
-        </is>
-      </c>
-      <c r="E2" s="10" t="inlineStr">
-        <is>
-          <t>暂停销售</t>
-        </is>
-      </c>
-      <c r="F2" s="6" t="inlineStr">
-        <is>
-          <t>待售 (Pending)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="25" customHeight="1">
-      <c r="A3" s="11" t="inlineStr">
-        <is>
-          <t>196 套</t>
-        </is>
-      </c>
-      <c r="B3" s="12" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="C3" s="13" t="inlineStr">
-        <is>
-          <t>5 套</t>
-        </is>
-      </c>
-      <c r="D3" s="14" t="inlineStr">
-        <is>
-          <t>72 套</t>
-        </is>
-      </c>
-      <c r="E3" s="15" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="F3" s="11" t="inlineStr">
-        <is>
-          <t>119 套</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="25" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>楼层\房号</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>E</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="65" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>39/F</t>
-        </is>
-      </c>
-      <c r="B6" s="16" t="inlineStr">
-        <is>
-          <t>A | 1378呎 (4+房)
-$4,668万
-$33,877/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="C6" s="17" t="inlineStr"/>
-      <c r="D6" s="18" t="inlineStr">
-        <is>
-          <t>C | 493呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E6" s="18" t="inlineStr">
-        <is>
-          <t>D | 434呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F6" s="18" t="inlineStr">
-        <is>
-          <t>E | 429呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G6" s="18" t="inlineStr">
-        <is>
-          <t>F | 428呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="65" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>38/F</t>
-        </is>
-      </c>
-      <c r="B7" s="18" t="inlineStr">
-        <is>
-          <t>A | 641呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C7" s="18" t="inlineStr">
-        <is>
-          <t>B | 696呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D7" s="18" t="inlineStr">
-        <is>
-          <t>C | 518呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E7" s="18" t="inlineStr">
-        <is>
-          <t>D | 436呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F7" s="18" t="inlineStr">
-        <is>
-          <t>E | 429呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G7" s="18" t="inlineStr">
-        <is>
-          <t>F | 428呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="65" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>37/F</t>
-        </is>
-      </c>
-      <c r="B8" s="18" t="inlineStr">
-        <is>
-          <t>A | 641呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C8" s="18" t="inlineStr">
-        <is>
-          <t>B | 696呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D8" s="18" t="inlineStr">
-        <is>
-          <t>C | 518呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E8" s="18" t="inlineStr">
-        <is>
-          <t>D | 436呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F8" s="18" t="inlineStr">
-        <is>
-          <t>E | 429呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G8" s="18" t="inlineStr">
-        <is>
-          <t>F | 430呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="65" customHeight="1">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>36/F</t>
-        </is>
-      </c>
-      <c r="B9" s="18" t="inlineStr">
-        <is>
-          <t>A | 641呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C9" s="18" t="inlineStr">
-        <is>
-          <t>B | 696呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D9" s="18" t="inlineStr">
-        <is>
-          <t>C | 518呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E9" s="18" t="inlineStr">
-        <is>
-          <t>D | 436呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F9" s="18" t="inlineStr">
-        <is>
-          <t>E | 429呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G9" s="18" t="inlineStr">
-        <is>
-          <t>F | 430呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="65" customHeight="1">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>35/F</t>
-        </is>
-      </c>
-      <c r="B10" s="18" t="inlineStr">
-        <is>
-          <t>A | 641呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C10" s="18" t="inlineStr">
-        <is>
-          <t>B | 696呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D10" s="18" t="inlineStr">
-        <is>
-          <t>C | 518呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E10" s="18" t="inlineStr">
-        <is>
-          <t>D | 436呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F10" s="18" t="inlineStr">
-        <is>
-          <t>E | 429呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G10" s="18" t="inlineStr">
-        <is>
-          <t>F | 430呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="65" customHeight="1">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>33/F</t>
-        </is>
-      </c>
-      <c r="B11" s="18" t="inlineStr">
-        <is>
-          <t>A | 641呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C11" s="19" t="inlineStr">
-        <is>
-          <t>B | 696呎 (3房)
-$1,806万
-$25,948/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="D11" s="18" t="inlineStr">
-        <is>
-          <t>C | 518呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E11" s="18" t="inlineStr">
-        <is>
-          <t>D | 436呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F11" s="18" t="inlineStr">
-        <is>
-          <t>E | 429呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G11" s="18" t="inlineStr">
-        <is>
-          <t>F | 430呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="65" customHeight="1">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>32/F</t>
-        </is>
-      </c>
-      <c r="B12" s="18" t="inlineStr">
-        <is>
-          <t>A | 641呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C12" s="19" t="inlineStr">
-        <is>
-          <t>B | 696呎 (3房)
-$1,802万
-$25,884/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="D12" s="18" t="inlineStr">
-        <is>
-          <t>C | 518呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E12" s="18" t="inlineStr">
-        <is>
-          <t>D | 436呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F12" s="18" t="inlineStr">
-        <is>
-          <t>E | 429呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G12" s="18" t="inlineStr">
-        <is>
-          <t>F | 430呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="65" customHeight="1">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>31/F</t>
-        </is>
-      </c>
-      <c r="B13" s="18" t="inlineStr">
-        <is>
-          <t>A | 641呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C13" s="18" t="inlineStr">
-        <is>
-          <t>B | 696呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D13" s="18" t="inlineStr">
-        <is>
-          <t>C | 518呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E13" s="18" t="inlineStr">
-        <is>
-          <t>D | 436呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F13" s="18" t="inlineStr">
-        <is>
-          <t>E | 429呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G13" s="16" t="inlineStr">
-        <is>
-          <t>F | 431呎 (2房)
-$791万
-$18,346/呎
-(26年-05月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="65" customHeight="1">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>30/F</t>
-        </is>
-      </c>
-      <c r="B14" s="18" t="inlineStr">
-        <is>
-          <t>A | 641呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C14" s="16" t="inlineStr">
-        <is>
-          <t>B | 695呎 (3房)
-$1,631万
-$23,471/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="D14" s="18" t="inlineStr">
-        <is>
-          <t>C | 518呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E14" s="18" t="inlineStr">
-        <is>
-          <t>D | 436呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F14" s="18" t="inlineStr">
-        <is>
-          <t>E | 429呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G14" s="16" t="inlineStr">
-        <is>
-          <t>F | 431呎 (2房)
-$789万
-$18,302/呎
-(26年-05月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="65" customHeight="1">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>29/F</t>
-        </is>
-      </c>
-      <c r="B15" s="18" t="inlineStr">
-        <is>
-          <t>A | 641呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C15" s="19" t="inlineStr">
-        <is>
-          <t>B | 696呎 (3房)
-$1,788万
-$25,690/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="D15" s="18" t="inlineStr">
-        <is>
-          <t>C | 518呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E15" s="18" t="inlineStr">
-        <is>
-          <t>D | 436呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F15" s="16" t="inlineStr">
-        <is>
-          <t>E | 429呎 (2房)
-$800万
-$18,653/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="G15" s="16" t="inlineStr">
-        <is>
-          <t>F | 431呎 (2房)
-$796万
-$18,459/呎
-(26年-05月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="65" customHeight="1">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>28/F</t>
-        </is>
-      </c>
-      <c r="B16" s="18" t="inlineStr">
-        <is>
-          <t>A | 641呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C16" s="18" t="inlineStr">
-        <is>
-          <t>B | 696呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D16" s="18" t="inlineStr">
-        <is>
-          <t>C | 518呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E16" s="18" t="inlineStr">
-        <is>
-          <t>D | 436呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F16" s="18" t="inlineStr">
-        <is>
-          <t>E | 429呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G16" s="18" t="inlineStr">
-        <is>
-          <t>F | 430呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="65" customHeight="1">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>27/F</t>
-        </is>
-      </c>
-      <c r="B17" s="18" t="inlineStr">
-        <is>
-          <t>A | 641呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C17" s="19" t="inlineStr">
-        <is>
-          <t>B | 696呎 (3房)
-$1,775万
-$25,499/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="D17" s="18" t="inlineStr">
-        <is>
-          <t>C | 518呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E17" s="18" t="inlineStr">
-        <is>
-          <t>D | 436呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F17" s="16" t="inlineStr">
-        <is>
-          <t>E | 429呎 (2房)
-$794万
-$18,513/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="G17" s="16" t="inlineStr">
-        <is>
-          <t>F | 431呎 (2房)
-$790万
-$18,323/呎
-(26年-05月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="65" customHeight="1">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>26/F</t>
-        </is>
-      </c>
-      <c r="B18" s="18" t="inlineStr">
-        <is>
-          <t>A | 641呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C18" s="16" t="inlineStr">
-        <is>
-          <t>B | 695呎 (3房)
-$1,558万
-$22,416/呎
-(26年-01月)</t>
-        </is>
-      </c>
-      <c r="D18" s="18" t="inlineStr">
-        <is>
-          <t>C | 518呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E18" s="18" t="inlineStr">
-        <is>
-          <t>D | 436呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F18" s="16" t="inlineStr">
-        <is>
-          <t>E | 429呎 (2房)
-$792万
-$18,466/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="G18" s="16" t="inlineStr">
-        <is>
-          <t>F | 431呎 (2房)
-$788万
-$18,276/呎
-(26年-05月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="65" customHeight="1">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>25/F</t>
-        </is>
-      </c>
-      <c r="B19" s="18" t="inlineStr">
-        <is>
-          <t>A | 641呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C19" s="18" t="inlineStr">
-        <is>
-          <t>B | 696呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D19" s="18" t="inlineStr">
-        <is>
-          <t>C | 518呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E19" s="18" t="inlineStr">
-        <is>
-          <t>D | 436呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F19" s="16" t="inlineStr">
-        <is>
-          <t>E | 429呎 (2房)
-$790万
-$18,420/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="G19" s="16" t="inlineStr">
-        <is>
-          <t>F | 431呎 (2房)
-$786万
-$18,230/呎
-(26年-05月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="65" customHeight="1">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>23/F</t>
-        </is>
-      </c>
-      <c r="B20" s="18" t="inlineStr">
-        <is>
-          <t>A | 641呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C20" s="16" t="inlineStr">
-        <is>
-          <t>B | 695呎 (3房)
-$1,550万
-$22,304/呎
-(26年-02月)</t>
-        </is>
-      </c>
-      <c r="D20" s="18" t="inlineStr">
-        <is>
-          <t>C | 518呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E20" s="18" t="inlineStr">
-        <is>
-          <t>D | 436呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F20" s="16" t="inlineStr">
-        <is>
-          <t>E | 429呎 (2房)
-$788万
-$18,373/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="G20" s="16" t="inlineStr">
-        <is>
-          <t>F | 431呎 (2房)
-$792万
-$18,387/呎
-(26年-05月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="65" customHeight="1">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>22/F</t>
-        </is>
-      </c>
-      <c r="B21" s="18" t="inlineStr">
-        <is>
-          <t>A | 641呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C21" s="16" t="inlineStr">
-        <is>
-          <t>B | 695呎 (3房)
-$1,546万
-$22,249/呎
-(26年-02月)</t>
-        </is>
-      </c>
-      <c r="D21" s="18" t="inlineStr">
-        <is>
-          <t>C | 518呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E21" s="18" t="inlineStr">
-        <is>
-          <t>D | 436呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F21" s="16" t="inlineStr">
-        <is>
-          <t>E | 429呎 (2房)
-$786万
-$18,329/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="G21" s="16" t="inlineStr">
-        <is>
-          <t>F | 431呎 (2房)
-$782万
-$18,139/呎
-(26年-05月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="65" customHeight="1">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>21/F</t>
-        </is>
-      </c>
-      <c r="B22" s="16" t="inlineStr">
-        <is>
-          <t>A | 640呎 (3房)
-$1,444万
-$22,564/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="C22" s="16" t="inlineStr">
-        <is>
-          <t>B | 695呎 (3房)
-$1,542万
-$22,193/呎
-(26年-03月)</t>
-        </is>
-      </c>
-      <c r="D22" s="18" t="inlineStr">
-        <is>
-          <t>C | 518呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E22" s="18" t="inlineStr">
-        <is>
-          <t>D | 436呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F22" s="16" t="inlineStr">
-        <is>
-          <t>E | 429呎 (2房)
-$784万
-$18,282/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="G22" s="16" t="inlineStr">
-        <is>
-          <t>F | 431呎 (2房)
-$780万
-$18,095/呎
-(26年-05月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="65" customHeight="1">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>20/F</t>
-        </is>
-      </c>
-      <c r="B23" s="16" t="inlineStr">
-        <is>
-          <t>A | 640呎 (3房)
-$1,432万
-$22,383/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="C23" s="16" t="inlineStr">
-        <is>
-          <t>B | 695呎 (3房)
-$1,556万
-$22,388/呎
-(26年-01月)</t>
-        </is>
-      </c>
-      <c r="D23" s="18" t="inlineStr">
-        <is>
-          <t>C | 518呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E23" s="18" t="inlineStr">
-        <is>
-          <t>D | 436呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F23" s="16" t="inlineStr">
-        <is>
-          <t>E | 429呎 (2房)
-$782万
-$18,238/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="G23" s="16" t="inlineStr">
-        <is>
-          <t>F | 431呎 (2房)
-$769万
-$17,849/呎
-(26年-05月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="65" customHeight="1">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>19/F</t>
-        </is>
-      </c>
-      <c r="B24" s="16" t="inlineStr">
-        <is>
-          <t>A | 640呎 (3房)
-$1,429万
-$22,327/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="C24" s="16" t="inlineStr">
-        <is>
-          <t>B | 695呎 (3房)
-$1,604万
-$23,085/呎
-(26年-01月)</t>
-        </is>
-      </c>
-      <c r="D24" s="18" t="inlineStr">
-        <is>
-          <t>C | 518呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E24" s="18" t="inlineStr">
-        <is>
-          <t>D | 436呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F24" s="16" t="inlineStr">
-        <is>
-          <t>E | 429呎 (2房)
-$780万
-$18,191/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="G24" s="16" t="inlineStr">
-        <is>
-          <t>F | 431呎 (2房)
-$776万
-$18,005/呎
-(26年-05月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="65" customHeight="1">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>18/F</t>
-        </is>
-      </c>
-      <c r="B25" s="16" t="inlineStr">
-        <is>
-          <t>A | 640呎 (3房)
-$1,433万
-$22,397/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="C25" s="16" t="inlineStr">
-        <is>
-          <t>B | 695呎 (3房)
-$1,531万
-$22,027/呎
-(26年-03月)</t>
-        </is>
-      </c>
-      <c r="D25" s="18" t="inlineStr">
-        <is>
-          <t>C | 518呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E25" s="18" t="inlineStr">
-        <is>
-          <t>D | 436呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F25" s="16" t="inlineStr">
-        <is>
-          <t>E | 429呎 (2房)
-$787万
-$18,350/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="G25" s="16" t="inlineStr">
-        <is>
-          <t>F | 431呎 (2房)
-$729万
-$16,914/呎
-(26年-01月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="65" customHeight="1">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>17/F</t>
-        </is>
-      </c>
-      <c r="B26" s="16" t="inlineStr">
-        <is>
-          <t>A | 640呎 (3房)
-$1,426万
-$22,284/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="C26" s="16" t="inlineStr">
-        <is>
-          <t>B | 695呎 (3房)
-$1,523万
-$21,917/呎
-(26年-02月)</t>
-        </is>
-      </c>
-      <c r="D26" s="18" t="inlineStr">
-        <is>
-          <t>C | 518呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E26" s="18" t="inlineStr">
-        <is>
-          <t>D | 436呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F26" s="16" t="inlineStr">
-        <is>
-          <t>E | 429呎 (2房)
-$783万
-$18,259/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="G26" s="16" t="inlineStr">
-        <is>
-          <t>F | 431呎 (2房)
-$725万
-$16,828/呎
-(26年-01月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="65" customHeight="1">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>16/F</t>
-        </is>
-      </c>
-      <c r="B27" s="16" t="inlineStr">
-        <is>
-          <t>A | 640呎 (3房)
-$1,415万
-$22,105/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="C27" s="16" t="inlineStr">
-        <is>
-          <t>B | 695呎 (3房)
-$1,520万
-$21,863/呎
-(26年-03月)</t>
-        </is>
-      </c>
-      <c r="D27" s="18" t="inlineStr">
-        <is>
-          <t>C | 518呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E27" s="18" t="inlineStr">
-        <is>
-          <t>D | 436呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F27" s="16" t="inlineStr">
-        <is>
-          <t>E | 429呎 (2房)
-$773万
-$18,012/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="G27" s="16" t="inlineStr">
-        <is>
-          <t>F | 431呎 (2房)
-$724万
-$16,789/呎
-(26年-01月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="65" customHeight="1">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>15/F</t>
-        </is>
-      </c>
-      <c r="B28" s="16" t="inlineStr">
-        <is>
-          <t>A | 640呎 (3房)
-$1,357万
-$21,202/呎
-(26年-01月)</t>
-        </is>
-      </c>
-      <c r="C28" s="16" t="inlineStr">
-        <is>
-          <t>B | 695呎 (3房)
-$1,516万
-$21,809/呎
-(26年-01月)</t>
-        </is>
-      </c>
-      <c r="D28" s="18" t="inlineStr">
-        <is>
-          <t>C | 518呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E28" s="18" t="inlineStr">
-        <is>
-          <t>D | 436呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F28" s="16" t="inlineStr">
-        <is>
-          <t>E | 429呎 (2房)
-$771万
-$17,967/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="G28" s="16" t="inlineStr">
-        <is>
-          <t>F | 431呎 (2房)
-$722万
-$16,745/呎
-(26年-01月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="65" customHeight="1">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>12/F</t>
-        </is>
-      </c>
-      <c r="B29" s="16" t="inlineStr">
-        <is>
-          <t>A | 640呎 (3房)
-$1,416万
-$22,119/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="C29" s="16" t="inlineStr">
-        <is>
-          <t>B | 695呎 (3房)
-$1,512万
-$21,754/呎
-(26年-01月)</t>
-        </is>
-      </c>
-      <c r="D29" s="18" t="inlineStr">
-        <is>
-          <t>C | 518呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E29" s="18" t="inlineStr">
-        <is>
-          <t>D | 436呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F29" s="16" t="inlineStr">
-        <is>
-          <t>E | 429呎 (2房)
-$740万
-$17,261/呎
-(26年-01月)</t>
-        </is>
-      </c>
-      <c r="G29" s="16" t="inlineStr">
-        <is>
-          <t>F | 431呎 (2房)
-$720万
-$16,705/呎
-(26年-01月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="65" customHeight="1">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t>11/F</t>
-        </is>
-      </c>
-      <c r="B30" s="16" t="inlineStr">
-        <is>
-          <t>A | 640呎 (3房)
-$1,404万
-$21,941/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="C30" s="16" t="inlineStr">
-        <is>
-          <t>B | 695呎 (3房)
-$1,508万
-$21,699/呎
-(26年-02月)</t>
-        </is>
-      </c>
-      <c r="D30" s="18" t="inlineStr">
-        <is>
-          <t>C | 518呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E30" s="18" t="inlineStr">
-        <is>
-          <t>D | 436呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F30" s="16" t="inlineStr">
-        <is>
-          <t>E | 429呎 (2房)
-$730万
-$17,026/呎
-(26年-01月)</t>
-        </is>
-      </c>
-      <c r="G30" s="16" t="inlineStr">
-        <is>
-          <t>F | 431呎 (2房)
-$718万
-$16,661/呎
-(26年-01月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="65" customHeight="1">
-      <c r="A31" s="2" t="inlineStr">
-        <is>
-          <t>10/F</t>
-        </is>
-      </c>
-      <c r="B31" s="16" t="inlineStr">
-        <is>
-          <t>A | 640呎 (3房)
-$1,401万
-$21,884/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="C31" s="16" t="inlineStr">
-        <is>
-          <t>B | 695呎 (3房)
-$1,522万
-$21,892/呎
-(26年-02月)</t>
-        </is>
-      </c>
-      <c r="D31" s="18" t="inlineStr">
-        <is>
-          <t>C | 518呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E31" s="18" t="inlineStr">
-        <is>
-          <t>D | 436呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F31" s="16" t="inlineStr">
-        <is>
-          <t>E | 429呎 (2房)
-$729万
-$16,984/呎
-(26年-01月)</t>
-        </is>
-      </c>
-      <c r="G31" s="16" t="inlineStr">
-        <is>
-          <t>F | 431呎 (2房)
-$716万
-$16,622/呎
-(26年-01月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="65" customHeight="1">
-      <c r="A32" s="2" t="inlineStr">
-        <is>
-          <t>9/F</t>
-        </is>
-      </c>
-      <c r="B32" s="16" t="inlineStr">
-        <is>
-          <t>A | 640呎 (3房)
-$1,397万
-$21,831/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="C32" s="16" t="inlineStr">
-        <is>
-          <t>B | 695呎 (3房)
-$1,501万
-$21,591/呎
-(26年-01月)</t>
-        </is>
-      </c>
-      <c r="D32" s="18" t="inlineStr">
-        <is>
-          <t>C | 518呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E32" s="18" t="inlineStr">
-        <is>
-          <t>D | 436呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F32" s="16" t="inlineStr">
-        <is>
-          <t>E | 429呎 (2房)
-$727万
-$16,942/呎
-(26年-01月)</t>
-        </is>
-      </c>
-      <c r="G32" s="16" t="inlineStr">
-        <is>
-          <t>F | 431呎 (2房)
-$750万
-$17,408/呎
-(26年-05月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="65" customHeight="1">
-      <c r="A33" s="2" t="inlineStr">
-        <is>
-          <t>8/F</t>
-        </is>
-      </c>
-      <c r="B33" s="16" t="inlineStr">
-        <is>
-          <t>A | 640呎 (3房)
-$1,340万
-$20,939/呎
-(26年-01月)</t>
-        </is>
-      </c>
-      <c r="C33" s="16" t="inlineStr">
-        <is>
-          <t>B | 695呎 (3房)
-$1,497万
-$21,538/呎
-(26年-01月)</t>
-        </is>
-      </c>
-      <c r="D33" s="18" t="inlineStr">
-        <is>
-          <t>C | 518呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E33" s="18" t="inlineStr">
-        <is>
-          <t>D | 436呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F33" s="16" t="inlineStr">
-        <is>
-          <t>E | 429呎 (2房)
-$725万
-$16,897/呎
-(26年-01月)</t>
-        </is>
-      </c>
-      <c r="G33" s="16" t="inlineStr">
-        <is>
-          <t>F | 431呎 (2房)
-$748万
-$17,367/呎
-(26年-05月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="65" customHeight="1">
-      <c r="A34" s="2" t="inlineStr">
-        <is>
-          <t>7/F</t>
-        </is>
-      </c>
-      <c r="B34" s="18" t="inlineStr">
-        <is>
-          <t>A | 641呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C34" s="16" t="inlineStr">
-        <is>
-          <t>B | 695呎 (3房)
-$1,557万
-$22,404/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="D34" s="18" t="inlineStr">
-        <is>
-          <t>C | 518呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E34" s="18" t="inlineStr">
-        <is>
-          <t>D | 436呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F34" s="16" t="inlineStr">
-        <is>
-          <t>E | 429呎 (2房)
-$766万
-$17,853/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="G34" s="16" t="inlineStr">
-        <is>
-          <t>F | 431呎 (2房)
-$753万
-$17,473/呎
-(26年-05月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="35" ht="65" customHeight="1">
-      <c r="A35" s="2" t="inlineStr">
-        <is>
-          <t>6/F</t>
-        </is>
-      </c>
-      <c r="B35" s="18" t="inlineStr">
-        <is>
-          <t>A | 641呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C35" s="19" t="inlineStr">
-        <is>
-          <t>B | 696呎 (3房)
-$1,688万
-$24,257/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="D35" s="18" t="inlineStr">
-        <is>
-          <t>C | 518呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E35" s="18" t="inlineStr">
-        <is>
-          <t>D | 436呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F35" s="16" t="inlineStr">
-        <is>
-          <t>E | 429呎 (2房)
-$756万
-$17,611/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="G35" s="16" t="inlineStr">
-        <is>
-          <t>F | 431呎 (2房)
-$743万
-$17,234/呎
-(26年-05月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" ht="65" customHeight="1">
-      <c r="A36" s="2" t="inlineStr">
-        <is>
-          <t>5/F</t>
-        </is>
-      </c>
-      <c r="B36" s="18" t="inlineStr">
-        <is>
-          <t>A | 641呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C36" s="18" t="inlineStr">
-        <is>
-          <t>B | 696呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D36" s="18" t="inlineStr">
-        <is>
-          <t>C | 518呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E36" s="18" t="inlineStr">
-        <is>
-          <t>D | 436呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F36" s="18" t="inlineStr">
-        <is>
-          <t>E | 429呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G36" s="18" t="inlineStr">
-        <is>
-          <t>F | 430呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="37" ht="65" customHeight="1">
-      <c r="A37" s="2" t="inlineStr">
-        <is>
-          <t>3/F</t>
-        </is>
-      </c>
-      <c r="B37" s="18" t="inlineStr">
-        <is>
-          <t>A | 641呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C37" s="18" t="inlineStr">
-        <is>
-          <t>B | 696呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D37" s="18" t="inlineStr">
-        <is>
-          <t>C | 518呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E37" s="18" t="inlineStr">
-        <is>
-          <t>D | 436呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F37" s="18" t="inlineStr">
-        <is>
-          <t>E | 429呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G37" s="18" t="inlineStr">
-        <is>
-          <t>F | 430呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="38" ht="65" customHeight="1">
-      <c r="A38" s="2" t="inlineStr">
-        <is>
-          <t>2/F</t>
-        </is>
-      </c>
-      <c r="B38" s="18" t="inlineStr">
-        <is>
-          <t>A | 641呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C38" s="18" t="inlineStr">
-        <is>
-          <t>B | 696呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D38" s="18" t="inlineStr">
-        <is>
-          <t>C | 518呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E38" s="18" t="inlineStr">
-        <is>
-          <t>D | 436呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F38" s="18" t="inlineStr">
-        <is>
-          <t>E | 434呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G38" s="17" t="inlineStr"/>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:G1"/>
-  </mergeCells>
-  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
-  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:K38"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
-    <col width="18" customWidth="1" min="8" max="8"/>
-    <col width="18" customWidth="1" min="9" max="9"/>
-    <col width="18" customWidth="1" min="10" max="10"/>
-    <col width="18" customWidth="1" min="11" max="11"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="40" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Double Coast III - 1B座 销控网格图</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="6" t="inlineStr">
-        <is>
-          <t>总套数</t>
-        </is>
-      </c>
-      <c r="B2" s="7" t="inlineStr">
-        <is>
-          <t>在售 (Sale)</t>
-        </is>
-      </c>
-      <c r="C2" s="8" t="inlineStr">
-        <is>
-          <t>已定价未售</t>
-        </is>
-      </c>
-      <c r="D2" s="9" t="inlineStr">
-        <is>
-          <t>已售 (Sold)</t>
-        </is>
-      </c>
-      <c r="E2" s="10" t="inlineStr">
-        <is>
-          <t>暂停销售</t>
-        </is>
-      </c>
-      <c r="F2" s="6" t="inlineStr">
-        <is>
-          <t>待售 (Pending)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="25" customHeight="1">
-      <c r="A3" s="11" t="inlineStr">
-        <is>
-          <t>329 套</t>
-        </is>
-      </c>
-      <c r="B3" s="12" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="C3" s="13" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="D3" s="14" t="inlineStr">
-        <is>
-          <t>147 套</t>
-        </is>
-      </c>
-      <c r="E3" s="15" t="inlineStr">
-        <is>
-          <t>2 套</t>
-        </is>
-      </c>
-      <c r="F3" s="11" t="inlineStr">
-        <is>
-          <t>180 套</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="25" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>楼层\房号</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>E</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>G</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>H</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>J</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>K</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="65" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>39/F</t>
-        </is>
-      </c>
-      <c r="B6" s="17" t="inlineStr"/>
-      <c r="C6" s="18" t="inlineStr">
-        <is>
-          <t>B | 455呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D6" s="18" t="inlineStr">
-        <is>
-          <t>C | 330呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E6" s="18" t="inlineStr">
-        <is>
-          <t>D | 311呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F6" s="18" t="inlineStr">
-        <is>
-          <t>E | 319呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G6" s="18" t="inlineStr">
-        <is>
-          <t>F | 319呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="H6" s="18" t="inlineStr">
-        <is>
-          <t>G | 249呎 (开放式)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="I6" s="18" t="inlineStr">
-        <is>
-          <t>H | 322呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="J6" s="18" t="inlineStr">
-        <is>
-          <t>J | 414呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="K6" s="18" t="inlineStr">
-        <is>
-          <t>K | 423呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="65" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>38/F</t>
-        </is>
-      </c>
-      <c r="B7" s="18" t="inlineStr">
-        <is>
-          <t>A | 468呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C7" s="18" t="inlineStr">
-        <is>
-          <t>B | 455呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D7" s="18" t="inlineStr">
-        <is>
-          <t>C | 330呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E7" s="18" t="inlineStr">
-        <is>
-          <t>D | 311呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F7" s="18" t="inlineStr">
-        <is>
-          <t>E | 319呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G7" s="18" t="inlineStr">
-        <is>
-          <t>F | 319呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="H7" s="18" t="inlineStr">
-        <is>
-          <t>G | 249呎 (开放式)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="I7" s="18" t="inlineStr">
-        <is>
-          <t>H | 322呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="J7" s="18" t="inlineStr">
-        <is>
-          <t>J | 414呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="K7" s="18" t="inlineStr">
-        <is>
-          <t>K | 423呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="65" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>37/F</t>
-        </is>
-      </c>
-      <c r="B8" s="18" t="inlineStr">
-        <is>
-          <t>A | 468呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C8" s="18" t="inlineStr">
-        <is>
-          <t>B | 455呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D8" s="18" t="inlineStr">
-        <is>
-          <t>C | 330呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E8" s="18" t="inlineStr">
-        <is>
-          <t>D | 311呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F8" s="18" t="inlineStr">
-        <is>
-          <t>E | 319呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G8" s="18" t="inlineStr">
-        <is>
-          <t>F | 319呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="H8" s="18" t="inlineStr">
-        <is>
-          <t>G | 249呎 (开放式)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="I8" s="18" t="inlineStr">
-        <is>
-          <t>H | 322呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="J8" s="18" t="inlineStr">
-        <is>
-          <t>J | 414呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="K8" s="18" t="inlineStr">
-        <is>
-          <t>K | 423呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="65" customHeight="1">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>36/F</t>
-        </is>
-      </c>
-      <c r="B9" s="18" t="inlineStr">
-        <is>
-          <t>A | 468呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C9" s="18" t="inlineStr">
-        <is>
-          <t>B | 455呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D9" s="16" t="inlineStr">
-        <is>
-          <t>C | 329呎 (1房)
-$639万
-$19,416/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="E9" s="18" t="inlineStr">
-        <is>
-          <t>D | 311呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F9" s="16" t="inlineStr">
-        <is>
-          <t>E | 320呎 (1房)
-$622万
-$19,431/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="G9" s="16" t="inlineStr">
-        <is>
-          <t>F | 320呎 (1房)
-$620万
-$19,369/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="H9" s="16" t="inlineStr">
-        <is>
-          <t>G | 250呎 (开放式)
-$478万
-$19,136/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="I9" s="18" t="inlineStr">
-        <is>
-          <t>H | 322呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="J9" s="18" t="inlineStr">
-        <is>
-          <t>J | 414呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="K9" s="18" t="inlineStr">
-        <is>
-          <t>K | 423呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="65" customHeight="1">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>35/F</t>
-        </is>
-      </c>
-      <c r="B10" s="18" t="inlineStr">
-        <is>
-          <t>A | 468呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C10" s="18" t="inlineStr">
-        <is>
-          <t>B | 455呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D10" s="16" t="inlineStr">
-        <is>
-          <t>C | 329呎 (1房)
-$637万
-$19,368/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="E10" s="18" t="inlineStr">
-        <is>
-          <t>D | 311呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F10" s="16" t="inlineStr">
-        <is>
-          <t>E | 320呎 (1房)
-$620万
-$19,384/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="G10" s="16" t="inlineStr">
-        <is>
-          <t>F | 320呎 (1房)
-$618万
-$19,319/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="H10" s="16" t="inlineStr">
-        <is>
-          <t>G | 250呎 (开放式)
-$477万
-$19,092/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="I10" s="18" t="inlineStr">
-        <is>
-          <t>H | 322呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="J10" s="16" t="inlineStr">
-        <is>
-          <t>J | 414呎 (2房)
-$829万
-$20,019/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="K10" s="18" t="inlineStr">
-        <is>
-          <t>K | 423呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="65" customHeight="1">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>33/F</t>
-        </is>
-      </c>
-      <c r="B11" s="18" t="inlineStr">
-        <is>
-          <t>A | 468呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C11" s="18" t="inlineStr">
-        <is>
-          <t>B | 455呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D11" s="16" t="inlineStr">
-        <is>
-          <t>C | 329呎 (1房)
-$643万
-$19,535/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="E11" s="18" t="inlineStr">
-        <is>
-          <t>D | 311呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F11" s="16" t="inlineStr">
-        <is>
-          <t>E | 320呎 (1房)
-$619万
-$19,338/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="G11" s="16" t="inlineStr">
-        <is>
-          <t>F | 320呎 (1房)
-$622万
-$19,431/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="H11" s="16" t="inlineStr">
-        <is>
-          <t>G | 250呎 (开放式)
-$482万
-$19,260/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="I11" s="18" t="inlineStr">
-        <is>
-          <t>H | 322呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="J11" s="16" t="inlineStr">
-        <is>
-          <t>J | 414呎 (2房)
-$836万
-$20,196/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="K11" s="18" t="inlineStr">
-        <is>
-          <t>K | 423呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="65" customHeight="1">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>32/F</t>
-        </is>
-      </c>
-      <c r="B12" s="18" t="inlineStr">
-        <is>
-          <t>A | 468呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C12" s="18" t="inlineStr">
-        <is>
-          <t>B | 455呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D12" s="16" t="inlineStr">
-        <is>
-          <t>C | 329呎 (1房)
-$629万
-$19,109/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="E12" s="18" t="inlineStr">
-        <is>
-          <t>D | 311呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F12" s="16" t="inlineStr">
-        <is>
-          <t>E | 320呎 (1房)
-$617万
-$19,291/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="G12" s="16" t="inlineStr">
-        <is>
-          <t>F | 320呎 (1房)
-$622万
-$19,438/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="H12" s="16" t="inlineStr">
-        <is>
-          <t>G | 250呎 (开放式)
-$475万
-$18,996/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="I12" s="18" t="inlineStr">
-        <is>
-          <t>H | 322呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="J12" s="16" t="inlineStr">
-        <is>
-          <t>J | 414呎 (2房)
-$825万
-$19,920/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="K12" s="18" t="inlineStr">
-        <is>
-          <t>K | 423呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="65" customHeight="1">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>31/F</t>
-        </is>
-      </c>
-      <c r="B13" s="18" t="inlineStr">
-        <is>
-          <t>A | 468呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C13" s="18" t="inlineStr">
-        <is>
-          <t>B | 455呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D13" s="16" t="inlineStr">
-        <is>
-          <t>C | 329呎 (1房)
-$627万
-$19,061/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="E13" s="18" t="inlineStr">
-        <is>
-          <t>D | 311呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F13" s="16" t="inlineStr">
-        <is>
-          <t>E | 320呎 (1房)
-$616万
-$19,241/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="G13" s="16" t="inlineStr">
-        <is>
-          <t>F | 320呎 (1房)
-$614万
-$19,175/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="H13" s="16" t="inlineStr">
-        <is>
-          <t>G | 250呎 (开放式)
-$474万
-$18,948/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="I13" s="18" t="inlineStr">
-        <is>
-          <t>H | 322呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="J13" s="16" t="inlineStr">
-        <is>
-          <t>J | 414呎 (2房)
-$823万
-$19,872/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="K13" s="18" t="inlineStr">
-        <is>
-          <t>K | 423呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="65" customHeight="1">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>30/F</t>
-        </is>
-      </c>
-      <c r="B14" s="18" t="inlineStr">
-        <is>
-          <t>A | 468呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C14" s="18" t="inlineStr">
-        <is>
-          <t>B | 455呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D14" s="16" t="inlineStr">
-        <is>
-          <t>C | 329呎 (1房)
-$626万
-$19,015/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="E14" s="18" t="inlineStr">
-        <is>
-          <t>D | 311呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F14" s="16" t="inlineStr">
-        <is>
-          <t>E | 320呎 (1房)
-$613万
-$19,156/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="G14" s="16" t="inlineStr">
-        <is>
-          <t>F | 320呎 (1房)
-$583万
-$18,219/呎
-(26年-03月)</t>
-        </is>
-      </c>
-      <c r="H14" s="16" t="inlineStr">
-        <is>
-          <t>G | 250呎 (开放式)
-$473万
-$18,904/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="I14" s="18" t="inlineStr">
-        <is>
-          <t>H | 322呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="J14" s="16" t="inlineStr">
-        <is>
-          <t>J | 414呎 (2房)
-$820万
-$19,819/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="K14" s="18" t="inlineStr">
-        <is>
-          <t>K | 423呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="65" customHeight="1">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>29/F</t>
-        </is>
-      </c>
-      <c r="B15" s="18" t="inlineStr">
-        <is>
-          <t>A | 468呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C15" s="16" t="inlineStr">
-        <is>
-          <t>B | 454呎 (2房)
-$962万
-$21,198/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="D15" s="16" t="inlineStr">
-        <is>
-          <t>C | 329呎 (1房)
-$624万
-$18,967/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="E15" s="18" t="inlineStr">
-        <is>
-          <t>D | 311呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F15" s="16" t="inlineStr">
-        <is>
-          <t>E | 320呎 (1房)
-$611万
-$19,106/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="G15" s="16" t="inlineStr">
-        <is>
-          <t>F | 320呎 (1房)
-$582万
-$18,172/呎
-(26年-02月)</t>
-        </is>
-      </c>
-      <c r="H15" s="16" t="inlineStr">
-        <is>
-          <t>G | 250呎 (开放式)
-$471万
-$18,852/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="I15" s="18" t="inlineStr">
-        <is>
-          <t>H | 322呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="J15" s="16" t="inlineStr">
-        <is>
-          <t>J | 414呎 (2房)
-$818万
-$19,771/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="K15" s="18" t="inlineStr">
-        <is>
-          <t>K | 423呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="65" customHeight="1">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>28/F</t>
-        </is>
-      </c>
-      <c r="B16" s="18" t="inlineStr">
-        <is>
-          <t>A | 468呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C16" s="18" t="inlineStr">
-        <is>
-          <t>B | 455呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D16" s="18" t="inlineStr">
-        <is>
-          <t>C | 330呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E16" s="18" t="inlineStr">
-        <is>
-          <t>D | 311呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F16" s="18" t="inlineStr">
-        <is>
-          <t>E | 319呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G16" s="18" t="inlineStr">
-        <is>
-          <t>F | 319呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="H16" s="18" t="inlineStr">
-        <is>
-          <t>G | 249呎 (开放式)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="I16" s="18" t="inlineStr">
-        <is>
-          <t>H | 322呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="J16" s="18" t="inlineStr">
-        <is>
-          <t>J | 414呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="K16" s="18" t="inlineStr">
-        <is>
-          <t>K | 423呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="65" customHeight="1">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>27/F</t>
-        </is>
-      </c>
-      <c r="B17" s="18" t="inlineStr">
-        <is>
-          <t>A | 468呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C17" s="16" t="inlineStr">
-        <is>
-          <t>B | 454呎 (2房)
-$955万
-$21,040/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="D17" s="16" t="inlineStr">
-        <is>
-          <t>C | 329呎 (1房)
-$619万
-$18,827/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="E17" s="18" t="inlineStr">
-        <is>
-          <t>D | 311呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F17" s="16" t="inlineStr">
-        <is>
-          <t>E | 320呎 (1房)
-$607万
-$18,966/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="G17" s="16" t="inlineStr">
-        <is>
-          <t>F | 320呎 (1房)
-$577万
-$18,038/呎
-(26年-02月)</t>
-        </is>
-      </c>
-      <c r="H17" s="16" t="inlineStr">
-        <is>
-          <t>G | 250呎 (开放式)
-$468万
-$18,712/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="I17" s="18" t="inlineStr">
-        <is>
-          <t>H | 322呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="J17" s="16" t="inlineStr">
-        <is>
-          <t>J | 414呎 (2房)
-$812万
-$19,623/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="K17" s="18" t="inlineStr">
-        <is>
-          <t>K | 423呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="65" customHeight="1">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>26/F</t>
-        </is>
-      </c>
-      <c r="B18" s="18" t="inlineStr">
-        <is>
-          <t>A | 468呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C18" s="16" t="inlineStr">
-        <is>
-          <t>B | 454呎 (2房)
-$953万
-$20,987/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="D18" s="16" t="inlineStr">
-        <is>
-          <t>C | 329呎 (1房)
-$618万
-$18,781/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="E18" s="18" t="inlineStr">
-        <is>
-          <t>D | 311呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F18" s="16" t="inlineStr">
-        <is>
-          <t>E | 320呎 (1房)
-$579万
-$18,106/呎
-(26年-02月)</t>
-        </is>
-      </c>
-      <c r="G18" s="16" t="inlineStr">
-        <is>
-          <t>F | 320呎 (1房)
-$576万
-$17,991/呎
-(26年-02月)</t>
-        </is>
-      </c>
-      <c r="H18" s="16" t="inlineStr">
-        <is>
-          <t>G | 250呎 (开放式)
-$467万
-$18,668/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="I18" s="18" t="inlineStr">
-        <is>
-          <t>H | 322呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="J18" s="16" t="inlineStr">
-        <is>
-          <t>J | 414呎 (2房)
-$810万
-$19,575/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="K18" s="18" t="inlineStr">
-        <is>
-          <t>K | 423呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="65" customHeight="1">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>25/F</t>
-        </is>
-      </c>
-      <c r="B19" s="18" t="inlineStr">
-        <is>
-          <t>A | 468呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C19" s="16" t="inlineStr">
-        <is>
-          <t>B | 454呎 (2房)
-$961万
-$21,172/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="D19" s="16" t="inlineStr">
-        <is>
-          <t>C | 329呎 (1房)
-$616万
-$18,733/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="E19" s="18" t="inlineStr">
-        <is>
-          <t>D | 311呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F19" s="16" t="inlineStr">
-        <is>
-          <t>E | 320呎 (1房)
-$604万
-$18,872/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="G19" s="16" t="inlineStr">
-        <is>
-          <t>F | 320呎 (1房)
-$574万
-$17,944/呎
-(26年-02月)</t>
-        </is>
-      </c>
-      <c r="H19" s="16" t="inlineStr">
-        <is>
-          <t>G | 250呎 (开放式)
-$471万
-$18,828/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="I19" s="18" t="inlineStr">
-        <is>
-          <t>H | 322呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="J19" s="16" t="inlineStr">
-        <is>
-          <t>J | 414呎 (2房)
-$817万
-$19,744/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="K19" s="18" t="inlineStr">
-        <is>
-          <t>K | 423呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="65" customHeight="1">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>23/F</t>
-        </is>
-      </c>
-      <c r="B20" s="18" t="inlineStr">
-        <is>
-          <t>A | 468呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C20" s="16" t="inlineStr">
-        <is>
-          <t>B | 454呎 (2房)
-$959万
-$21,117/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="D20" s="16" t="inlineStr">
-        <is>
-          <t>C | 329呎 (1房)
-$615万
-$18,687/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="E20" s="18" t="inlineStr">
-        <is>
-          <t>D | 311呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F20" s="16" t="inlineStr">
-        <is>
-          <t>E | 320呎 (1房)
-$602万
-$18,825/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="G20" s="16" t="inlineStr">
-        <is>
-          <t>F | 320呎 (1房)
-$573万
-$17,900/呎
-(26年-02月)</t>
-        </is>
-      </c>
-      <c r="H20" s="16" t="inlineStr">
-        <is>
-          <t>G | 250呎 (开放式)
-$475万
-$18,992/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="I20" s="18" t="inlineStr">
-        <is>
-          <t>H | 322呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="J20" s="16" t="inlineStr">
-        <is>
-          <t>J | 414呎 (2房)
-$815万
-$19,696/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="K20" s="18" t="inlineStr">
-        <is>
-          <t>K | 423呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="65" customHeight="1">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>22/F</t>
-        </is>
-      </c>
-      <c r="B21" s="18" t="inlineStr">
-        <is>
-          <t>A | 468呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C21" s="16" t="inlineStr">
-        <is>
-          <t>B | 454呎 (2房)
-$946万
-$20,830/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="D21" s="16" t="inlineStr">
-        <is>
-          <t>C | 329呎 (1房)
-$613万
-$18,641/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="E21" s="18" t="inlineStr">
-        <is>
-          <t>D | 311呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F21" s="16" t="inlineStr">
-        <is>
-          <t>E | 320呎 (1房)
-$601万
-$18,775/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="G21" s="16" t="inlineStr">
-        <is>
-          <t>F | 320呎 (1房)
-$571万
-$17,856/呎
-(26年-02月)</t>
-        </is>
-      </c>
-      <c r="H21" s="16" t="inlineStr">
-        <is>
-          <t>G | 250呎 (开放式)
-$468万
-$18,736/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="I21" s="18" t="inlineStr">
-        <is>
-          <t>H | 322呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="J21" s="16" t="inlineStr">
-        <is>
-          <t>J | 414呎 (2房)
-$804万
-$19,428/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="K21" s="18" t="inlineStr">
-        <is>
-          <t>K | 423呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="65" customHeight="1">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>21/F</t>
-        </is>
-      </c>
-      <c r="B22" s="18" t="inlineStr">
-        <is>
-          <t>A | 468呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C22" s="16" t="inlineStr">
-        <is>
-          <t>B | 454呎 (2房)
-$943万
-$20,780/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="D22" s="16" t="inlineStr">
-        <is>
-          <t>C | 329呎 (1房)
-$612万
-$18,593/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="E22" s="18" t="inlineStr">
-        <is>
-          <t>D | 311呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F22" s="16" t="inlineStr">
-        <is>
-          <t>E | 320呎 (1房)
-$599万
-$18,728/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="G22" s="16" t="inlineStr">
-        <is>
-          <t>F | 320呎 (1房)
-$570万
-$17,812/呎
-(26年-01月)</t>
-        </is>
-      </c>
-      <c r="H22" s="16" t="inlineStr">
-        <is>
-          <t>G | 250呎 (开放式)
-$462万
-$18,480/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="I22" s="18" t="inlineStr">
-        <is>
-          <t>H | 322呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="J22" s="16" t="inlineStr">
-        <is>
-          <t>J | 414呎 (2房)
-$811万
-$19,599/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="K22" s="18" t="inlineStr">
-        <is>
-          <t>K | 423呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="65" customHeight="1">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>20/F</t>
-        </is>
-      </c>
-      <c r="B23" s="18" t="inlineStr">
-        <is>
-          <t>A | 468呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C23" s="16" t="inlineStr">
-        <is>
-          <t>B | 454呎 (2房)
-$923万
-$20,322/呎
-(26年-03月)</t>
-        </is>
-      </c>
-      <c r="D23" s="16" t="inlineStr">
-        <is>
-          <t>C | 329呎 (1房)
-$610万
-$18,547/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="E23" s="18" t="inlineStr">
-        <is>
-          <t>D | 311呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F23" s="16" t="inlineStr">
-        <is>
-          <t>E | 320呎 (1房)
-$566万
-$17,678/呎
-(26年-02月)</t>
-        </is>
-      </c>
-      <c r="G23" s="16" t="inlineStr">
-        <is>
-          <t>F | 320呎 (1房)
-$568万
-$17,766/呎
-(26年-02月)</t>
-        </is>
-      </c>
-      <c r="H23" s="16" t="inlineStr">
-        <is>
-          <t>G | 250呎 (开放式)
-$461万
-$18,436/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="I23" s="18" t="inlineStr">
-        <is>
-          <t>H | 322呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="J23" s="16" t="inlineStr">
-        <is>
-          <t>J | 414呎 (2房)
-$800万
-$19,331/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="K23" s="18" t="inlineStr">
-        <is>
-          <t>K | 423呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="65" customHeight="1">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>19/F</t>
-        </is>
-      </c>
-      <c r="B24" s="18" t="inlineStr">
-        <is>
-          <t>A | 468呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C24" s="16" t="inlineStr">
-        <is>
-          <t>B | 454呎 (2房)
-$931万
-$20,500/呎
-(26年-03月)</t>
-        </is>
-      </c>
-      <c r="D24" s="16" t="inlineStr">
-        <is>
-          <t>C | 329呎 (1房)
-$609万
-$18,498/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="E24" s="18" t="inlineStr">
-        <is>
-          <t>D | 311呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F24" s="16" t="inlineStr">
-        <is>
-          <t>E | 320呎 (1房)
-$564万
-$17,634/呎
-(26年-01月)</t>
-        </is>
-      </c>
-      <c r="G24" s="16" t="inlineStr">
-        <is>
-          <t>F | 320呎 (1房)
-$567万
-$17,722/呎
-(26年-02月)</t>
-        </is>
-      </c>
-      <c r="H24" s="16" t="inlineStr">
-        <is>
-          <t>G | 250呎 (开放式)
-$465万
-$18,596/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="I24" s="18" t="inlineStr">
-        <is>
-          <t>H | 322呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="J24" s="16" t="inlineStr">
-        <is>
-          <t>J | 414呎 (2房)
-$798万
-$19,285/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="K24" s="18" t="inlineStr">
-        <is>
-          <t>K | 423呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="65" customHeight="1">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>18/F</t>
-        </is>
-      </c>
-      <c r="B25" s="18" t="inlineStr">
-        <is>
-          <t>A | 468呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C25" s="16" t="inlineStr">
-        <is>
-          <t>B | 454呎 (2房)
-$918万
-$20,220/呎
-(26年-02月)</t>
-        </is>
-      </c>
-      <c r="D25" s="16" t="inlineStr">
-        <is>
-          <t>C | 329呎 (1房)
-$607万
-$18,453/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="E25" s="18" t="inlineStr">
-        <is>
-          <t>D | 311呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F25" s="16" t="inlineStr">
-        <is>
-          <t>E | 320呎 (1房)
-$563万
-$17,591/呎
-(26年-01月)</t>
-        </is>
-      </c>
-      <c r="G25" s="16" t="inlineStr">
-        <is>
-          <t>F | 320呎 (1房)
-$566万
-$17,678/呎
-(26年-02月)</t>
-        </is>
-      </c>
-      <c r="H25" s="16" t="inlineStr">
-        <is>
-          <t>G | 250呎 (开放式)
-$459万
-$18,344/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="I25" s="18" t="inlineStr">
-        <is>
-          <t>H | 322呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="J25" s="16" t="inlineStr">
-        <is>
-          <t>J | 414呎 (2房)
-$796万
-$19,234/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="K25" s="18" t="inlineStr">
-        <is>
-          <t>K | 423呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="65" customHeight="1">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>17/F</t>
-        </is>
-      </c>
-      <c r="B26" s="18" t="inlineStr">
-        <is>
-          <t>A | 468呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C26" s="16" t="inlineStr">
-        <is>
-          <t>B | 454呎 (2房)
-$913万
-$20,119/呎
-(26年-03月)</t>
-        </is>
-      </c>
-      <c r="D26" s="16" t="inlineStr">
-        <is>
-          <t>C | 329呎 (1房)
-$604万
-$18,362/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="E26" s="18" t="inlineStr">
-        <is>
-          <t>D | 311呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F26" s="16" t="inlineStr">
-        <is>
-          <t>E | 320呎 (1房)
-$560万
-$17,503/呎
-(26年-01月)</t>
-        </is>
-      </c>
-      <c r="G26" s="16" t="inlineStr">
-        <is>
-          <t>F | 320呎 (1房)
-$563万
-$17,591/呎
-(26年-02月)</t>
-        </is>
-      </c>
-      <c r="H26" s="16" t="inlineStr">
-        <is>
-          <t>G | 250呎 (开放式)
-$426万
-$17,056/呎
-(26年-01月)</t>
-        </is>
-      </c>
-      <c r="I26" s="18" t="inlineStr">
-        <is>
-          <t>H | 322呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="J26" s="16" t="inlineStr">
-        <is>
-          <t>J | 414呎 (2房)
-$792万
-$19,140/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="K26" s="18" t="inlineStr">
-        <is>
-          <t>K | 423呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="65" customHeight="1">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>16/F</t>
-        </is>
-      </c>
-      <c r="B27" s="18" t="inlineStr">
-        <is>
-          <t>A | 468呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C27" s="16" t="inlineStr">
-        <is>
-          <t>B | 454呎 (2房)
-$911万
-$20,068/呎
-(26年-02月)</t>
-        </is>
-      </c>
-      <c r="D27" s="16" t="inlineStr">
-        <is>
-          <t>C | 329呎 (1房)
-$603万
-$18,319/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="E27" s="18" t="inlineStr">
-        <is>
-          <t>D | 311呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F27" s="16" t="inlineStr">
-        <is>
-          <t>E | 320呎 (1房)
-$559万
-$17,462/呎
-(26年-01月)</t>
-        </is>
-      </c>
-      <c r="G27" s="16" t="inlineStr">
-        <is>
-          <t>F | 320呎 (1房)
-$562万
-$17,547/呎
-(26年-02月)</t>
-        </is>
-      </c>
-      <c r="H27" s="16" t="inlineStr">
-        <is>
-          <t>G | 250呎 (开放式)
-$425万
-$17,016/呎
-(26年-01月)</t>
-        </is>
-      </c>
-      <c r="I27" s="18" t="inlineStr">
-        <is>
-          <t>H | 322呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="J27" s="16" t="inlineStr">
-        <is>
-          <t>J | 414呎 (2房)
-$790万
-$19,094/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="K27" s="18" t="inlineStr">
-        <is>
-          <t>K | 423呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="65" customHeight="1">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>15/F</t>
-        </is>
-      </c>
-      <c r="B28" s="18" t="inlineStr">
-        <is>
-          <t>A | 468呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C28" s="16" t="inlineStr">
-        <is>
-          <t>B | 454呎 (2房)
-$909万
-$20,018/呎
-(26年-02月)</t>
-        </is>
-      </c>
-      <c r="D28" s="16" t="inlineStr">
-        <is>
-          <t>C | 329呎 (1房)
-$601万
-$18,274/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="E28" s="18" t="inlineStr">
-        <is>
-          <t>D | 311呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F28" s="16" t="inlineStr">
-        <is>
-          <t>E | 320呎 (1房)
-$557万
-$17,419/呎
-(26年-01月)</t>
-        </is>
-      </c>
-      <c r="G28" s="16" t="inlineStr">
-        <is>
-          <t>F | 320呎 (1房)
-$560万
-$17,503/呎
-(26年-01月)</t>
-        </is>
-      </c>
-      <c r="H28" s="16" t="inlineStr">
-        <is>
-          <t>G | 250呎 (开放式)
-$424万
-$16,972/呎
-(26年-01月)</t>
-        </is>
-      </c>
-      <c r="I28" s="18" t="inlineStr">
-        <is>
-          <t>H | 322呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="J28" s="16" t="inlineStr">
-        <is>
-          <t>J | 414呎 (2房)
-$744万
-$17,966/呎
-(26年-01月)</t>
-        </is>
-      </c>
-      <c r="K28" s="18" t="inlineStr">
-        <is>
-          <t>K | 423呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="65" customHeight="1">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>12/F</t>
-        </is>
-      </c>
-      <c r="B29" s="18" t="inlineStr">
-        <is>
-          <t>A | 468呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C29" s="16" t="inlineStr">
-        <is>
-          <t>B | 454呎 (2房)
-$906万
-$19,967/呎
-(26年-03月)</t>
-        </is>
-      </c>
-      <c r="D29" s="16" t="inlineStr">
-        <is>
-          <t>C | 329呎 (1房)
-$606万
-$18,432/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="E29" s="18" t="inlineStr">
-        <is>
-          <t>D | 311呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F29" s="16" t="inlineStr">
-        <is>
-          <t>E | 320呎 (1房)
-$556万
-$17,372/呎
-(26年-01月)</t>
-        </is>
-      </c>
-      <c r="G29" s="16" t="inlineStr">
-        <is>
-          <t>F | 320呎 (1房)
-$559万
-$17,459/呎
-(26年-02月)</t>
-        </is>
-      </c>
-      <c r="H29" s="16" t="inlineStr">
-        <is>
-          <t>G | 250呎 (开放式)
-$442万
-$17,700/呎
-(26年-01月)</t>
-        </is>
-      </c>
-      <c r="I29" s="18" t="inlineStr">
-        <is>
-          <t>H | 322呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="J29" s="16" t="inlineStr">
-        <is>
-          <t>J | 414呎 (2房)
-$776万
-$18,737/呎
-(26年-01月)</t>
-        </is>
-      </c>
-      <c r="K29" s="18" t="inlineStr">
-        <is>
-          <t>K | 423呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="65" customHeight="1">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t>11/F</t>
-        </is>
-      </c>
-      <c r="B30" s="18" t="inlineStr">
-        <is>
-          <t>A | 468呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C30" s="16" t="inlineStr">
-        <is>
-          <t>B | 454呎 (2房)
-$904万
-$19,919/呎
-(26年-03月)</t>
-        </is>
-      </c>
-      <c r="D30" s="16" t="inlineStr">
-        <is>
-          <t>C | 329呎 (1房)
-$598万
-$18,179/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="E30" s="18" t="inlineStr">
-        <is>
-          <t>D | 311呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F30" s="16" t="inlineStr">
-        <is>
-          <t>E | 320呎 (1房)
-$554万
-$17,328/呎
-(26年-01月)</t>
-        </is>
-      </c>
-      <c r="G30" s="16" t="inlineStr">
-        <is>
-          <t>F | 320呎 (1房)
-$557万
-$17,419/呎
-(26年-02月)</t>
-        </is>
-      </c>
-      <c r="H30" s="16" t="inlineStr">
-        <is>
-          <t>G | 250呎 (开放式)
-$422万
-$16,888/呎
-(26年-01月)</t>
-        </is>
-      </c>
-      <c r="I30" s="18" t="inlineStr">
-        <is>
-          <t>H | 322呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="J30" s="16" t="inlineStr">
-        <is>
-          <t>J | 414呎 (2房)
-$774万
-$18,691/呎
-(26年-01月)</t>
-        </is>
-      </c>
-      <c r="K30" s="18" t="inlineStr">
-        <is>
-          <t>K | 423呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="65" customHeight="1">
-      <c r="A31" s="2" t="inlineStr">
-        <is>
-          <t>10/F</t>
-        </is>
-      </c>
-      <c r="B31" s="18" t="inlineStr">
-        <is>
-          <t>A | 468呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C31" s="16" t="inlineStr">
-        <is>
-          <t>B | 454呎 (2房)
-$902万
-$19,868/呎
-(26年-01月)</t>
-        </is>
-      </c>
-      <c r="D31" s="16" t="inlineStr">
-        <is>
-          <t>C | 329呎 (1房)
-$597万
-$18,134/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="E31" s="18" t="inlineStr">
-        <is>
-          <t>D | 311呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F31" s="16" t="inlineStr">
-        <is>
-          <t>E | 320呎 (1房)
-$553万
-$17,284/呎
-(26年-01月)</t>
-        </is>
-      </c>
-      <c r="G31" s="16" t="inlineStr">
-        <is>
-          <t>F | 320呎 (1房)
-$556万
-$17,372/呎
-(26年-02月)</t>
-        </is>
-      </c>
-      <c r="H31" s="16" t="inlineStr">
-        <is>
-          <t>G | 250呎 (开放式)
-$421万
-$16,844/呎
-(26年-01月)</t>
-        </is>
-      </c>
-      <c r="I31" s="18" t="inlineStr">
-        <is>
-          <t>H | 322呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="J31" s="16" t="inlineStr">
-        <is>
-          <t>J | 414呎 (2房)
-$738万
-$17,833/呎
-(26年-01月)</t>
-        </is>
-      </c>
-      <c r="K31" s="18" t="inlineStr">
-        <is>
-          <t>K | 423呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="65" customHeight="1">
-      <c r="A32" s="2" t="inlineStr">
-        <is>
-          <t>9/F</t>
-        </is>
-      </c>
-      <c r="B32" s="18" t="inlineStr">
-        <is>
-          <t>A | 468呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C32" s="16" t="inlineStr">
-        <is>
-          <t>B | 454呎 (2房)
-$900万
-$19,819/呎
-(26年-02月)</t>
-        </is>
-      </c>
-      <c r="D32" s="16" t="inlineStr">
-        <is>
-          <t>C | 329呎 (1房)
-$595万
-$18,091/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="E32" s="18" t="inlineStr">
-        <is>
-          <t>D | 311呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F32" s="16" t="inlineStr">
-        <is>
-          <t>E | 320呎 (1房)
-$577万
-$18,028/呎
-(26年-01月)</t>
-        </is>
-      </c>
-      <c r="G32" s="16" t="inlineStr">
-        <is>
-          <t>F | 320呎 (1房)
-$561万
-$17,525/呎
-(26年-01月)</t>
-        </is>
-      </c>
-      <c r="H32" s="16" t="inlineStr">
-        <is>
-          <t>G | 250呎 (开放式)
-$420万
-$16,804/呎
-(26年-01月)</t>
-        </is>
-      </c>
-      <c r="I32" s="18" t="inlineStr">
-        <is>
-          <t>H | 322呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="J32" s="16" t="inlineStr">
-        <is>
-          <t>J | 414呎 (2房)
-$736万
-$17,787/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="K32" s="18" t="inlineStr">
-        <is>
-          <t>K | 423呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="65" customHeight="1">
-      <c r="A33" s="2" t="inlineStr">
-        <is>
-          <t>8/F</t>
-        </is>
-      </c>
-      <c r="B33" s="18" t="inlineStr">
-        <is>
-          <t>A | 468呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C33" s="16" t="inlineStr">
-        <is>
-          <t>B | 454呎 (2房)
-$908万
-$19,996/呎
-(26年-03月)</t>
-        </is>
-      </c>
-      <c r="D33" s="16" t="inlineStr">
-        <is>
-          <t>C | 329呎 (1房)
-$594万
-$18,046/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="E33" s="18" t="inlineStr">
-        <is>
-          <t>D | 311呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F33" s="16" t="inlineStr">
-        <is>
-          <t>E | 320呎 (1房)
-$582万
-$18,178/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="G33" s="16" t="inlineStr">
-        <is>
-          <t>F | 320呎 (1房)
-$553万
-$17,284/呎
-(26年-02月)</t>
-        </is>
-      </c>
-      <c r="H33" s="16" t="inlineStr">
-        <is>
-          <t>G | 250呎 (开放式)
-$419万
-$16,764/呎
-(26年-01月)</t>
-        </is>
-      </c>
-      <c r="I33" s="18" t="inlineStr">
-        <is>
-          <t>H | 322呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="J33" s="16" t="inlineStr">
-        <is>
-          <t>J | 414呎 (2房)
-$735万
-$17,744/呎
-(26年-01月)</t>
-        </is>
-      </c>
-      <c r="K33" s="18" t="inlineStr">
-        <is>
-          <t>K | 423呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="65" customHeight="1">
-      <c r="A34" s="2" t="inlineStr">
-        <is>
-          <t>7/F</t>
-        </is>
-      </c>
-      <c r="B34" s="18" t="inlineStr">
-        <is>
-          <t>A | 468呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C34" s="16" t="inlineStr">
-        <is>
-          <t>B | 454呎 (2房)
-$903万
-$19,894/呎
-(26年-03月)</t>
-        </is>
-      </c>
-      <c r="D34" s="16" t="inlineStr">
-        <is>
-          <t>C | 329呎 (1房)
-$596万
-$18,106/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="E34" s="18" t="inlineStr">
-        <is>
-          <t>D | 311呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F34" s="20" t="inlineStr">
-        <is>
-          <t>E | 319呎 (1房)
-$622万
-$19,508/呎
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="G34" s="16" t="inlineStr">
-        <is>
-          <t>F | 320呎 (1房)
-$548万
-$17,116/呎
-(26年-02月)</t>
-        </is>
-      </c>
-      <c r="H34" s="16" t="inlineStr">
-        <is>
-          <t>G | 250呎 (开放式)
-$451万
-$18,044/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="I34" s="18" t="inlineStr">
-        <is>
-          <t>H | 322呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="J34" s="16" t="inlineStr">
-        <is>
-          <t>J | 414呎 (2房)
-$731万
-$17,657/呎
-(26年-01月)</t>
-        </is>
-      </c>
-      <c r="K34" s="18" t="inlineStr">
-        <is>
-          <t>K | 423呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="35" ht="65" customHeight="1">
-      <c r="A35" s="2" t="inlineStr">
-        <is>
-          <t>6/F</t>
-        </is>
-      </c>
-      <c r="B35" s="18" t="inlineStr">
-        <is>
-          <t>A | 468呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C35" s="16" t="inlineStr">
-        <is>
-          <t>B | 454呎 (2房)
-$919万
-$20,240/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="D35" s="16" t="inlineStr">
-        <is>
-          <t>C | 329呎 (1房)
-$594万
-$18,061/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="E35" s="18" t="inlineStr">
-        <is>
-          <t>D | 311呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F35" s="16" t="inlineStr">
-        <is>
-          <t>E | 320呎 (1房)
-$546万
-$17,075/呎
-(26年-01月)</t>
-        </is>
-      </c>
-      <c r="G35" s="20" t="inlineStr">
-        <is>
-          <t>F | 319呎 (1房)
-$621万
-$19,458/呎
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="H35" s="16" t="inlineStr">
-        <is>
-          <t>G | 250呎 (开放式)
-$450万
-$18,000/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="I35" s="18" t="inlineStr">
-        <is>
-          <t>H | 322呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="J35" s="16" t="inlineStr">
-        <is>
-          <t>J | 414呎 (2房)
-$782万
-$18,877/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="K35" s="18" t="inlineStr">
-        <is>
-          <t>K | 423呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" ht="65" customHeight="1">
-      <c r="A36" s="2" t="inlineStr">
-        <is>
-          <t>5/F</t>
-        </is>
-      </c>
-      <c r="B36" s="18" t="inlineStr">
-        <is>
-          <t>A | 468呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C36" s="18" t="inlineStr">
-        <is>
-          <t>B | 455呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D36" s="18" t="inlineStr">
-        <is>
-          <t>C | 330呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E36" s="18" t="inlineStr">
-        <is>
-          <t>D | 311呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F36" s="18" t="inlineStr">
-        <is>
-          <t>E | 319呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G36" s="18" t="inlineStr">
-        <is>
-          <t>F | 319呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="H36" s="18" t="inlineStr">
-        <is>
-          <t>G | 249呎 (开放式)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="I36" s="18" t="inlineStr">
-        <is>
-          <t>H | 322呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="J36" s="18" t="inlineStr">
-        <is>
-          <t>J | 414呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="K36" s="18" t="inlineStr">
-        <is>
-          <t>K | 423呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="37" ht="65" customHeight="1">
-      <c r="A37" s="2" t="inlineStr">
-        <is>
-          <t>3/F</t>
-        </is>
-      </c>
-      <c r="B37" s="18" t="inlineStr">
-        <is>
-          <t>A | 468呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C37" s="18" t="inlineStr">
-        <is>
-          <t>B | 340呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D37" s="18" t="inlineStr">
-        <is>
-          <t>C | 330呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E37" s="18" t="inlineStr">
-        <is>
-          <t>D | 311呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F37" s="18" t="inlineStr">
-        <is>
-          <t>E | 319呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G37" s="18" t="inlineStr">
-        <is>
-          <t>F | 319呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="H37" s="18" t="inlineStr">
-        <is>
-          <t>G | 249呎 (开放式)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="I37" s="18" t="inlineStr">
-        <is>
-          <t>H | 322呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="J37" s="18" t="inlineStr">
-        <is>
-          <t>J | 414呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="K37" s="18" t="inlineStr">
-        <is>
-          <t>K | 423呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="38" ht="65" customHeight="1">
-      <c r="A38" s="2" t="inlineStr">
-        <is>
-          <t>2/F</t>
-        </is>
-      </c>
-      <c r="B38" s="18" t="inlineStr">
-        <is>
-          <t>A | 431呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C38" s="18" t="inlineStr">
-        <is>
-          <t>B | 302呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D38" s="18" t="inlineStr">
-        <is>
-          <t>C | 292呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E38" s="18" t="inlineStr">
-        <is>
-          <t>D | 311呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F38" s="18" t="inlineStr">
-        <is>
-          <t>E | 319呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G38" s="18" t="inlineStr">
-        <is>
-          <t>F | 319呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="H38" s="18" t="inlineStr">
-        <is>
-          <t>G | 249呎 (开放式)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="I38" s="18" t="inlineStr">
-        <is>
-          <t>H | 322呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="J38" s="18" t="inlineStr">
-        <is>
-          <t>J | 414呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="K38" s="18" t="inlineStr">
-        <is>
-          <t>K | 423呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:K1"/>
-  </mergeCells>
-  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
-  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
-</worksheet>
 </file>
--- a/files/九龙-启德-Double Coast III.xlsx
+++ b/files/九龙-启德-Double Coast III.xlsx
@@ -8,6 +8,8 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="销控汇总明细" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1A座" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1B座" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -19,7 +21,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="$#,##0"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="21">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -41,8 +43,101 @@
       <name val="Microsoft YaHei"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <sz val="13"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00000000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00000000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00004D00"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00004D00"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00002060"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00002060"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00660000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00660000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00000000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="007F7F7F"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="007F7F7F"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00660000"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="007F7F7F"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00002060"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00000000"/>
+      <sz val="8"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="9">
     <fill>
       <patternFill/>
     </fill>
@@ -53,6 +148,42 @@
       <patternFill patternType="solid">
         <fgColor rgb="00F2F2F2"/>
         <bgColor rgb="00F2F2F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFFFF"/>
+        <bgColor rgb="00FFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00A9F5A9"/>
+        <bgColor rgb="00A9F5A9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00A9D0F5"/>
+        <bgColor rgb="00A9D0F5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F5A9A9"/>
+        <bgColor rgb="00F5A9A9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFC000"/>
+        <bgColor rgb="00FFC000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E8E8E8"/>
+        <bgColor rgb="00E8E8E8"/>
       </patternFill>
     </fill>
   </fills>
@@ -82,7 +213,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -98,6 +229,63 @@
     </xf>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -474,7 +662,7 @@
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
   </cols>
@@ -25891,4 +26079,4963 @@
   <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:G37"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>1A座 销控网格图</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>总套数</t>
+        </is>
+      </c>
+      <c r="B2" s="8" t="inlineStr">
+        <is>
+          <t>在售 (Sale)</t>
+        </is>
+      </c>
+      <c r="C2" s="9" t="inlineStr">
+        <is>
+          <t>已定价未售</t>
+        </is>
+      </c>
+      <c r="D2" s="10" t="inlineStr">
+        <is>
+          <t>已售 (Sold)</t>
+        </is>
+      </c>
+      <c r="E2" s="11" t="inlineStr">
+        <is>
+          <t>暂停销售</t>
+        </is>
+      </c>
+      <c r="F2" s="12" t="inlineStr">
+        <is>
+          <t>待售 (Pending)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="13" t="inlineStr">
+        <is>
+          <t>196</t>
+        </is>
+      </c>
+      <c r="B3" s="14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="E3" s="17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" s="18" t="inlineStr">
+        <is>
+          <t>119</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="19" t="inlineStr">
+        <is>
+          <t>楼层</t>
+        </is>
+      </c>
+      <c r="B4" s="19" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C4" s="19" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D4" s="19" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E4" s="19" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="F4" s="19" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="G4" s="19" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="58" customHeight="1">
+      <c r="A5" s="19" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="B5" s="20" t="inlineStr">
+        <is>
+          <t>A | 1378呎 (4+房)
+$4668万
+$33,877/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="C5" s="21" t="inlineStr"/>
+      <c r="D5" s="22" t="inlineStr">
+        <is>
+          <t>C | 493呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E5" s="22" t="inlineStr">
+        <is>
+          <t>D | 434呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F5" s="22" t="inlineStr">
+        <is>
+          <t>E | 429呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G5" s="22" t="inlineStr">
+        <is>
+          <t>F | 428呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="58" customHeight="1">
+      <c r="A6" s="19" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="B6" s="22" t="inlineStr">
+        <is>
+          <t>A | 641呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C6" s="22" t="inlineStr">
+        <is>
+          <t>B | 696呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D6" s="22" t="inlineStr">
+        <is>
+          <t>C | 518呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E6" s="22" t="inlineStr">
+        <is>
+          <t>D | 436呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F6" s="22" t="inlineStr">
+        <is>
+          <t>E | 429呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G6" s="22" t="inlineStr">
+        <is>
+          <t>F | 428呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="B7" s="22" t="inlineStr">
+        <is>
+          <t>A | 641呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C7" s="22" t="inlineStr">
+        <is>
+          <t>B | 696呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D7" s="22" t="inlineStr">
+        <is>
+          <t>C | 518呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E7" s="22" t="inlineStr">
+        <is>
+          <t>D | 436呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F7" s="22" t="inlineStr">
+        <is>
+          <t>E | 429呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G7" s="22" t="inlineStr">
+        <is>
+          <t>F | 430呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="58" customHeight="1">
+      <c r="A8" s="19" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="B8" s="22" t="inlineStr">
+        <is>
+          <t>A | 641呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C8" s="22" t="inlineStr">
+        <is>
+          <t>B | 696呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D8" s="22" t="inlineStr">
+        <is>
+          <t>C | 518呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E8" s="22" t="inlineStr">
+        <is>
+          <t>D | 436呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F8" s="22" t="inlineStr">
+        <is>
+          <t>E | 429呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G8" s="22" t="inlineStr">
+        <is>
+          <t>F | 430呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="58" customHeight="1">
+      <c r="A9" s="19" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="B9" s="22" t="inlineStr">
+        <is>
+          <t>A | 641呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C9" s="22" t="inlineStr">
+        <is>
+          <t>B | 696呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D9" s="22" t="inlineStr">
+        <is>
+          <t>C | 518呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E9" s="22" t="inlineStr">
+        <is>
+          <t>D | 436呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F9" s="22" t="inlineStr">
+        <is>
+          <t>E | 429呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G9" s="22" t="inlineStr">
+        <is>
+          <t>F | 430呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="58" customHeight="1">
+      <c r="A10" s="19" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="B10" s="22" t="inlineStr">
+        <is>
+          <t>A | 641呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C10" s="23" t="inlineStr">
+        <is>
+          <t>B | 696呎 (3房)
+$1806万
+$25,948/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="D10" s="22" t="inlineStr">
+        <is>
+          <t>C | 518呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E10" s="22" t="inlineStr">
+        <is>
+          <t>D | 436呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F10" s="22" t="inlineStr">
+        <is>
+          <t>E | 429呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G10" s="22" t="inlineStr">
+        <is>
+          <t>F | 430呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="58" customHeight="1">
+      <c r="A11" s="19" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="B11" s="22" t="inlineStr">
+        <is>
+          <t>A | 641呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C11" s="23" t="inlineStr">
+        <is>
+          <t>B | 696呎 (3房)
+$1802万
+$25,884/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="D11" s="22" t="inlineStr">
+        <is>
+          <t>C | 518呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E11" s="22" t="inlineStr">
+        <is>
+          <t>D | 436呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F11" s="22" t="inlineStr">
+        <is>
+          <t>E | 429呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G11" s="22" t="inlineStr">
+        <is>
+          <t>F | 430呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="58" customHeight="1">
+      <c r="A12" s="19" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="B12" s="22" t="inlineStr">
+        <is>
+          <t>A | 641呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C12" s="22" t="inlineStr">
+        <is>
+          <t>B | 696呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D12" s="22" t="inlineStr">
+        <is>
+          <t>C | 518呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E12" s="22" t="inlineStr">
+        <is>
+          <t>D | 436呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F12" s="22" t="inlineStr">
+        <is>
+          <t>E | 429呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G12" s="20" t="inlineStr">
+        <is>
+          <t>F | 431呎 (2房)
+$791万
+$18,346/呎
+(26年-05月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="58" customHeight="1">
+      <c r="A13" s="19" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="B13" s="22" t="inlineStr">
+        <is>
+          <t>A | 641呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C13" s="20" t="inlineStr">
+        <is>
+          <t>B | 695呎 (3房)
+$1631万
+$23,471/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="D13" s="22" t="inlineStr">
+        <is>
+          <t>C | 518呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E13" s="22" t="inlineStr">
+        <is>
+          <t>D | 436呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F13" s="22" t="inlineStr">
+        <is>
+          <t>E | 429呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G13" s="20" t="inlineStr">
+        <is>
+          <t>F | 431呎 (2房)
+$789万
+$18,302/呎
+(26年-05月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="58" customHeight="1">
+      <c r="A14" s="19" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="B14" s="22" t="inlineStr">
+        <is>
+          <t>A | 641呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C14" s="23" t="inlineStr">
+        <is>
+          <t>B | 696呎 (3房)
+$1788万
+$25,690/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="D14" s="22" t="inlineStr">
+        <is>
+          <t>C | 518呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E14" s="22" t="inlineStr">
+        <is>
+          <t>D | 436呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F14" s="20" t="inlineStr">
+        <is>
+          <t>E | 429呎 (2房)
+$800万
+$18,653/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="G14" s="20" t="inlineStr">
+        <is>
+          <t>F | 431呎 (2房)
+$796万
+$18,459/呎
+(26年-05月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="58" customHeight="1">
+      <c r="A15" s="19" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="B15" s="22" t="inlineStr">
+        <is>
+          <t>A | 641呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C15" s="22" t="inlineStr">
+        <is>
+          <t>B | 696呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D15" s="22" t="inlineStr">
+        <is>
+          <t>C | 518呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E15" s="22" t="inlineStr">
+        <is>
+          <t>D | 436呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F15" s="22" t="inlineStr">
+        <is>
+          <t>E | 429呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G15" s="22" t="inlineStr">
+        <is>
+          <t>F | 430呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="58" customHeight="1">
+      <c r="A16" s="19" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="B16" s="22" t="inlineStr">
+        <is>
+          <t>A | 641呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C16" s="23" t="inlineStr">
+        <is>
+          <t>B | 696呎 (3房)
+$1775万
+$25,499/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="D16" s="22" t="inlineStr">
+        <is>
+          <t>C | 518呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E16" s="22" t="inlineStr">
+        <is>
+          <t>D | 436呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F16" s="20" t="inlineStr">
+        <is>
+          <t>E | 429呎 (2房)
+$794万
+$18,513/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="G16" s="20" t="inlineStr">
+        <is>
+          <t>F | 431呎 (2房)
+$790万
+$18,323/呎
+(26年-05月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="58" customHeight="1">
+      <c r="A17" s="19" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="B17" s="22" t="inlineStr">
+        <is>
+          <t>A | 641呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C17" s="20" t="inlineStr">
+        <is>
+          <t>B | 695呎 (3房)
+$1558万
+$22,416/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="D17" s="22" t="inlineStr">
+        <is>
+          <t>C | 518呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E17" s="22" t="inlineStr">
+        <is>
+          <t>D | 436呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F17" s="20" t="inlineStr">
+        <is>
+          <t>E | 429呎 (2房)
+$792万
+$18,466/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="G17" s="20" t="inlineStr">
+        <is>
+          <t>F | 431呎 (2房)
+$788万
+$18,276/呎
+(26年-05月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="58" customHeight="1">
+      <c r="A18" s="19" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="B18" s="22" t="inlineStr">
+        <is>
+          <t>A | 641呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C18" s="22" t="inlineStr">
+        <is>
+          <t>B | 696呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D18" s="22" t="inlineStr">
+        <is>
+          <t>C | 518呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E18" s="22" t="inlineStr">
+        <is>
+          <t>D | 436呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F18" s="20" t="inlineStr">
+        <is>
+          <t>E | 429呎 (2房)
+$790万
+$18,420/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="G18" s="20" t="inlineStr">
+        <is>
+          <t>F | 431呎 (2房)
+$786万
+$18,230/呎
+(26年-05月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="58" customHeight="1">
+      <c r="A19" s="19" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="B19" s="22" t="inlineStr">
+        <is>
+          <t>A | 641呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C19" s="20" t="inlineStr">
+        <is>
+          <t>B | 695呎 (3房)
+$1550万
+$22,304/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="D19" s="22" t="inlineStr">
+        <is>
+          <t>C | 518呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E19" s="22" t="inlineStr">
+        <is>
+          <t>D | 436呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F19" s="20" t="inlineStr">
+        <is>
+          <t>E | 429呎 (2房)
+$788万
+$18,373/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="G19" s="20" t="inlineStr">
+        <is>
+          <t>F | 431呎 (2房)
+$792万
+$18,387/呎
+(26年-05月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="58" customHeight="1">
+      <c r="A20" s="19" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="B20" s="22" t="inlineStr">
+        <is>
+          <t>A | 641呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C20" s="20" t="inlineStr">
+        <is>
+          <t>B | 695呎 (3房)
+$1546万
+$22,249/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="D20" s="22" t="inlineStr">
+        <is>
+          <t>C | 518呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E20" s="22" t="inlineStr">
+        <is>
+          <t>D | 436呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F20" s="20" t="inlineStr">
+        <is>
+          <t>E | 429呎 (2房)
+$786万
+$18,329/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="G20" s="20" t="inlineStr">
+        <is>
+          <t>F | 431呎 (2房)
+$782万
+$18,139/呎
+(26年-05月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="58" customHeight="1">
+      <c r="A21" s="19" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="B21" s="20" t="inlineStr">
+        <is>
+          <t>A | 640呎 (3房)
+$1444万
+$22,564/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="C21" s="20" t="inlineStr">
+        <is>
+          <t>B | 695呎 (3房)
+$1542万
+$22,193/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="D21" s="22" t="inlineStr">
+        <is>
+          <t>C | 518呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E21" s="22" t="inlineStr">
+        <is>
+          <t>D | 436呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F21" s="20" t="inlineStr">
+        <is>
+          <t>E | 429呎 (2房)
+$784万
+$18,282/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="G21" s="20" t="inlineStr">
+        <is>
+          <t>F | 431呎 (2房)
+$780万
+$18,095/呎
+(26年-05月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="58" customHeight="1">
+      <c r="A22" s="19" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B22" s="20" t="inlineStr">
+        <is>
+          <t>A | 640呎 (3房)
+$1432万
+$22,383/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="C22" s="20" t="inlineStr">
+        <is>
+          <t>B | 695呎 (3房)
+$1556万
+$22,388/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="D22" s="22" t="inlineStr">
+        <is>
+          <t>C | 518呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E22" s="22" t="inlineStr">
+        <is>
+          <t>D | 436呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F22" s="20" t="inlineStr">
+        <is>
+          <t>E | 429呎 (2房)
+$782万
+$18,238/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="G22" s="20" t="inlineStr">
+        <is>
+          <t>F | 431呎 (2房)
+$769万
+$17,849/呎
+(26年-05月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="58" customHeight="1">
+      <c r="A23" s="19" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B23" s="20" t="inlineStr">
+        <is>
+          <t>A | 640呎 (3房)
+$1429万
+$22,327/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="C23" s="20" t="inlineStr">
+        <is>
+          <t>B | 695呎 (3房)
+$1604万
+$23,085/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="D23" s="22" t="inlineStr">
+        <is>
+          <t>C | 518呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E23" s="22" t="inlineStr">
+        <is>
+          <t>D | 436呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F23" s="20" t="inlineStr">
+        <is>
+          <t>E | 429呎 (2房)
+$780万
+$18,191/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="G23" s="20" t="inlineStr">
+        <is>
+          <t>F | 431呎 (2房)
+$776万
+$18,005/呎
+(26年-05月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="58" customHeight="1">
+      <c r="A24" s="19" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B24" s="20" t="inlineStr">
+        <is>
+          <t>A | 640呎 (3房)
+$1433万
+$22,397/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="C24" s="20" t="inlineStr">
+        <is>
+          <t>B | 695呎 (3房)
+$1531万
+$22,027/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="D24" s="22" t="inlineStr">
+        <is>
+          <t>C | 518呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E24" s="22" t="inlineStr">
+        <is>
+          <t>D | 436呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F24" s="20" t="inlineStr">
+        <is>
+          <t>E | 429呎 (2房)
+$787万
+$18,350/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="G24" s="20" t="inlineStr">
+        <is>
+          <t>F | 431呎 (2房)
+$729万
+$16,914/呎
+(26年-01月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="58" customHeight="1">
+      <c r="A25" s="19" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B25" s="20" t="inlineStr">
+        <is>
+          <t>A | 640呎 (3房)
+$1426万
+$22,284/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="C25" s="20" t="inlineStr">
+        <is>
+          <t>B | 695呎 (3房)
+$1523万
+$21,917/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="D25" s="22" t="inlineStr">
+        <is>
+          <t>C | 518呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E25" s="22" t="inlineStr">
+        <is>
+          <t>D | 436呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F25" s="20" t="inlineStr">
+        <is>
+          <t>E | 429呎 (2房)
+$783万
+$18,259/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="G25" s="20" t="inlineStr">
+        <is>
+          <t>F | 431呎 (2房)
+$725万
+$16,828/呎
+(26年-01月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="58" customHeight="1">
+      <c r="A26" s="19" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B26" s="20" t="inlineStr">
+        <is>
+          <t>A | 640呎 (3房)
+$1415万
+$22,105/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="C26" s="20" t="inlineStr">
+        <is>
+          <t>B | 695呎 (3房)
+$1520万
+$21,863/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="D26" s="22" t="inlineStr">
+        <is>
+          <t>C | 518呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E26" s="22" t="inlineStr">
+        <is>
+          <t>D | 436呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F26" s="20" t="inlineStr">
+        <is>
+          <t>E | 429呎 (2房)
+$773万
+$18,012/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="G26" s="20" t="inlineStr">
+        <is>
+          <t>F | 431呎 (2房)
+$724万
+$16,789/呎
+(26年-01月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="58" customHeight="1">
+      <c r="A27" s="19" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B27" s="20" t="inlineStr">
+        <is>
+          <t>A | 640呎 (3房)
+$1357万
+$21,202/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="C27" s="20" t="inlineStr">
+        <is>
+          <t>B | 695呎 (3房)
+$1516万
+$21,809/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="D27" s="22" t="inlineStr">
+        <is>
+          <t>C | 518呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E27" s="22" t="inlineStr">
+        <is>
+          <t>D | 436呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F27" s="20" t="inlineStr">
+        <is>
+          <t>E | 429呎 (2房)
+$771万
+$17,967/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="G27" s="20" t="inlineStr">
+        <is>
+          <t>F | 431呎 (2房)
+$722万
+$16,745/呎
+(26年-01月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="58" customHeight="1">
+      <c r="A28" s="19" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B28" s="20" t="inlineStr">
+        <is>
+          <t>A | 640呎 (3房)
+$1416万
+$22,119/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="C28" s="20" t="inlineStr">
+        <is>
+          <t>B | 695呎 (3房)
+$1512万
+$21,754/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="D28" s="22" t="inlineStr">
+        <is>
+          <t>C | 518呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E28" s="22" t="inlineStr">
+        <is>
+          <t>D | 436呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F28" s="20" t="inlineStr">
+        <is>
+          <t>E | 429呎 (2房)
+$740万
+$17,261/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="G28" s="20" t="inlineStr">
+        <is>
+          <t>F | 431呎 (2房)
+$720万
+$16,705/呎
+(26年-01月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="58" customHeight="1">
+      <c r="A29" s="19" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B29" s="20" t="inlineStr">
+        <is>
+          <t>A | 640呎 (3房)
+$1404万
+$21,941/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="C29" s="20" t="inlineStr">
+        <is>
+          <t>B | 695呎 (3房)
+$1508万
+$21,699/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="D29" s="22" t="inlineStr">
+        <is>
+          <t>C | 518呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E29" s="22" t="inlineStr">
+        <is>
+          <t>D | 436呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F29" s="20" t="inlineStr">
+        <is>
+          <t>E | 429呎 (2房)
+$730万
+$17,026/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="G29" s="20" t="inlineStr">
+        <is>
+          <t>F | 431呎 (2房)
+$718万
+$16,661/呎
+(26年-01月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="58" customHeight="1">
+      <c r="A30" s="19" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B30" s="20" t="inlineStr">
+        <is>
+          <t>A | 640呎 (3房)
+$1401万
+$21,884/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="C30" s="20" t="inlineStr">
+        <is>
+          <t>B | 695呎 (3房)
+$1522万
+$21,892/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="D30" s="22" t="inlineStr">
+        <is>
+          <t>C | 518呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E30" s="22" t="inlineStr">
+        <is>
+          <t>D | 436呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F30" s="20" t="inlineStr">
+        <is>
+          <t>E | 429呎 (2房)
+$729万
+$16,984/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="G30" s="20" t="inlineStr">
+        <is>
+          <t>F | 431呎 (2房)
+$716万
+$16,622/呎
+(26年-01月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="58" customHeight="1">
+      <c r="A31" s="19" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B31" s="20" t="inlineStr">
+        <is>
+          <t>A | 640呎 (3房)
+$1397万
+$21,831/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="C31" s="20" t="inlineStr">
+        <is>
+          <t>B | 695呎 (3房)
+$1501万
+$21,591/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="D31" s="22" t="inlineStr">
+        <is>
+          <t>C | 518呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E31" s="22" t="inlineStr">
+        <is>
+          <t>D | 436呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F31" s="20" t="inlineStr">
+        <is>
+          <t>E | 429呎 (2房)
+$727万
+$16,942/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="G31" s="20" t="inlineStr">
+        <is>
+          <t>F | 431呎 (2房)
+$750万
+$17,408/呎
+(26年-05月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="58" customHeight="1">
+      <c r="A32" s="19" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B32" s="20" t="inlineStr">
+        <is>
+          <t>A | 640呎 (3房)
+$1340万
+$20,939/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="C32" s="20" t="inlineStr">
+        <is>
+          <t>B | 695呎 (3房)
+$1497万
+$21,538/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="D32" s="22" t="inlineStr">
+        <is>
+          <t>C | 518呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E32" s="22" t="inlineStr">
+        <is>
+          <t>D | 436呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F32" s="20" t="inlineStr">
+        <is>
+          <t>E | 429呎 (2房)
+$725万
+$16,897/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="G32" s="20" t="inlineStr">
+        <is>
+          <t>F | 431呎 (2房)
+$748万
+$17,367/呎
+(26年-05月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="58" customHeight="1">
+      <c r="A33" s="19" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B33" s="22" t="inlineStr">
+        <is>
+          <t>A | 641呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C33" s="20" t="inlineStr">
+        <is>
+          <t>B | 695呎 (3房)
+$1557万
+$22,404/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="D33" s="22" t="inlineStr">
+        <is>
+          <t>C | 518呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E33" s="22" t="inlineStr">
+        <is>
+          <t>D | 436呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F33" s="20" t="inlineStr">
+        <is>
+          <t>E | 429呎 (2房)
+$766万
+$17,853/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="G33" s="20" t="inlineStr">
+        <is>
+          <t>F | 431呎 (2房)
+$753万
+$17,473/呎
+(26年-05月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="58" customHeight="1">
+      <c r="A34" s="19" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B34" s="22" t="inlineStr">
+        <is>
+          <t>A | 641呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C34" s="23" t="inlineStr">
+        <is>
+          <t>B | 696呎 (3房)
+$1688万
+$24,257/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="D34" s="22" t="inlineStr">
+        <is>
+          <t>C | 518呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E34" s="22" t="inlineStr">
+        <is>
+          <t>D | 436呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F34" s="20" t="inlineStr">
+        <is>
+          <t>E | 429呎 (2房)
+$756万
+$17,611/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="G34" s="20" t="inlineStr">
+        <is>
+          <t>F | 431呎 (2房)
+$743万
+$17,234/呎
+(26年-05月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="58" customHeight="1">
+      <c r="A35" s="19" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B35" s="22" t="inlineStr">
+        <is>
+          <t>A | 641呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C35" s="22" t="inlineStr">
+        <is>
+          <t>B | 696呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D35" s="22" t="inlineStr">
+        <is>
+          <t>C | 518呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E35" s="22" t="inlineStr">
+        <is>
+          <t>D | 436呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F35" s="22" t="inlineStr">
+        <is>
+          <t>E | 429呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G35" s="22" t="inlineStr">
+        <is>
+          <t>F | 430呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="58" customHeight="1">
+      <c r="A36" s="19" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B36" s="22" t="inlineStr">
+        <is>
+          <t>A | 641呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C36" s="22" t="inlineStr">
+        <is>
+          <t>B | 696呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D36" s="22" t="inlineStr">
+        <is>
+          <t>C | 518呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E36" s="22" t="inlineStr">
+        <is>
+          <t>D | 436呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F36" s="22" t="inlineStr">
+        <is>
+          <t>E | 429呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G36" s="22" t="inlineStr">
+        <is>
+          <t>F | 430呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="58" customHeight="1">
+      <c r="A37" s="19" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B37" s="22" t="inlineStr">
+        <is>
+          <t>A | 641呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C37" s="22" t="inlineStr">
+        <is>
+          <t>B | 696呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D37" s="22" t="inlineStr">
+        <is>
+          <t>C | 518呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E37" s="22" t="inlineStr">
+        <is>
+          <t>D | 436呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F37" s="22" t="inlineStr">
+        <is>
+          <t>E | 434呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G37" s="21" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
+  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:K37"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>1B座 销控网格图</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>总套数</t>
+        </is>
+      </c>
+      <c r="B2" s="8" t="inlineStr">
+        <is>
+          <t>在售 (Sale)</t>
+        </is>
+      </c>
+      <c r="C2" s="9" t="inlineStr">
+        <is>
+          <t>已定价未售</t>
+        </is>
+      </c>
+      <c r="D2" s="10" t="inlineStr">
+        <is>
+          <t>已售 (Sold)</t>
+        </is>
+      </c>
+      <c r="E2" s="11" t="inlineStr">
+        <is>
+          <t>暂停销售</t>
+        </is>
+      </c>
+      <c r="F2" s="12" t="inlineStr">
+        <is>
+          <t>待售 (Pending)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="13" t="inlineStr">
+        <is>
+          <t>329</t>
+        </is>
+      </c>
+      <c r="B3" s="14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t>147</t>
+        </is>
+      </c>
+      <c r="E3" s="17" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F3" s="18" t="inlineStr">
+        <is>
+          <t>180</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="19" t="inlineStr">
+        <is>
+          <t>楼层</t>
+        </is>
+      </c>
+      <c r="B4" s="19" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C4" s="19" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D4" s="19" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E4" s="19" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="F4" s="19" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="G4" s="19" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="H4" s="19" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="I4" s="19" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="J4" s="19" t="inlineStr">
+        <is>
+          <t>J</t>
+        </is>
+      </c>
+      <c r="K4" s="19" t="inlineStr">
+        <is>
+          <t>K</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="58" customHeight="1">
+      <c r="A5" s="19" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="B5" s="21" t="inlineStr"/>
+      <c r="C5" s="22" t="inlineStr">
+        <is>
+          <t>B | 455呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D5" s="22" t="inlineStr">
+        <is>
+          <t>C | 330呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E5" s="22" t="inlineStr">
+        <is>
+          <t>D | 311呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F5" s="22" t="inlineStr">
+        <is>
+          <t>E | 319呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G5" s="22" t="inlineStr">
+        <is>
+          <t>F | 319呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H5" s="22" t="inlineStr">
+        <is>
+          <t>G | 249呎 (开放式)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="I5" s="22" t="inlineStr">
+        <is>
+          <t>H | 322呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="J5" s="22" t="inlineStr">
+        <is>
+          <t>J | 414呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="K5" s="22" t="inlineStr">
+        <is>
+          <t>K | 423呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="58" customHeight="1">
+      <c r="A6" s="19" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="B6" s="22" t="inlineStr">
+        <is>
+          <t>A | 468呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C6" s="22" t="inlineStr">
+        <is>
+          <t>B | 455呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D6" s="22" t="inlineStr">
+        <is>
+          <t>C | 330呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E6" s="22" t="inlineStr">
+        <is>
+          <t>D | 311呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F6" s="22" t="inlineStr">
+        <is>
+          <t>E | 319呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G6" s="22" t="inlineStr">
+        <is>
+          <t>F | 319呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H6" s="22" t="inlineStr">
+        <is>
+          <t>G | 249呎 (开放式)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="I6" s="22" t="inlineStr">
+        <is>
+          <t>H | 322呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="J6" s="22" t="inlineStr">
+        <is>
+          <t>J | 414呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="K6" s="22" t="inlineStr">
+        <is>
+          <t>K | 423呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="B7" s="22" t="inlineStr">
+        <is>
+          <t>A | 468呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C7" s="22" t="inlineStr">
+        <is>
+          <t>B | 455呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D7" s="22" t="inlineStr">
+        <is>
+          <t>C | 330呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E7" s="22" t="inlineStr">
+        <is>
+          <t>D | 311呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F7" s="22" t="inlineStr">
+        <is>
+          <t>E | 319呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G7" s="22" t="inlineStr">
+        <is>
+          <t>F | 319呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H7" s="22" t="inlineStr">
+        <is>
+          <t>G | 249呎 (开放式)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="I7" s="22" t="inlineStr">
+        <is>
+          <t>H | 322呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="J7" s="22" t="inlineStr">
+        <is>
+          <t>J | 414呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="K7" s="22" t="inlineStr">
+        <is>
+          <t>K | 423呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="58" customHeight="1">
+      <c r="A8" s="19" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="B8" s="22" t="inlineStr">
+        <is>
+          <t>A | 468呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C8" s="22" t="inlineStr">
+        <is>
+          <t>B | 455呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D8" s="20" t="inlineStr">
+        <is>
+          <t>C | 329呎 (1房)
+$639万
+$19,416/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="E8" s="22" t="inlineStr">
+        <is>
+          <t>D | 311呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F8" s="20" t="inlineStr">
+        <is>
+          <t>E | 320呎 (1房)
+$622万
+$19,431/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="G8" s="20" t="inlineStr">
+        <is>
+          <t>F | 320呎 (1房)
+$620万
+$19,369/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="H8" s="20" t="inlineStr">
+        <is>
+          <t>G | 250呎 (开放式)
+$478万
+$19,136/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="I8" s="22" t="inlineStr">
+        <is>
+          <t>H | 322呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="J8" s="22" t="inlineStr">
+        <is>
+          <t>J | 414呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="K8" s="22" t="inlineStr">
+        <is>
+          <t>K | 423呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="58" customHeight="1">
+      <c r="A9" s="19" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="B9" s="22" t="inlineStr">
+        <is>
+          <t>A | 468呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C9" s="22" t="inlineStr">
+        <is>
+          <t>B | 455呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D9" s="20" t="inlineStr">
+        <is>
+          <t>C | 329呎 (1房)
+$637万
+$19,368/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="E9" s="22" t="inlineStr">
+        <is>
+          <t>D | 311呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F9" s="20" t="inlineStr">
+        <is>
+          <t>E | 320呎 (1房)
+$620万
+$19,384/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="G9" s="20" t="inlineStr">
+        <is>
+          <t>F | 320呎 (1房)
+$618万
+$19,319/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="H9" s="20" t="inlineStr">
+        <is>
+          <t>G | 250呎 (开放式)
+$477万
+$19,092/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="I9" s="22" t="inlineStr">
+        <is>
+          <t>H | 322呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="J9" s="20" t="inlineStr">
+        <is>
+          <t>J | 414呎 (2房)
+$829万
+$20,019/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="K9" s="22" t="inlineStr">
+        <is>
+          <t>K | 423呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="58" customHeight="1">
+      <c r="A10" s="19" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="B10" s="22" t="inlineStr">
+        <is>
+          <t>A | 468呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C10" s="22" t="inlineStr">
+        <is>
+          <t>B | 455呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D10" s="20" t="inlineStr">
+        <is>
+          <t>C | 329呎 (1房)
+$643万
+$19,535/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="E10" s="22" t="inlineStr">
+        <is>
+          <t>D | 311呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F10" s="20" t="inlineStr">
+        <is>
+          <t>E | 320呎 (1房)
+$619万
+$19,338/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="G10" s="20" t="inlineStr">
+        <is>
+          <t>F | 320呎 (1房)
+$622万
+$19,431/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="H10" s="20" t="inlineStr">
+        <is>
+          <t>G | 250呎 (开放式)
+$482万
+$19,260/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="I10" s="22" t="inlineStr">
+        <is>
+          <t>H | 322呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="J10" s="20" t="inlineStr">
+        <is>
+          <t>J | 414呎 (2房)
+$836万
+$20,196/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="K10" s="22" t="inlineStr">
+        <is>
+          <t>K | 423呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="58" customHeight="1">
+      <c r="A11" s="19" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="B11" s="22" t="inlineStr">
+        <is>
+          <t>A | 468呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C11" s="22" t="inlineStr">
+        <is>
+          <t>B | 455呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D11" s="20" t="inlineStr">
+        <is>
+          <t>C | 329呎 (1房)
+$629万
+$19,109/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="E11" s="22" t="inlineStr">
+        <is>
+          <t>D | 311呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F11" s="20" t="inlineStr">
+        <is>
+          <t>E | 320呎 (1房)
+$617万
+$19,291/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="G11" s="20" t="inlineStr">
+        <is>
+          <t>F | 320呎 (1房)
+$622万
+$19,438/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="H11" s="20" t="inlineStr">
+        <is>
+          <t>G | 250呎 (开放式)
+$475万
+$18,996/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="I11" s="22" t="inlineStr">
+        <is>
+          <t>H | 322呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="J11" s="20" t="inlineStr">
+        <is>
+          <t>J | 414呎 (2房)
+$825万
+$19,920/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="K11" s="22" t="inlineStr">
+        <is>
+          <t>K | 423呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="58" customHeight="1">
+      <c r="A12" s="19" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="B12" s="22" t="inlineStr">
+        <is>
+          <t>A | 468呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C12" s="22" t="inlineStr">
+        <is>
+          <t>B | 455呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D12" s="20" t="inlineStr">
+        <is>
+          <t>C | 329呎 (1房)
+$627万
+$19,061/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="E12" s="22" t="inlineStr">
+        <is>
+          <t>D | 311呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F12" s="20" t="inlineStr">
+        <is>
+          <t>E | 320呎 (1房)
+$616万
+$19,241/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="G12" s="20" t="inlineStr">
+        <is>
+          <t>F | 320呎 (1房)
+$614万
+$19,175/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="H12" s="20" t="inlineStr">
+        <is>
+          <t>G | 250呎 (开放式)
+$474万
+$18,948/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="I12" s="22" t="inlineStr">
+        <is>
+          <t>H | 322呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="J12" s="20" t="inlineStr">
+        <is>
+          <t>J | 414呎 (2房)
+$823万
+$19,872/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="K12" s="22" t="inlineStr">
+        <is>
+          <t>K | 423呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="58" customHeight="1">
+      <c r="A13" s="19" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="B13" s="22" t="inlineStr">
+        <is>
+          <t>A | 468呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C13" s="22" t="inlineStr">
+        <is>
+          <t>B | 455呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D13" s="20" t="inlineStr">
+        <is>
+          <t>C | 329呎 (1房)
+$626万
+$19,015/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="E13" s="22" t="inlineStr">
+        <is>
+          <t>D | 311呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F13" s="20" t="inlineStr">
+        <is>
+          <t>E | 320呎 (1房)
+$613万
+$19,156/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="G13" s="20" t="inlineStr">
+        <is>
+          <t>F | 320呎 (1房)
+$583万
+$18,219/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="H13" s="20" t="inlineStr">
+        <is>
+          <t>G | 250呎 (开放式)
+$473万
+$18,904/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="I13" s="22" t="inlineStr">
+        <is>
+          <t>H | 322呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="J13" s="20" t="inlineStr">
+        <is>
+          <t>J | 414呎 (2房)
+$820万
+$19,819/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="K13" s="22" t="inlineStr">
+        <is>
+          <t>K | 423呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="58" customHeight="1">
+      <c r="A14" s="19" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="B14" s="22" t="inlineStr">
+        <is>
+          <t>A | 468呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C14" s="20" t="inlineStr">
+        <is>
+          <t>B | 454呎 (2房)
+$962万
+$21,198/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="D14" s="20" t="inlineStr">
+        <is>
+          <t>C | 329呎 (1房)
+$624万
+$18,967/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="E14" s="22" t="inlineStr">
+        <is>
+          <t>D | 311呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F14" s="20" t="inlineStr">
+        <is>
+          <t>E | 320呎 (1房)
+$611万
+$19,106/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="G14" s="20" t="inlineStr">
+        <is>
+          <t>F | 320呎 (1房)
+$582万
+$18,172/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="H14" s="20" t="inlineStr">
+        <is>
+          <t>G | 250呎 (开放式)
+$471万
+$18,852/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="I14" s="22" t="inlineStr">
+        <is>
+          <t>H | 322呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="J14" s="20" t="inlineStr">
+        <is>
+          <t>J | 414呎 (2房)
+$818万
+$19,771/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="K14" s="22" t="inlineStr">
+        <is>
+          <t>K | 423呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="58" customHeight="1">
+      <c r="A15" s="19" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="B15" s="22" t="inlineStr">
+        <is>
+          <t>A | 468呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C15" s="22" t="inlineStr">
+        <is>
+          <t>B | 455呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D15" s="22" t="inlineStr">
+        <is>
+          <t>C | 330呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E15" s="22" t="inlineStr">
+        <is>
+          <t>D | 311呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F15" s="22" t="inlineStr">
+        <is>
+          <t>E | 319呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G15" s="22" t="inlineStr">
+        <is>
+          <t>F | 319呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H15" s="22" t="inlineStr">
+        <is>
+          <t>G | 249呎 (开放式)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="I15" s="22" t="inlineStr">
+        <is>
+          <t>H | 322呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="J15" s="22" t="inlineStr">
+        <is>
+          <t>J | 414呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="K15" s="22" t="inlineStr">
+        <is>
+          <t>K | 423呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="58" customHeight="1">
+      <c r="A16" s="19" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="B16" s="22" t="inlineStr">
+        <is>
+          <t>A | 468呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C16" s="20" t="inlineStr">
+        <is>
+          <t>B | 454呎 (2房)
+$955万
+$21,040/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="D16" s="20" t="inlineStr">
+        <is>
+          <t>C | 329呎 (1房)
+$619万
+$18,827/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="E16" s="22" t="inlineStr">
+        <is>
+          <t>D | 311呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F16" s="20" t="inlineStr">
+        <is>
+          <t>E | 320呎 (1房)
+$607万
+$18,966/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="G16" s="20" t="inlineStr">
+        <is>
+          <t>F | 320呎 (1房)
+$577万
+$18,038/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="H16" s="20" t="inlineStr">
+        <is>
+          <t>G | 250呎 (开放式)
+$468万
+$18,712/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="I16" s="22" t="inlineStr">
+        <is>
+          <t>H | 322呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="J16" s="20" t="inlineStr">
+        <is>
+          <t>J | 414呎 (2房)
+$812万
+$19,623/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="K16" s="22" t="inlineStr">
+        <is>
+          <t>K | 423呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="58" customHeight="1">
+      <c r="A17" s="19" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="B17" s="22" t="inlineStr">
+        <is>
+          <t>A | 468呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C17" s="20" t="inlineStr">
+        <is>
+          <t>B | 454呎 (2房)
+$953万
+$20,987/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="D17" s="20" t="inlineStr">
+        <is>
+          <t>C | 329呎 (1房)
+$618万
+$18,781/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="E17" s="22" t="inlineStr">
+        <is>
+          <t>D | 311呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F17" s="20" t="inlineStr">
+        <is>
+          <t>E | 320呎 (1房)
+$579万
+$18,106/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="G17" s="20" t="inlineStr">
+        <is>
+          <t>F | 320呎 (1房)
+$576万
+$17,991/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="H17" s="20" t="inlineStr">
+        <is>
+          <t>G | 250呎 (开放式)
+$467万
+$18,668/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="I17" s="22" t="inlineStr">
+        <is>
+          <t>H | 322呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="J17" s="20" t="inlineStr">
+        <is>
+          <t>J | 414呎 (2房)
+$810万
+$19,575/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="K17" s="22" t="inlineStr">
+        <is>
+          <t>K | 423呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="58" customHeight="1">
+      <c r="A18" s="19" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="B18" s="22" t="inlineStr">
+        <is>
+          <t>A | 468呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C18" s="20" t="inlineStr">
+        <is>
+          <t>B | 454呎 (2房)
+$961万
+$21,172/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="D18" s="20" t="inlineStr">
+        <is>
+          <t>C | 329呎 (1房)
+$616万
+$18,733/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="E18" s="22" t="inlineStr">
+        <is>
+          <t>D | 311呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F18" s="20" t="inlineStr">
+        <is>
+          <t>E | 320呎 (1房)
+$604万
+$18,872/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="G18" s="20" t="inlineStr">
+        <is>
+          <t>F | 320呎 (1房)
+$574万
+$17,944/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="H18" s="20" t="inlineStr">
+        <is>
+          <t>G | 250呎 (开放式)
+$471万
+$18,828/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="I18" s="22" t="inlineStr">
+        <is>
+          <t>H | 322呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="J18" s="20" t="inlineStr">
+        <is>
+          <t>J | 414呎 (2房)
+$817万
+$19,744/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="K18" s="22" t="inlineStr">
+        <is>
+          <t>K | 423呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="58" customHeight="1">
+      <c r="A19" s="19" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="B19" s="22" t="inlineStr">
+        <is>
+          <t>A | 468呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C19" s="20" t="inlineStr">
+        <is>
+          <t>B | 454呎 (2房)
+$959万
+$21,117/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="D19" s="20" t="inlineStr">
+        <is>
+          <t>C | 329呎 (1房)
+$615万
+$18,687/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="E19" s="22" t="inlineStr">
+        <is>
+          <t>D | 311呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F19" s="20" t="inlineStr">
+        <is>
+          <t>E | 320呎 (1房)
+$602万
+$18,825/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="G19" s="20" t="inlineStr">
+        <is>
+          <t>F | 320呎 (1房)
+$573万
+$17,900/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="H19" s="20" t="inlineStr">
+        <is>
+          <t>G | 250呎 (开放式)
+$475万
+$18,992/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="I19" s="22" t="inlineStr">
+        <is>
+          <t>H | 322呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="J19" s="20" t="inlineStr">
+        <is>
+          <t>J | 414呎 (2房)
+$815万
+$19,696/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="K19" s="22" t="inlineStr">
+        <is>
+          <t>K | 423呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="58" customHeight="1">
+      <c r="A20" s="19" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="B20" s="22" t="inlineStr">
+        <is>
+          <t>A | 468呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C20" s="20" t="inlineStr">
+        <is>
+          <t>B | 454呎 (2房)
+$946万
+$20,830/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="D20" s="20" t="inlineStr">
+        <is>
+          <t>C | 329呎 (1房)
+$613万
+$18,641/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="E20" s="22" t="inlineStr">
+        <is>
+          <t>D | 311呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F20" s="20" t="inlineStr">
+        <is>
+          <t>E | 320呎 (1房)
+$601万
+$18,775/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="G20" s="20" t="inlineStr">
+        <is>
+          <t>F | 320呎 (1房)
+$571万
+$17,856/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="H20" s="20" t="inlineStr">
+        <is>
+          <t>G | 250呎 (开放式)
+$468万
+$18,736/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="I20" s="22" t="inlineStr">
+        <is>
+          <t>H | 322呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="J20" s="20" t="inlineStr">
+        <is>
+          <t>J | 414呎 (2房)
+$804万
+$19,428/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="K20" s="22" t="inlineStr">
+        <is>
+          <t>K | 423呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="58" customHeight="1">
+      <c r="A21" s="19" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="B21" s="22" t="inlineStr">
+        <is>
+          <t>A | 468呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C21" s="20" t="inlineStr">
+        <is>
+          <t>B | 454呎 (2房)
+$943万
+$20,780/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="D21" s="20" t="inlineStr">
+        <is>
+          <t>C | 329呎 (1房)
+$612万
+$18,593/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="E21" s="22" t="inlineStr">
+        <is>
+          <t>D | 311呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F21" s="20" t="inlineStr">
+        <is>
+          <t>E | 320呎 (1房)
+$599万
+$18,728/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="G21" s="20" t="inlineStr">
+        <is>
+          <t>F | 320呎 (1房)
+$570万
+$17,812/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="H21" s="20" t="inlineStr">
+        <is>
+          <t>G | 250呎 (开放式)
+$462万
+$18,480/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="I21" s="22" t="inlineStr">
+        <is>
+          <t>H | 322呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="J21" s="20" t="inlineStr">
+        <is>
+          <t>J | 414呎 (2房)
+$811万
+$19,599/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="K21" s="22" t="inlineStr">
+        <is>
+          <t>K | 423呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="58" customHeight="1">
+      <c r="A22" s="19" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B22" s="22" t="inlineStr">
+        <is>
+          <t>A | 468呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C22" s="20" t="inlineStr">
+        <is>
+          <t>B | 454呎 (2房)
+$923万
+$20,322/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="D22" s="20" t="inlineStr">
+        <is>
+          <t>C | 329呎 (1房)
+$610万
+$18,547/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="E22" s="22" t="inlineStr">
+        <is>
+          <t>D | 311呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F22" s="20" t="inlineStr">
+        <is>
+          <t>E | 320呎 (1房)
+$566万
+$17,678/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="G22" s="20" t="inlineStr">
+        <is>
+          <t>F | 320呎 (1房)
+$568万
+$17,766/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="H22" s="20" t="inlineStr">
+        <is>
+          <t>G | 250呎 (开放式)
+$461万
+$18,436/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="I22" s="22" t="inlineStr">
+        <is>
+          <t>H | 322呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="J22" s="20" t="inlineStr">
+        <is>
+          <t>J | 414呎 (2房)
+$800万
+$19,331/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="K22" s="22" t="inlineStr">
+        <is>
+          <t>K | 423呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="58" customHeight="1">
+      <c r="A23" s="19" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B23" s="22" t="inlineStr">
+        <is>
+          <t>A | 468呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C23" s="20" t="inlineStr">
+        <is>
+          <t>B | 454呎 (2房)
+$931万
+$20,500/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="D23" s="20" t="inlineStr">
+        <is>
+          <t>C | 329呎 (1房)
+$609万
+$18,498/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="E23" s="22" t="inlineStr">
+        <is>
+          <t>D | 311呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F23" s="20" t="inlineStr">
+        <is>
+          <t>E | 320呎 (1房)
+$564万
+$17,634/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="G23" s="20" t="inlineStr">
+        <is>
+          <t>F | 320呎 (1房)
+$567万
+$17,722/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="H23" s="20" t="inlineStr">
+        <is>
+          <t>G | 250呎 (开放式)
+$465万
+$18,596/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="I23" s="22" t="inlineStr">
+        <is>
+          <t>H | 322呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="J23" s="20" t="inlineStr">
+        <is>
+          <t>J | 414呎 (2房)
+$798万
+$19,285/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="K23" s="22" t="inlineStr">
+        <is>
+          <t>K | 423呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="58" customHeight="1">
+      <c r="A24" s="19" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B24" s="22" t="inlineStr">
+        <is>
+          <t>A | 468呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C24" s="20" t="inlineStr">
+        <is>
+          <t>B | 454呎 (2房)
+$918万
+$20,220/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="D24" s="20" t="inlineStr">
+        <is>
+          <t>C | 329呎 (1房)
+$607万
+$18,453/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="E24" s="22" t="inlineStr">
+        <is>
+          <t>D | 311呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F24" s="20" t="inlineStr">
+        <is>
+          <t>E | 320呎 (1房)
+$563万
+$17,591/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="G24" s="20" t="inlineStr">
+        <is>
+          <t>F | 320呎 (1房)
+$566万
+$17,678/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="H24" s="20" t="inlineStr">
+        <is>
+          <t>G | 250呎 (开放式)
+$459万
+$18,344/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="I24" s="22" t="inlineStr">
+        <is>
+          <t>H | 322呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="J24" s="20" t="inlineStr">
+        <is>
+          <t>J | 414呎 (2房)
+$796万
+$19,234/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="K24" s="22" t="inlineStr">
+        <is>
+          <t>K | 423呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="58" customHeight="1">
+      <c r="A25" s="19" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B25" s="22" t="inlineStr">
+        <is>
+          <t>A | 468呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C25" s="20" t="inlineStr">
+        <is>
+          <t>B | 454呎 (2房)
+$913万
+$20,119/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="D25" s="20" t="inlineStr">
+        <is>
+          <t>C | 329呎 (1房)
+$604万
+$18,362/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="E25" s="22" t="inlineStr">
+        <is>
+          <t>D | 311呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F25" s="20" t="inlineStr">
+        <is>
+          <t>E | 320呎 (1房)
+$560万
+$17,503/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="G25" s="20" t="inlineStr">
+        <is>
+          <t>F | 320呎 (1房)
+$563万
+$17,591/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="H25" s="20" t="inlineStr">
+        <is>
+          <t>G | 250呎 (开放式)
+$426万
+$17,056/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="I25" s="22" t="inlineStr">
+        <is>
+          <t>H | 322呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="J25" s="20" t="inlineStr">
+        <is>
+          <t>J | 414呎 (2房)
+$792万
+$19,140/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="K25" s="22" t="inlineStr">
+        <is>
+          <t>K | 423呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="58" customHeight="1">
+      <c r="A26" s="19" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B26" s="22" t="inlineStr">
+        <is>
+          <t>A | 468呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C26" s="20" t="inlineStr">
+        <is>
+          <t>B | 454呎 (2房)
+$911万
+$20,068/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="D26" s="20" t="inlineStr">
+        <is>
+          <t>C | 329呎 (1房)
+$603万
+$18,319/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="E26" s="22" t="inlineStr">
+        <is>
+          <t>D | 311呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F26" s="20" t="inlineStr">
+        <is>
+          <t>E | 320呎 (1房)
+$559万
+$17,462/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="G26" s="20" t="inlineStr">
+        <is>
+          <t>F | 320呎 (1房)
+$562万
+$17,547/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="H26" s="20" t="inlineStr">
+        <is>
+          <t>G | 250呎 (开放式)
+$425万
+$17,016/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="I26" s="22" t="inlineStr">
+        <is>
+          <t>H | 322呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="J26" s="20" t="inlineStr">
+        <is>
+          <t>J | 414呎 (2房)
+$790万
+$19,094/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="K26" s="22" t="inlineStr">
+        <is>
+          <t>K | 423呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="58" customHeight="1">
+      <c r="A27" s="19" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B27" s="22" t="inlineStr">
+        <is>
+          <t>A | 468呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C27" s="20" t="inlineStr">
+        <is>
+          <t>B | 454呎 (2房)
+$909万
+$20,018/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="D27" s="20" t="inlineStr">
+        <is>
+          <t>C | 329呎 (1房)
+$601万
+$18,274/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="E27" s="22" t="inlineStr">
+        <is>
+          <t>D | 311呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F27" s="20" t="inlineStr">
+        <is>
+          <t>E | 320呎 (1房)
+$557万
+$17,419/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="G27" s="20" t="inlineStr">
+        <is>
+          <t>F | 320呎 (1房)
+$560万
+$17,503/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="H27" s="20" t="inlineStr">
+        <is>
+          <t>G | 250呎 (开放式)
+$424万
+$16,972/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="I27" s="22" t="inlineStr">
+        <is>
+          <t>H | 322呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="J27" s="20" t="inlineStr">
+        <is>
+          <t>J | 414呎 (2房)
+$744万
+$17,966/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="K27" s="22" t="inlineStr">
+        <is>
+          <t>K | 423呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="58" customHeight="1">
+      <c r="A28" s="19" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B28" s="22" t="inlineStr">
+        <is>
+          <t>A | 468呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C28" s="20" t="inlineStr">
+        <is>
+          <t>B | 454呎 (2房)
+$906万
+$19,967/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="D28" s="20" t="inlineStr">
+        <is>
+          <t>C | 329呎 (1房)
+$606万
+$18,432/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="E28" s="22" t="inlineStr">
+        <is>
+          <t>D | 311呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F28" s="20" t="inlineStr">
+        <is>
+          <t>E | 320呎 (1房)
+$556万
+$17,372/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="G28" s="20" t="inlineStr">
+        <is>
+          <t>F | 320呎 (1房)
+$559万
+$17,459/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="H28" s="20" t="inlineStr">
+        <is>
+          <t>G | 250呎 (开放式)
+$442万
+$17,700/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="I28" s="22" t="inlineStr">
+        <is>
+          <t>H | 322呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="J28" s="20" t="inlineStr">
+        <is>
+          <t>J | 414呎 (2房)
+$776万
+$18,737/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="K28" s="22" t="inlineStr">
+        <is>
+          <t>K | 423呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="58" customHeight="1">
+      <c r="A29" s="19" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B29" s="22" t="inlineStr">
+        <is>
+          <t>A | 468呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C29" s="20" t="inlineStr">
+        <is>
+          <t>B | 454呎 (2房)
+$904万
+$19,919/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="D29" s="20" t="inlineStr">
+        <is>
+          <t>C | 329呎 (1房)
+$598万
+$18,179/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="E29" s="22" t="inlineStr">
+        <is>
+          <t>D | 311呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F29" s="20" t="inlineStr">
+        <is>
+          <t>E | 320呎 (1房)
+$554万
+$17,328/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="G29" s="20" t="inlineStr">
+        <is>
+          <t>F | 320呎 (1房)
+$557万
+$17,419/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="H29" s="20" t="inlineStr">
+        <is>
+          <t>G | 250呎 (开放式)
+$422万
+$16,888/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="I29" s="22" t="inlineStr">
+        <is>
+          <t>H | 322呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="J29" s="20" t="inlineStr">
+        <is>
+          <t>J | 414呎 (2房)
+$774万
+$18,691/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="K29" s="22" t="inlineStr">
+        <is>
+          <t>K | 423呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="58" customHeight="1">
+      <c r="A30" s="19" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B30" s="22" t="inlineStr">
+        <is>
+          <t>A | 468呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C30" s="20" t="inlineStr">
+        <is>
+          <t>B | 454呎 (2房)
+$902万
+$19,868/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="D30" s="20" t="inlineStr">
+        <is>
+          <t>C | 329呎 (1房)
+$597万
+$18,134/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="E30" s="22" t="inlineStr">
+        <is>
+          <t>D | 311呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F30" s="20" t="inlineStr">
+        <is>
+          <t>E | 320呎 (1房)
+$553万
+$17,284/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="G30" s="20" t="inlineStr">
+        <is>
+          <t>F | 320呎 (1房)
+$556万
+$17,372/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="H30" s="20" t="inlineStr">
+        <is>
+          <t>G | 250呎 (开放式)
+$421万
+$16,844/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="I30" s="22" t="inlineStr">
+        <is>
+          <t>H | 322呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="J30" s="20" t="inlineStr">
+        <is>
+          <t>J | 414呎 (2房)
+$738万
+$17,833/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="K30" s="22" t="inlineStr">
+        <is>
+          <t>K | 423呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="58" customHeight="1">
+      <c r="A31" s="19" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B31" s="22" t="inlineStr">
+        <is>
+          <t>A | 468呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C31" s="20" t="inlineStr">
+        <is>
+          <t>B | 454呎 (2房)
+$900万
+$19,819/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="D31" s="20" t="inlineStr">
+        <is>
+          <t>C | 329呎 (1房)
+$595万
+$18,091/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="E31" s="22" t="inlineStr">
+        <is>
+          <t>D | 311呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F31" s="20" t="inlineStr">
+        <is>
+          <t>E | 320呎 (1房)
+$577万
+$18,028/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="G31" s="20" t="inlineStr">
+        <is>
+          <t>F | 320呎 (1房)
+$561万
+$17,525/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="H31" s="20" t="inlineStr">
+        <is>
+          <t>G | 250呎 (开放式)
+$420万
+$16,804/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="I31" s="22" t="inlineStr">
+        <is>
+          <t>H | 322呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="J31" s="20" t="inlineStr">
+        <is>
+          <t>J | 414呎 (2房)
+$736万
+$17,787/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="K31" s="22" t="inlineStr">
+        <is>
+          <t>K | 423呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="58" customHeight="1">
+      <c r="A32" s="19" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B32" s="22" t="inlineStr">
+        <is>
+          <t>A | 468呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C32" s="20" t="inlineStr">
+        <is>
+          <t>B | 454呎 (2房)
+$908万
+$19,996/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="D32" s="20" t="inlineStr">
+        <is>
+          <t>C | 329呎 (1房)
+$594万
+$18,046/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="E32" s="22" t="inlineStr">
+        <is>
+          <t>D | 311呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F32" s="20" t="inlineStr">
+        <is>
+          <t>E | 320呎 (1房)
+$582万
+$18,178/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="G32" s="20" t="inlineStr">
+        <is>
+          <t>F | 320呎 (1房)
+$553万
+$17,284/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="H32" s="20" t="inlineStr">
+        <is>
+          <t>G | 250呎 (开放式)
+$419万
+$16,764/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="I32" s="22" t="inlineStr">
+        <is>
+          <t>H | 322呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="J32" s="20" t="inlineStr">
+        <is>
+          <t>J | 414呎 (2房)
+$735万
+$17,744/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="K32" s="22" t="inlineStr">
+        <is>
+          <t>K | 423呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="58" customHeight="1">
+      <c r="A33" s="19" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B33" s="22" t="inlineStr">
+        <is>
+          <t>A | 468呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C33" s="20" t="inlineStr">
+        <is>
+          <t>B | 454呎 (2房)
+$903万
+$19,894/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="D33" s="20" t="inlineStr">
+        <is>
+          <t>C | 329呎 (1房)
+$596万
+$18,106/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="E33" s="22" t="inlineStr">
+        <is>
+          <t>D | 311呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F33" s="24" t="inlineStr">
+        <is>
+          <t>E | 319呎 (1房)
+$622万
+$19,508/呎
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="G33" s="20" t="inlineStr">
+        <is>
+          <t>F | 320呎 (1房)
+$548万
+$17,116/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="H33" s="20" t="inlineStr">
+        <is>
+          <t>G | 250呎 (开放式)
+$451万
+$18,044/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="I33" s="22" t="inlineStr">
+        <is>
+          <t>H | 322呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="J33" s="20" t="inlineStr">
+        <is>
+          <t>J | 414呎 (2房)
+$731万
+$17,657/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="K33" s="22" t="inlineStr">
+        <is>
+          <t>K | 423呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="58" customHeight="1">
+      <c r="A34" s="19" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B34" s="22" t="inlineStr">
+        <is>
+          <t>A | 468呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C34" s="20" t="inlineStr">
+        <is>
+          <t>B | 454呎 (2房)
+$919万
+$20,240/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="D34" s="20" t="inlineStr">
+        <is>
+          <t>C | 329呎 (1房)
+$594万
+$18,061/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="E34" s="22" t="inlineStr">
+        <is>
+          <t>D | 311呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F34" s="20" t="inlineStr">
+        <is>
+          <t>E | 320呎 (1房)
+$546万
+$17,075/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="G34" s="24" t="inlineStr">
+        <is>
+          <t>F | 319呎 (1房)
+$621万
+$19,458/呎
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="H34" s="20" t="inlineStr">
+        <is>
+          <t>G | 250呎 (开放式)
+$450万
+$18,000/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="I34" s="22" t="inlineStr">
+        <is>
+          <t>H | 322呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="J34" s="20" t="inlineStr">
+        <is>
+          <t>J | 414呎 (2房)
+$782万
+$18,877/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="K34" s="22" t="inlineStr">
+        <is>
+          <t>K | 423呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="58" customHeight="1">
+      <c r="A35" s="19" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B35" s="22" t="inlineStr">
+        <is>
+          <t>A | 468呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C35" s="22" t="inlineStr">
+        <is>
+          <t>B | 455呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D35" s="22" t="inlineStr">
+        <is>
+          <t>C | 330呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E35" s="22" t="inlineStr">
+        <is>
+          <t>D | 311呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F35" s="22" t="inlineStr">
+        <is>
+          <t>E | 319呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G35" s="22" t="inlineStr">
+        <is>
+          <t>F | 319呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H35" s="22" t="inlineStr">
+        <is>
+          <t>G | 249呎 (开放式)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="I35" s="22" t="inlineStr">
+        <is>
+          <t>H | 322呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="J35" s="22" t="inlineStr">
+        <is>
+          <t>J | 414呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="K35" s="22" t="inlineStr">
+        <is>
+          <t>K | 423呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="58" customHeight="1">
+      <c r="A36" s="19" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B36" s="22" t="inlineStr">
+        <is>
+          <t>A | 468呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C36" s="22" t="inlineStr">
+        <is>
+          <t>B | 340呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D36" s="22" t="inlineStr">
+        <is>
+          <t>C | 330呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E36" s="22" t="inlineStr">
+        <is>
+          <t>D | 311呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F36" s="22" t="inlineStr">
+        <is>
+          <t>E | 319呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G36" s="22" t="inlineStr">
+        <is>
+          <t>F | 319呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H36" s="22" t="inlineStr">
+        <is>
+          <t>G | 249呎 (开放式)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="I36" s="22" t="inlineStr">
+        <is>
+          <t>H | 322呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="J36" s="22" t="inlineStr">
+        <is>
+          <t>J | 414呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="K36" s="22" t="inlineStr">
+        <is>
+          <t>K | 423呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="58" customHeight="1">
+      <c r="A37" s="19" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B37" s="22" t="inlineStr">
+        <is>
+          <t>A | 431呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C37" s="22" t="inlineStr">
+        <is>
+          <t>B | 302呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D37" s="22" t="inlineStr">
+        <is>
+          <t>C | 292呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E37" s="22" t="inlineStr">
+        <is>
+          <t>D | 311呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F37" s="22" t="inlineStr">
+        <is>
+          <t>E | 319呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G37" s="22" t="inlineStr">
+        <is>
+          <t>F | 319呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H37" s="22" t="inlineStr">
+        <is>
+          <t>G | 249呎 (开放式)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="I37" s="22" t="inlineStr">
+        <is>
+          <t>H | 322呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="J37" s="22" t="inlineStr">
+        <is>
+          <t>J | 414呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="K37" s="22" t="inlineStr">
+        <is>
+          <t>K | 423呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
+  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
+</worksheet>
 </file>
--- a/files/九龙-启德-Double Coast III.xlsx
+++ b/files/九龙-启德-Double Coast III.xlsx
@@ -662,7 +662,7 @@
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
   </cols>

--- a/files/九龙-启德-Double Coast III.xlsx
+++ b/files/九龙-启德-Double Coast III.xlsx
@@ -3094,14 +3094,14 @@
       </c>
       <c r="J36" s="3" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>8%</t>
         </is>
       </c>
       <c r="K36" s="5" t="n">
-        <v>16299150</v>
+        <v>16615200</v>
       </c>
       <c r="L36" s="5" t="n">
-        <v>23418</v>
+        <v>23872</v>
       </c>
       <c r="M36" s="3" t="inlineStr">
         <is>
@@ -3506,14 +3506,14 @@
       </c>
       <c r="J42" s="3" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>8%</t>
         </is>
       </c>
       <c r="K42" s="5" t="n">
-        <v>16258538</v>
+        <v>16573800</v>
       </c>
       <c r="L42" s="5" t="n">
-        <v>23360</v>
+        <v>23813</v>
       </c>
       <c r="M42" s="3" t="inlineStr">
         <is>
@@ -4718,14 +4718,14 @@
       </c>
       <c r="J60" s="3" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>8%</t>
         </is>
       </c>
       <c r="K60" s="5" t="n">
-        <v>16136700</v>
+        <v>16449600</v>
       </c>
       <c r="L60" s="5" t="n">
-        <v>23185</v>
+        <v>23634</v>
       </c>
       <c r="M60" s="3" t="inlineStr">
         <is>
@@ -5534,14 +5534,14 @@
       </c>
       <c r="J72" s="3" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>8%</t>
         </is>
       </c>
       <c r="K72" s="5" t="n">
-        <v>16016668</v>
+        <v>16327240</v>
       </c>
       <c r="L72" s="5" t="n">
-        <v>23012</v>
+        <v>23459</v>
       </c>
       <c r="M72" s="3" t="inlineStr">
         <is>
@@ -12574,14 +12574,14 @@
       </c>
       <c r="J180" s="3" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>8%</t>
         </is>
       </c>
       <c r="K180" s="5" t="n">
-        <v>15236908</v>
+        <v>15532360</v>
       </c>
       <c r="L180" s="5" t="n">
-        <v>21892</v>
+        <v>22317</v>
       </c>
       <c r="M180" s="3" t="inlineStr">
         <is>
@@ -32656,14 +32656,14 @@
       </c>
       <c r="J483" s="3" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>7%</t>
         </is>
       </c>
       <c r="K483" s="5" t="n">
-        <v>5616258</v>
+        <v>5787390</v>
       </c>
       <c r="L483" s="5" t="n">
-        <v>17606</v>
+        <v>18142</v>
       </c>
       <c r="M483" s="3" t="inlineStr">
         <is>
@@ -33246,14 +33246,14 @@
       </c>
       <c r="J492" s="3" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>7%</t>
         </is>
       </c>
       <c r="K492" s="5" t="n">
-        <v>5601818</v>
+        <v>5772510</v>
       </c>
       <c r="L492" s="5" t="n">
-        <v>17561</v>
+        <v>18096</v>
       </c>
       <c r="M492" s="3" t="inlineStr">
         <is>

--- a/files/九龙-启德-Double Coast III.xlsx
+++ b/files/九龙-启德-Double Coast III.xlsx
@@ -32656,7 +32656,7 @@
       </c>
       <c r="J483" s="3" t="inlineStr">
         <is>
-          <t>7%</t>
+          <t>7.0%</t>
         </is>
       </c>
       <c r="K483" s="5" t="n">
@@ -33246,7 +33246,7 @@
       </c>
       <c r="J492" s="3" t="inlineStr">
         <is>
-          <t>7%</t>
+          <t>7.0%</t>
         </is>
       </c>
       <c r="K492" s="5" t="n">

--- a/files/九龙-启德-Double Coast III.xlsx
+++ b/files/九龙-启德-Double Coast III.xlsx
@@ -35838,7 +35838,7 @@
           <t>A | 1378呎 (4+房)
 $4668万
 $33,877/呎
-(26年-04月-07日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="C5" s="21" t="inlineStr"/>
@@ -36256,7 +36256,7 @@
           <t>F | 431呎 (2房)
 $791万
 $18,346/呎
-(26年-05月-05日)</t>
+(26年-05月)</t>
         </is>
       </c>
     </row>
@@ -36279,7 +36279,7 @@
           <t>B | 695呎 (3房)
 $1631万
 $23,471/呎
-(26年-04月-26日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="D13" s="22" t="inlineStr">
@@ -36311,7 +36311,7 @@
           <t>F | 431呎 (2房)
 $789万
 $18,302/呎
-(26年-05月-06日)</t>
+(26年-05月)</t>
         </is>
       </c>
     </row>
@@ -36358,7 +36358,7 @@
           <t>E | 429呎 (2房)
 $800万
 $18,653/呎
-(26年-05月-05日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="G14" s="20" t="inlineStr">
@@ -36366,7 +36366,7 @@
           <t>F | 431呎 (2房)
 $796万
 $18,459/呎
-(26年-05月-06日)</t>
+(26年-05月)</t>
         </is>
       </c>
     </row>
@@ -36468,7 +36468,7 @@
           <t>E | 429呎 (2房)
 $794万
 $18,513/呎
-(26年-05月-07日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="G16" s="20" t="inlineStr">
@@ -36476,7 +36476,7 @@
           <t>F | 431呎 (2房)
 $790万
 $18,323/呎
-(26年-05月-06日)</t>
+(26年-05月)</t>
         </is>
       </c>
     </row>
@@ -36499,7 +36499,7 @@
           <t>B | 695呎 (3房)
 $1558万
 $22,416/呎
-(26年-01月-29日)</t>
+(26年-01月)</t>
         </is>
       </c>
       <c r="D17" s="22" t="inlineStr">
@@ -36523,7 +36523,7 @@
           <t>E | 429呎 (2房)
 $792万
 $18,466/呎
-(26年-05月-06日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="G17" s="20" t="inlineStr">
@@ -36531,7 +36531,7 @@
           <t>F | 431呎 (2房)
 $788万
 $18,276/呎
-(26年-05月-05日)</t>
+(26年-05月)</t>
         </is>
       </c>
     </row>
@@ -36578,7 +36578,7 @@
           <t>E | 429呎 (2房)
 $790万
 $18,420/呎
-(26年-05月-06日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="G18" s="20" t="inlineStr">
@@ -36586,7 +36586,7 @@
           <t>F | 431呎 (2房)
 $786万
 $18,230/呎
-(26年-05月-17日)</t>
+(26年-05月)</t>
         </is>
       </c>
     </row>
@@ -36609,7 +36609,7 @@
           <t>B | 695呎 (3房)
 $1550万
 $22,304/呎
-(26年-02月-09日)</t>
+(26年-02月)</t>
         </is>
       </c>
       <c r="D19" s="22" t="inlineStr">
@@ -36633,7 +36633,7 @@
           <t>E | 429呎 (2房)
 $788万
 $18,373/呎
-(26年-05月-06日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="G19" s="20" t="inlineStr">
@@ -36641,7 +36641,7 @@
           <t>F | 431呎 (2房)
 $792万
 $18,387/呎
-(26年-05月-14日)</t>
+(26年-05月)</t>
         </is>
       </c>
     </row>
@@ -36664,7 +36664,7 @@
           <t>B | 695呎 (3房)
 $1546万
 $22,249/呎
-(26年-02月-25日)</t>
+(26年-02月)</t>
         </is>
       </c>
       <c r="D20" s="22" t="inlineStr">
@@ -36688,7 +36688,7 @@
           <t>E | 429呎 (2房)
 $786万
 $18,329/呎
-(26年-05月-06日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="G20" s="20" t="inlineStr">
@@ -36696,7 +36696,7 @@
           <t>F | 431呎 (2房)
 $782万
 $18,139/呎
-(26年-05月-05日)</t>
+(26年-05月)</t>
         </is>
       </c>
     </row>
@@ -36711,7 +36711,7 @@
           <t>A | 640呎 (3房)
 $1444万
 $22,564/呎
-(26年-05月-18日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="C21" s="20" t="inlineStr">
@@ -36719,7 +36719,7 @@
           <t>B | 695呎 (3房)
 $1542万
 $22,193/呎
-(26年-03月-02日)</t>
+(26年-03月)</t>
         </is>
       </c>
       <c r="D21" s="22" t="inlineStr">
@@ -36743,7 +36743,7 @@
           <t>E | 429呎 (2房)
 $784万
 $18,282/呎
-(26年-05月-06日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="G21" s="20" t="inlineStr">
@@ -36751,7 +36751,7 @@
           <t>F | 431呎 (2房)
 $780万
 $18,095/呎
-(26年-05月-05日)</t>
+(26年-05月)</t>
         </is>
       </c>
     </row>
@@ -36766,7 +36766,7 @@
           <t>A | 640呎 (3房)
 $1432万
 $22,383/呎
-(26年-05月-05日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="C22" s="20" t="inlineStr">
@@ -36774,7 +36774,7 @@
           <t>B | 695呎 (3房)
 $1556万
 $22,388/呎
-(26年-01月-20日)</t>
+(26年-01月)</t>
         </is>
       </c>
       <c r="D22" s="22" t="inlineStr">
@@ -36798,7 +36798,7 @@
           <t>E | 429呎 (2房)
 $782万
 $18,238/呎
-(26年-05月-06日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="G22" s="20" t="inlineStr">
@@ -36806,7 +36806,7 @@
           <t>F | 431呎 (2房)
 $769万
 $17,849/呎
-(26年-05月-05日)</t>
+(26年-05月)</t>
         </is>
       </c>
     </row>
@@ -36821,7 +36821,7 @@
           <t>A | 640呎 (3房)
 $1429万
 $22,327/呎
-(26年-05月-06日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="C23" s="20" t="inlineStr">
@@ -36829,7 +36829,7 @@
           <t>B | 695呎 (3房)
 $1604万
 $23,085/呎
-(26年-01月-07日)</t>
+(26年-01月)</t>
         </is>
       </c>
       <c r="D23" s="22" t="inlineStr">
@@ -36853,7 +36853,7 @@
           <t>E | 429呎 (2房)
 $780万
 $18,191/呎
-(26年-05月-11日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="G23" s="20" t="inlineStr">
@@ -36861,7 +36861,7 @@
           <t>F | 431呎 (2房)
 $776万
 $18,005/呎
-(26年-05月-12日)</t>
+(26年-05月)</t>
         </is>
       </c>
     </row>
@@ -36876,7 +36876,7 @@
           <t>A | 640呎 (3房)
 $1433万
 $22,397/呎
-(26年-05月-20日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="C24" s="20" t="inlineStr">
@@ -36884,7 +36884,7 @@
           <t>B | 695呎 (3房)
 $1531万
 $22,027/呎
-(26年-03月-03日)</t>
+(26年-03月)</t>
         </is>
       </c>
       <c r="D24" s="22" t="inlineStr">
@@ -36908,7 +36908,7 @@
           <t>E | 429呎 (2房)
 $787万
 $18,350/呎
-(26年-05月-17日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="G24" s="20" t="inlineStr">
@@ -36916,7 +36916,7 @@
           <t>F | 431呎 (2房)
 $729万
 $16,914/呎
-(26年-01月-05日)</t>
+(26年-01月)</t>
         </is>
       </c>
     </row>
@@ -36931,7 +36931,7 @@
           <t>A | 640呎 (3房)
 $1426万
 $22,284/呎
-(26年-05月-17日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="C25" s="20" t="inlineStr">
@@ -36939,7 +36939,7 @@
           <t>B | 695呎 (3房)
 $1523万
 $21,917/呎
-(26年-02月-22日)</t>
+(26年-02月)</t>
         </is>
       </c>
       <c r="D25" s="22" t="inlineStr">
@@ -36963,7 +36963,7 @@
           <t>E | 429呎 (2房)
 $783万
 $18,259/呎
-(26年-05月-14日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="G25" s="20" t="inlineStr">
@@ -36971,7 +36971,7 @@
           <t>F | 431呎 (2房)
 $725万
 $16,828/呎
-(26年-01月-07日)</t>
+(26年-01月)</t>
         </is>
       </c>
     </row>
@@ -36986,7 +36986,7 @@
           <t>A | 640呎 (3房)
 $1415万
 $22,105/呎
-(26年-05月-06日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="C26" s="20" t="inlineStr">
@@ -36994,7 +36994,7 @@
           <t>B | 695呎 (3房)
 $1520万
 $21,863/呎
-(26年-03月-01日)</t>
+(26年-03月)</t>
         </is>
       </c>
       <c r="D26" s="22" t="inlineStr">
@@ -37018,7 +37018,7 @@
           <t>E | 429呎 (2房)
 $773万
 $18,012/呎
-(26年-05月-07日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="G26" s="20" t="inlineStr">
@@ -37026,7 +37026,7 @@
           <t>F | 431呎 (2房)
 $724万
 $16,789/呎
-(26年-01月-07日)</t>
+(26年-01月)</t>
         </is>
       </c>
     </row>
@@ -37041,7 +37041,7 @@
           <t>A | 640呎 (3房)
 $1357万
 $21,202/呎
-(26年-01月-13日)</t>
+(26年-01月)</t>
         </is>
       </c>
       <c r="C27" s="20" t="inlineStr">
@@ -37049,7 +37049,7 @@
           <t>B | 695呎 (3房)
 $1516万
 $21,809/呎
-(26年-01月-08日)</t>
+(26年-01月)</t>
         </is>
       </c>
       <c r="D27" s="22" t="inlineStr">
@@ -37073,7 +37073,7 @@
           <t>E | 429呎 (2房)
 $771万
 $17,967/呎
-(26年-05月-07日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="G27" s="20" t="inlineStr">
@@ -37081,7 +37081,7 @@
           <t>F | 431呎 (2房)
 $722万
 $16,745/呎
-(26年-01月-05日)</t>
+(26年-01月)</t>
         </is>
       </c>
     </row>
@@ -37096,7 +37096,7 @@
           <t>A | 640呎 (3房)
 $1416万
 $22,119/呎
-(26年-05月-20日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="C28" s="20" t="inlineStr">
@@ -37104,7 +37104,7 @@
           <t>B | 695呎 (3房)
 $1512万
 $21,754/呎
-(26年-01月-08日)</t>
+(26年-01月)</t>
         </is>
       </c>
       <c r="D28" s="22" t="inlineStr">
@@ -37128,7 +37128,7 @@
           <t>E | 429呎 (2房)
 $740万
 $17,261/呎
-(26年-01月-07日)</t>
+(26年-01月)</t>
         </is>
       </c>
       <c r="G28" s="20" t="inlineStr">
@@ -37136,7 +37136,7 @@
           <t>F | 431呎 (2房)
 $720万
 $16,705/呎
-(26年-01月-06日)</t>
+(26年-01月)</t>
         </is>
       </c>
     </row>
@@ -37151,7 +37151,7 @@
           <t>A | 640呎 (3房)
 $1404万
 $21,941/呎
-(26年-05月-07日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="C29" s="20" t="inlineStr">
@@ -37159,7 +37159,7 @@
           <t>B | 695呎 (3房)
 $1508万
 $21,699/呎
-(26年-02月-24日)</t>
+(26年-02月)</t>
         </is>
       </c>
       <c r="D29" s="22" t="inlineStr">
@@ -37183,7 +37183,7 @@
           <t>E | 429呎 (2房)
 $730万
 $17,026/呎
-(26年-01月-08日)</t>
+(26年-01月)</t>
         </is>
       </c>
       <c r="G29" s="20" t="inlineStr">
@@ -37191,7 +37191,7 @@
           <t>F | 431呎 (2房)
 $718万
 $16,661/呎
-(26年-01月-01日)</t>
+(26年-01月)</t>
         </is>
       </c>
     </row>
@@ -37206,7 +37206,7 @@
           <t>A | 640呎 (3房)
 $1401万
 $21,884/呎
-(26年-05月-12日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="C30" s="20" t="inlineStr">
@@ -37214,7 +37214,7 @@
           <t>B | 695呎 (3房)
 $1522万
 $21,892/呎
-(26年-02月-25日)</t>
+(26年-02月)</t>
         </is>
       </c>
       <c r="D30" s="22" t="inlineStr">
@@ -37238,7 +37238,7 @@
           <t>E | 429呎 (2房)
 $729万
 $16,984/呎
-(26年-01月-11日)</t>
+(26年-01月)</t>
         </is>
       </c>
       <c r="G30" s="20" t="inlineStr">
@@ -37246,7 +37246,7 @@
           <t>F | 431呎 (2房)
 $716万
 $16,622/呎
-(26年-01月-06日)</t>
+(26年-01月)</t>
         </is>
       </c>
     </row>
@@ -37261,7 +37261,7 @@
           <t>A | 640呎 (3房)
 $1397万
 $21,831/呎
-(26年-05月-05日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="C31" s="20" t="inlineStr">
@@ -37269,7 +37269,7 @@
           <t>B | 695呎 (3房)
 $1501万
 $21,591/呎
-(26年-01月-13日)</t>
+(26年-01月)</t>
         </is>
       </c>
       <c r="D31" s="22" t="inlineStr">
@@ -37293,7 +37293,7 @@
           <t>E | 429呎 (2房)
 $727万
 $16,942/呎
-(26年-01月-12日)</t>
+(26年-01月)</t>
         </is>
       </c>
       <c r="G31" s="20" t="inlineStr">
@@ -37301,7 +37301,7 @@
           <t>F | 431呎 (2房)
 $750万
 $17,408/呎
-(26年-05月-18日)</t>
+(26年-05月)</t>
         </is>
       </c>
     </row>
@@ -37316,7 +37316,7 @@
           <t>A | 640呎 (3房)
 $1340万
 $20,939/呎
-(26年-01月-14日)</t>
+(26年-01月)</t>
         </is>
       </c>
       <c r="C32" s="20" t="inlineStr">
@@ -37324,7 +37324,7 @@
           <t>B | 695呎 (3房)
 $1497万
 $21,538/呎
-(26年-01月-15日)</t>
+(26年-01月)</t>
         </is>
       </c>
       <c r="D32" s="22" t="inlineStr">
@@ -37348,7 +37348,7 @@
           <t>E | 429呎 (2房)
 $725万
 $16,897/呎
-(26年-01月-11日)</t>
+(26年-01月)</t>
         </is>
       </c>
       <c r="G32" s="20" t="inlineStr">
@@ -37356,7 +37356,7 @@
           <t>F | 431呎 (2房)
 $748万
 $17,367/呎
-(26年-05月-13日)</t>
+(26年-05月)</t>
         </is>
       </c>
     </row>
@@ -37379,7 +37379,7 @@
           <t>B | 695呎 (3房)
 $1557万
 $22,404/呎
-(26年-04月-21日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="D33" s="22" t="inlineStr">
@@ -37403,7 +37403,7 @@
           <t>E | 429呎 (2房)
 $766万
 $17,853/呎
-(26年-05月-19日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="G33" s="20" t="inlineStr">
@@ -37411,7 +37411,7 @@
           <t>F | 431呎 (2房)
 $753万
 $17,473/呎
-(26年-05月-18日)</t>
+(26年-05月)</t>
         </is>
       </c>
     </row>
@@ -37458,7 +37458,7 @@
           <t>E | 429呎 (2房)
 $756万
 $17,611/呎
-(26年-05月-11日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="G34" s="20" t="inlineStr">
@@ -37466,7 +37466,7 @@
           <t>F | 431呎 (2房)
 $743万
 $17,234/呎
-(26年-05月-14日)</t>
+(26年-05月)</t>
         </is>
       </c>
     </row>
@@ -38068,7 +38068,7 @@
           <t>C | 329呎 (1房)
 $639万
 $19,416/呎
-(26年-05月-18日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="E8" s="22" t="inlineStr">
@@ -38084,7 +38084,7 @@
           <t>E | 320呎 (1房)
 $622万
 $19,431/呎
-(26年-05月-14日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="G8" s="20" t="inlineStr">
@@ -38092,7 +38092,7 @@
           <t>F | 320呎 (1房)
 $620万
 $19,369/呎
-(26年-05月-05日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="H8" s="20" t="inlineStr">
@@ -38100,7 +38100,7 @@
           <t>G | 250呎 (开放式)
 $478万
 $19,136/呎
-(26年-05月-10日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="I8" s="22" t="inlineStr">
@@ -38155,7 +38155,7 @@
           <t>C | 329呎 (1房)
 $637万
 $19,368/呎
-(26年-05月-20日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="E9" s="22" t="inlineStr">
@@ -38171,7 +38171,7 @@
           <t>E | 320呎 (1房)
 $620万
 $19,384/呎
-(26年-05月-18日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="G9" s="20" t="inlineStr">
@@ -38179,7 +38179,7 @@
           <t>F | 320呎 (1房)
 $618万
 $19,319/呎
-(26年-05月-06日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="H9" s="20" t="inlineStr">
@@ -38187,7 +38187,7 @@
           <t>G | 250呎 (开放式)
 $477万
 $19,092/呎
-(26年-05月-10日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="I9" s="22" t="inlineStr">
@@ -38203,7 +38203,7 @@
           <t>J | 414呎 (2房)
 $829万
 $20,019/呎
-(26年-05月-12日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="K9" s="22" t="inlineStr">
@@ -38242,7 +38242,7 @@
           <t>C | 329呎 (1房)
 $643万
 $19,535/呎
-(26年-05月-20日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="E10" s="22" t="inlineStr">
@@ -38258,7 +38258,7 @@
           <t>E | 320呎 (1房)
 $619万
 $19,338/呎
-(26年-05月-18日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="G10" s="20" t="inlineStr">
@@ -38266,7 +38266,7 @@
           <t>F | 320呎 (1房)
 $622万
 $19,431/呎
-(26年-05月-14日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="H10" s="20" t="inlineStr">
@@ -38274,7 +38274,7 @@
           <t>G | 250呎 (开放式)
 $482万
 $19,260/呎
-(26年-05月-19日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="I10" s="22" t="inlineStr">
@@ -38290,7 +38290,7 @@
           <t>J | 414呎 (2房)
 $836万
 $20,196/呎
-(26年-05月-20日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="K10" s="22" t="inlineStr">
@@ -38329,7 +38329,7 @@
           <t>C | 329呎 (1房)
 $629万
 $19,109/呎
-(26年-05月-06日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="E11" s="22" t="inlineStr">
@@ -38345,7 +38345,7 @@
           <t>E | 320呎 (1房)
 $617万
 $19,291/呎
-(26年-05月-18日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="G11" s="20" t="inlineStr">
@@ -38353,7 +38353,7 @@
           <t>F | 320呎 (1房)
 $622万
 $19,438/呎
-(26年-04月-09日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="H11" s="20" t="inlineStr">
@@ -38361,7 +38361,7 @@
           <t>G | 250呎 (开放式)
 $475万
 $18,996/呎
-(26年-05月-06日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="I11" s="22" t="inlineStr">
@@ -38377,7 +38377,7 @@
           <t>J | 414呎 (2房)
 $825万
 $19,920/呎
-(26年-05月-07日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="K11" s="22" t="inlineStr">
@@ -38416,7 +38416,7 @@
           <t>C | 329呎 (1房)
 $627万
 $19,061/呎
-(26年-05月-07日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="E12" s="22" t="inlineStr">
@@ -38432,7 +38432,7 @@
           <t>E | 320呎 (1房)
 $616万
 $19,241/呎
-(26年-05月-18日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="G12" s="20" t="inlineStr">
@@ -38440,7 +38440,7 @@
           <t>F | 320呎 (1房)
 $614万
 $19,175/呎
-(26年-05月-05日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="H12" s="20" t="inlineStr">
@@ -38448,7 +38448,7 @@
           <t>G | 250呎 (开放式)
 $474万
 $18,948/呎
-(26年-05月-06日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="I12" s="22" t="inlineStr">
@@ -38464,7 +38464,7 @@
           <t>J | 414呎 (2房)
 $823万
 $19,872/呎
-(26年-05月-06日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="K12" s="22" t="inlineStr">
@@ -38503,7 +38503,7 @@
           <t>C | 329呎 (1房)
 $626万
 $19,015/呎
-(26年-05月-07日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="E13" s="22" t="inlineStr">
@@ -38519,7 +38519,7 @@
           <t>E | 320呎 (1房)
 $613万
 $19,156/呎
-(26年-04月-28日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="G13" s="20" t="inlineStr">
@@ -38527,7 +38527,7 @@
           <t>F | 320呎 (1房)
 $583万
 $18,219/呎
-(26年-03月-01日)</t>
+(26年-03月)</t>
         </is>
       </c>
       <c r="H13" s="20" t="inlineStr">
@@ -38535,7 +38535,7 @@
           <t>G | 250呎 (开放式)
 $473万
 $18,904/呎
-(26年-05月-06日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="I13" s="22" t="inlineStr">
@@ -38551,7 +38551,7 @@
           <t>J | 414呎 (2房)
 $820万
 $19,819/呎
-(26年-05月-06日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="K13" s="22" t="inlineStr">
@@ -38582,7 +38582,7 @@
           <t>B | 454呎 (2房)
 $962万
 $21,198/呎
-(26年-05月-06日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="D14" s="20" t="inlineStr">
@@ -38590,7 +38590,7 @@
           <t>C | 329呎 (1房)
 $624万
 $18,967/呎
-(26年-05月-06日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="E14" s="22" t="inlineStr">
@@ -38606,7 +38606,7 @@
           <t>E | 320呎 (1房)
 $611万
 $19,106/呎
-(26年-05月-03日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="G14" s="20" t="inlineStr">
@@ -38614,7 +38614,7 @@
           <t>F | 320呎 (1房)
 $582万
 $18,172/呎
-(26年-02月-22日)</t>
+(26年-02月)</t>
         </is>
       </c>
       <c r="H14" s="20" t="inlineStr">
@@ -38622,7 +38622,7 @@
           <t>G | 250呎 (开放式)
 $471万
 $18,852/呎
-(26年-05月-07日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="I14" s="22" t="inlineStr">
@@ -38638,7 +38638,7 @@
           <t>J | 414呎 (2房)
 $818万
 $19,771/呎
-(26年-05月-11日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="K14" s="22" t="inlineStr">
@@ -38756,7 +38756,7 @@
           <t>B | 454呎 (2房)
 $955万
 $21,040/呎
-(26年-05月-07日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="D16" s="20" t="inlineStr">
@@ -38764,7 +38764,7 @@
           <t>C | 329呎 (1房)
 $619万
 $18,827/呎
-(26年-05月-06日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="E16" s="22" t="inlineStr">
@@ -38780,7 +38780,7 @@
           <t>E | 320呎 (1房)
 $607万
 $18,966/呎
-(26年-05月-03日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="G16" s="20" t="inlineStr">
@@ -38788,7 +38788,7 @@
           <t>F | 320呎 (1房)
 $577万
 $18,038/呎
-(26年-02月-25日)</t>
+(26年-02月)</t>
         </is>
       </c>
       <c r="H16" s="20" t="inlineStr">
@@ -38796,7 +38796,7 @@
           <t>G | 250呎 (开放式)
 $468万
 $18,712/呎
-(26年-05月-11日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="I16" s="22" t="inlineStr">
@@ -38812,7 +38812,7 @@
           <t>J | 414呎 (2房)
 $812万
 $19,623/呎
-(26年-05月-06日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="K16" s="22" t="inlineStr">
@@ -38843,7 +38843,7 @@
           <t>B | 454呎 (2房)
 $953万
 $20,987/呎
-(26年-05月-12日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="D17" s="20" t="inlineStr">
@@ -38851,7 +38851,7 @@
           <t>C | 329呎 (1房)
 $618万
 $18,781/呎
-(26年-05月-06日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="E17" s="22" t="inlineStr">
@@ -38867,7 +38867,7 @@
           <t>E | 320呎 (1房)
 $579万
 $18,106/呎
-(26年-02月-23日)</t>
+(26年-02月)</t>
         </is>
       </c>
       <c r="G17" s="20" t="inlineStr">
@@ -38875,7 +38875,7 @@
           <t>F | 320呎 (1房)
 $576万
 $17,991/呎
-(26年-02月-24日)</t>
+(26年-02月)</t>
         </is>
       </c>
       <c r="H17" s="20" t="inlineStr">
@@ -38883,7 +38883,7 @@
           <t>G | 250呎 (开放式)
 $467万
 $18,668/呎
-(26年-05月-17日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="I17" s="22" t="inlineStr">
@@ -38899,7 +38899,7 @@
           <t>J | 414呎 (2房)
 $810万
 $19,575/呎
-(26年-05月-06日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="K17" s="22" t="inlineStr">
@@ -38930,7 +38930,7 @@
           <t>B | 454呎 (2房)
 $961万
 $21,172/呎
-(26年-05月-18日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="D18" s="20" t="inlineStr">
@@ -38938,7 +38938,7 @@
           <t>C | 329呎 (1房)
 $616万
 $18,733/呎
-(26年-05月-06日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="E18" s="22" t="inlineStr">
@@ -38954,7 +38954,7 @@
           <t>E | 320呎 (1房)
 $604万
 $18,872/呎
-(26年-04月-28日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="G18" s="20" t="inlineStr">
@@ -38962,7 +38962,7 @@
           <t>F | 320呎 (1房)
 $574万
 $17,944/呎
-(26年-02月-12日)</t>
+(26年-02月)</t>
         </is>
       </c>
       <c r="H18" s="20" t="inlineStr">
@@ -38970,7 +38970,7 @@
           <t>G | 250呎 (开放式)
 $471万
 $18,828/呎
-(26年-05月-14日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="I18" s="22" t="inlineStr">
@@ -38986,7 +38986,7 @@
           <t>J | 414呎 (2房)
 $817万
 $19,744/呎
-(26年-05月-11日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="K18" s="22" t="inlineStr">
@@ -39017,7 +39017,7 @@
           <t>B | 454呎 (2房)
 $959万
 $21,117/呎
-(26年-05月-17日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="D19" s="20" t="inlineStr">
@@ -39025,7 +39025,7 @@
           <t>C | 329呎 (1房)
 $615万
 $18,687/呎
-(26年-05月-06日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="E19" s="22" t="inlineStr">
@@ -39041,7 +39041,7 @@
           <t>E | 320呎 (1房)
 $602万
 $18,825/呎
-(26年-05月-03日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="G19" s="20" t="inlineStr">
@@ -39049,7 +39049,7 @@
           <t>F | 320呎 (1房)
 $573万
 $17,900/呎
-(26年-02月-04日)</t>
+(26年-02月)</t>
         </is>
       </c>
       <c r="H19" s="20" t="inlineStr">
@@ -39057,7 +39057,7 @@
           <t>G | 250呎 (开放式)
 $475万
 $18,992/呎
-(26年-05月-18日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="I19" s="22" t="inlineStr">
@@ -39073,7 +39073,7 @@
           <t>J | 414呎 (2房)
 $815万
 $19,696/呎
-(26年-05月-18日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="K19" s="22" t="inlineStr">
@@ -39104,7 +39104,7 @@
           <t>B | 454呎 (2房)
 $946万
 $20,830/呎
-(26年-05月-07日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="D20" s="20" t="inlineStr">
@@ -39112,7 +39112,7 @@
           <t>C | 329呎 (1房)
 $613万
 $18,641/呎
-(26年-05月-06日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="E20" s="22" t="inlineStr">
@@ -39128,7 +39128,7 @@
           <t>E | 320呎 (1房)
 $601万
 $18,775/呎
-(26年-05月-03日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="G20" s="20" t="inlineStr">
@@ -39136,7 +39136,7 @@
           <t>F | 320呎 (1房)
 $571万
 $17,856/呎
-(26年-02月-01日)</t>
+(26年-02月)</t>
         </is>
       </c>
       <c r="H20" s="20" t="inlineStr">
@@ -39144,7 +39144,7 @@
           <t>G | 250呎 (开放式)
 $468万
 $18,736/呎
-(26年-05月-07日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="I20" s="22" t="inlineStr">
@@ -39160,7 +39160,7 @@
           <t>J | 414呎 (2房)
 $804万
 $19,428/呎
-(26年-05月-07日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="K20" s="22" t="inlineStr">
@@ -39191,7 +39191,7 @@
           <t>B | 454呎 (2房)
 $943万
 $20,780/呎
-(26年-05月-07日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="D21" s="20" t="inlineStr">
@@ -39199,7 +39199,7 @@
           <t>C | 329呎 (1房)
 $612万
 $18,593/呎
-(26年-05月-06日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="E21" s="22" t="inlineStr">
@@ -39215,7 +39215,7 @@
           <t>E | 320呎 (1房)
 $599万
 $18,728/呎
-(26年-05月-03日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="G21" s="20" t="inlineStr">
@@ -39223,7 +39223,7 @@
           <t>F | 320呎 (1房)
 $570万
 $17,812/呎
-(26年-01月-22日)</t>
+(26年-01月)</t>
         </is>
       </c>
       <c r="H21" s="20" t="inlineStr">
@@ -39231,7 +39231,7 @@
           <t>G | 250呎 (开放式)
 $462万
 $18,480/呎
-(26年-05月-10日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="I21" s="22" t="inlineStr">
@@ -39247,7 +39247,7 @@
           <t>J | 414呎 (2房)
 $811万
 $19,599/呎
-(26年-05月-12日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="K21" s="22" t="inlineStr">
@@ -39278,7 +39278,7 @@
           <t>B | 454呎 (2房)
 $923万
 $20,322/呎
-(26年-03月-02日)</t>
+(26年-03月)</t>
         </is>
       </c>
       <c r="D22" s="20" t="inlineStr">
@@ -39286,7 +39286,7 @@
           <t>C | 329呎 (1房)
 $610万
 $18,547/呎
-(26年-05月-06日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="E22" s="22" t="inlineStr">
@@ -39302,7 +39302,7 @@
           <t>E | 320呎 (1房)
 $566万
 $17,678/呎
-(26年-02月-12日)</t>
+(26年-02月)</t>
         </is>
       </c>
       <c r="G22" s="20" t="inlineStr">
@@ -39310,7 +39310,7 @@
           <t>F | 320呎 (1房)
 $568万
 $17,766/呎
-(26年-02月-03日)</t>
+(26年-02月)</t>
         </is>
       </c>
       <c r="H22" s="20" t="inlineStr">
@@ -39318,7 +39318,7 @@
           <t>G | 250呎 (开放式)
 $461万
 $18,436/呎
-(26年-05月-07日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="I22" s="22" t="inlineStr">
@@ -39334,7 +39334,7 @@
           <t>J | 414呎 (2房)
 $800万
 $19,331/呎
-(26年-05月-10日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="K22" s="22" t="inlineStr">
@@ -39365,7 +39365,7 @@
           <t>B | 454呎 (2房)
 $931万
 $20,500/呎
-(26年-03月-04日)</t>
+(26年-03月)</t>
         </is>
       </c>
       <c r="D23" s="20" t="inlineStr">
@@ -39373,7 +39373,7 @@
           <t>C | 329呎 (1房)
 $609万
 $18,498/呎
-(26年-05月-06日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="E23" s="22" t="inlineStr">
@@ -39389,7 +39389,7 @@
           <t>E | 320呎 (1房)
 $564万
 $17,634/呎
-(26年-01月-07日)</t>
+(26年-01月)</t>
         </is>
       </c>
       <c r="G23" s="20" t="inlineStr">
@@ -39397,7 +39397,7 @@
           <t>F | 320呎 (1房)
 $567万
 $17,722/呎
-(26年-02月-05日)</t>
+(26年-02月)</t>
         </is>
       </c>
       <c r="H23" s="20" t="inlineStr">
@@ -39405,7 +39405,7 @@
           <t>G | 250呎 (开放式)
 $465万
 $18,596/呎
-(26年-05月-06日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="I23" s="22" t="inlineStr">
@@ -39421,7 +39421,7 @@
           <t>J | 414呎 (2房)
 $798万
 $19,285/呎
-(26年-05月-05日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="K23" s="22" t="inlineStr">
@@ -39452,7 +39452,7 @@
           <t>B | 454呎 (2房)
 $918万
 $20,220/呎
-(26年-02月-25日)</t>
+(26年-02月)</t>
         </is>
       </c>
       <c r="D24" s="20" t="inlineStr">
@@ -39460,7 +39460,7 @@
           <t>C | 329呎 (1房)
 $607万
 $18,453/呎
-(26年-05月-05日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="E24" s="22" t="inlineStr">
@@ -39476,7 +39476,7 @@
           <t>E | 320呎 (1房)
 $563万
 $17,591/呎
-(26年-01月-12日)</t>
+(26年-01月)</t>
         </is>
       </c>
       <c r="G24" s="20" t="inlineStr">
@@ -39484,7 +39484,7 @@
           <t>F | 320呎 (1房)
 $566万
 $17,678/呎
-(26年-02月-05日)</t>
+(26年-02月)</t>
         </is>
       </c>
       <c r="H24" s="20" t="inlineStr">
@@ -39492,7 +39492,7 @@
           <t>G | 250呎 (开放式)
 $459万
 $18,344/呎
-(26年-05月-05日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="I24" s="22" t="inlineStr">
@@ -39508,7 +39508,7 @@
           <t>J | 414呎 (2房)
 $796万
 $19,234/呎
-(26年-05月-14日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="K24" s="22" t="inlineStr">
@@ -39539,7 +39539,7 @@
           <t>B | 454呎 (2房)
 $913万
 $20,119/呎
-(26年-03月-01日)</t>
+(26年-03月)</t>
         </is>
       </c>
       <c r="D25" s="20" t="inlineStr">
@@ -39547,7 +39547,7 @@
           <t>C | 329呎 (1房)
 $604万
 $18,362/呎
-(26年-05月-06日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="E25" s="22" t="inlineStr">
@@ -39563,7 +39563,7 @@
           <t>E | 320呎 (1房)
 $560万
 $17,503/呎
-(26年-01月-08日)</t>
+(26年-01月)</t>
         </is>
       </c>
       <c r="G25" s="20" t="inlineStr">
@@ -39571,7 +39571,7 @@
           <t>F | 320呎 (1房)
 $563万
 $17,591/呎
-(26年-02月-15日)</t>
+(26年-02月)</t>
         </is>
       </c>
       <c r="H25" s="20" t="inlineStr">
@@ -39579,7 +39579,7 @@
           <t>G | 250呎 (开放式)
 $426万
 $17,056/呎
-(26年-01月-08日)</t>
+(26年-01月)</t>
         </is>
       </c>
       <c r="I25" s="22" t="inlineStr">
@@ -39595,7 +39595,7 @@
           <t>J | 414呎 (2房)
 $792万
 $19,140/呎
-(26年-05月-07日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="K25" s="22" t="inlineStr">
@@ -39626,7 +39626,7 @@
           <t>B | 454呎 (2房)
 $911万
 $20,068/呎
-(26年-02月-10日)</t>
+(26年-02月)</t>
         </is>
       </c>
       <c r="D26" s="20" t="inlineStr">
@@ -39634,7 +39634,7 @@
           <t>C | 329呎 (1房)
 $603万
 $18,319/呎
-(26年-05月-06日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="E26" s="22" t="inlineStr">
@@ -39650,7 +39650,7 @@
           <t>E | 320呎 (1房)
 $559万
 $17,462/呎
-(26年-01月-08日)</t>
+(26年-01月)</t>
         </is>
       </c>
       <c r="G26" s="20" t="inlineStr">
@@ -39658,7 +39658,7 @@
           <t>F | 320呎 (1房)
 $562万
 $17,547/呎
-(26年-02月-05日)</t>
+(26年-02月)</t>
         </is>
       </c>
       <c r="H26" s="20" t="inlineStr">
@@ -39666,7 +39666,7 @@
           <t>G | 250呎 (开放式)
 $425万
 $17,016/呎
-(26年-01月-08日)</t>
+(26年-01月)</t>
         </is>
       </c>
       <c r="I26" s="22" t="inlineStr">
@@ -39682,7 +39682,7 @@
           <t>J | 414呎 (2房)
 $790万
 $19,094/呎
-(26年-05月-05日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="K26" s="22" t="inlineStr">
@@ -39713,7 +39713,7 @@
           <t>B | 454呎 (2房)
 $909万
 $20,018/呎
-(26年-02月-04日)</t>
+(26年-02月)</t>
         </is>
       </c>
       <c r="D27" s="20" t="inlineStr">
@@ -39721,7 +39721,7 @@
           <t>C | 329呎 (1房)
 $601万
 $18,274/呎
-(26年-05月-06日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="E27" s="22" t="inlineStr">
@@ -39737,7 +39737,7 @@
           <t>E | 320呎 (1房)
 $557万
 $17,419/呎
-(26年-01月-08日)</t>
+(26年-01月)</t>
         </is>
       </c>
       <c r="G27" s="20" t="inlineStr">
@@ -39745,7 +39745,7 @@
           <t>F | 320呎 (1房)
 $560万
 $17,503/呎
-(26年-01月-25日)</t>
+(26年-01月)</t>
         </is>
       </c>
       <c r="H27" s="20" t="inlineStr">
@@ -39753,7 +39753,7 @@
           <t>G | 250呎 (开放式)
 $424万
 $16,972/呎
-(26年-01月-13日)</t>
+(26年-01月)</t>
         </is>
       </c>
       <c r="I27" s="22" t="inlineStr">
@@ -39769,7 +39769,7 @@
           <t>J | 414呎 (2房)
 $744万
 $17,966/呎
-(26年-01月-13日)</t>
+(26年-01月)</t>
         </is>
       </c>
       <c r="K27" s="22" t="inlineStr">
@@ -39800,7 +39800,7 @@
           <t>B | 454呎 (2房)
 $906万
 $19,967/呎
-(26年-03月-01日)</t>
+(26年-03月)</t>
         </is>
       </c>
       <c r="D28" s="20" t="inlineStr">
@@ -39808,7 +39808,7 @@
           <t>C | 329呎 (1房)
 $606万
 $18,432/呎
-(26年-05月-07日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="E28" s="22" t="inlineStr">
@@ -39824,7 +39824,7 @@
           <t>E | 320呎 (1房)
 $556万
 $17,372/呎
-(26年-01月-11日)</t>
+(26年-01月)</t>
         </is>
       </c>
       <c r="G28" s="20" t="inlineStr">
@@ -39832,7 +39832,7 @@
           <t>F | 320呎 (1房)
 $559万
 $17,459/呎
-(26年-02月-12日)</t>
+(26年-02月)</t>
         </is>
       </c>
       <c r="H28" s="20" t="inlineStr">
@@ -39840,7 +39840,7 @@
           <t>G | 250呎 (开放式)
 $442万
 $17,700/呎
-(26年-01月-08日)</t>
+(26年-01月)</t>
         </is>
       </c>
       <c r="I28" s="22" t="inlineStr">
@@ -39856,7 +39856,7 @@
           <t>J | 414呎 (2房)
 $776万
 $18,737/呎
-(26年-01月-08日)</t>
+(26年-01月)</t>
         </is>
       </c>
       <c r="K28" s="22" t="inlineStr">
@@ -39887,7 +39887,7 @@
           <t>B | 454呎 (2房)
 $904万
 $19,919/呎
-(26年-03月-01日)</t>
+(26年-03月)</t>
         </is>
       </c>
       <c r="D29" s="20" t="inlineStr">
@@ -39895,7 +39895,7 @@
           <t>C | 329呎 (1房)
 $598万
 $18,179/呎
-(26年-05月-06日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="E29" s="22" t="inlineStr">
@@ -39911,7 +39911,7 @@
           <t>E | 320呎 (1房)
 $554万
 $17,328/呎
-(26年-01月-08日)</t>
+(26年-01月)</t>
         </is>
       </c>
       <c r="G29" s="20" t="inlineStr">
@@ -39919,7 +39919,7 @@
           <t>F | 320呎 (1房)
 $557万
 $17,419/呎
-(26年-02月-12日)</t>
+(26年-02月)</t>
         </is>
       </c>
       <c r="H29" s="20" t="inlineStr">
@@ -39927,7 +39927,7 @@
           <t>G | 250呎 (开放式)
 $422万
 $16,888/呎
-(26年-01月-08日)</t>
+(26年-01月)</t>
         </is>
       </c>
       <c r="I29" s="22" t="inlineStr">
@@ -39943,7 +39943,7 @@
           <t>J | 414呎 (2房)
 $774万
 $18,691/呎
-(26年-01月-08日)</t>
+(26年-01月)</t>
         </is>
       </c>
       <c r="K29" s="22" t="inlineStr">
@@ -39974,7 +39974,7 @@
           <t>B | 454呎 (2房)
 $902万
 $19,868/呎
-(26年-01月-13日)</t>
+(26年-01月)</t>
         </is>
       </c>
       <c r="D30" s="20" t="inlineStr">
@@ -39982,7 +39982,7 @@
           <t>C | 329呎 (1房)
 $597万
 $18,134/呎
-(26年-05月-05日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="E30" s="22" t="inlineStr">
@@ -39998,7 +39998,7 @@
           <t>E | 320呎 (1房)
 $553万
 $17,284/呎
-(26年-01月-18日)</t>
+(26年-01月)</t>
         </is>
       </c>
       <c r="G30" s="20" t="inlineStr">
@@ -40006,7 +40006,7 @@
           <t>F | 320呎 (1房)
 $556万
 $17,372/呎
-(26年-02月-23日)</t>
+(26年-02月)</t>
         </is>
       </c>
       <c r="H30" s="20" t="inlineStr">
@@ -40014,7 +40014,7 @@
           <t>G | 250呎 (开放式)
 $421万
 $16,844/呎
-(26年-01月-07日)</t>
+(26年-01月)</t>
         </is>
       </c>
       <c r="I30" s="22" t="inlineStr">
@@ -40030,7 +40030,7 @@
           <t>J | 414呎 (2房)
 $738万
 $17,833/呎
-(26年-01月-06日)</t>
+(26年-01月)</t>
         </is>
       </c>
       <c r="K30" s="22" t="inlineStr">
@@ -40061,7 +40061,7 @@
           <t>B | 454呎 (2房)
 $900万
 $19,819/呎
-(26年-02月-25日)</t>
+(26年-02月)</t>
         </is>
       </c>
       <c r="D31" s="20" t="inlineStr">
@@ -40069,7 +40069,7 @@
           <t>C | 329呎 (1房)
 $595万
 $18,091/呎
-(26年-05月-05日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="E31" s="22" t="inlineStr">
@@ -40085,7 +40085,7 @@
           <t>E | 320呎 (1房)
 $577万
 $18,028/呎
-(26年-01月-12日)</t>
+(26年-01月)</t>
         </is>
       </c>
       <c r="G31" s="20" t="inlineStr">
@@ -40093,7 +40093,7 @@
           <t>F | 320呎 (1房)
 $561万
 $17,525/呎
-(26年-01月-25日)</t>
+(26年-01月)</t>
         </is>
       </c>
       <c r="H31" s="20" t="inlineStr">
@@ -40101,7 +40101,7 @@
           <t>G | 250呎 (开放式)
 $420万
 $16,804/呎
-(26年-01月-08日)</t>
+(26年-01月)</t>
         </is>
       </c>
       <c r="I31" s="22" t="inlineStr">
@@ -40117,7 +40117,7 @@
           <t>J | 414呎 (2房)
 $736万
 $17,787/呎
-(25年-12月-13日)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="K31" s="22" t="inlineStr">
@@ -40148,7 +40148,7 @@
           <t>B | 454呎 (2房)
 $908万
 $19,996/呎
-(26年-03月-15日)</t>
+(26年-03月)</t>
         </is>
       </c>
       <c r="D32" s="20" t="inlineStr">
@@ -40156,7 +40156,7 @@
           <t>C | 329呎 (1房)
 $594万
 $18,046/呎
-(26年-05月-06日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="E32" s="22" t="inlineStr">
@@ -40172,7 +40172,7 @@
           <t>E | 320呎 (1房)
 $582万
 $18,178/呎
-(26年-04月-22日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="G32" s="20" t="inlineStr">
@@ -40180,7 +40180,7 @@
           <t>F | 320呎 (1房)
 $553万
 $17,284/呎
-(26年-02月-10日)</t>
+(26年-02月)</t>
         </is>
       </c>
       <c r="H32" s="20" t="inlineStr">
@@ -40188,7 +40188,7 @@
           <t>G | 250呎 (开放式)
 $419万
 $16,764/呎
-(26年-01月-13日)</t>
+(26年-01月)</t>
         </is>
       </c>
       <c r="I32" s="22" t="inlineStr">
@@ -40204,7 +40204,7 @@
           <t>J | 414呎 (2房)
 $735万
 $17,744/呎
-(26年-01月-06日)</t>
+(26年-01月)</t>
         </is>
       </c>
       <c r="K32" s="22" t="inlineStr">
@@ -40235,7 +40235,7 @@
           <t>B | 454呎 (2房)
 $903万
 $19,894/呎
-(26年-03月-16日)</t>
+(26年-03月)</t>
         </is>
       </c>
       <c r="D33" s="20" t="inlineStr">
@@ -40243,7 +40243,7 @@
           <t>C | 329呎 (1房)
 $596万
 $18,106/呎
-(26年-05月-18日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="E33" s="22" t="inlineStr">
@@ -40267,7 +40267,7 @@
           <t>F | 320呎 (1房)
 $548万
 $17,116/呎
-(26年-02月-24日)</t>
+(26年-02月)</t>
         </is>
       </c>
       <c r="H33" s="20" t="inlineStr">
@@ -40275,7 +40275,7 @@
           <t>G | 250呎 (开放式)
 $451万
 $18,044/呎
-(26年-05月-14日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="I33" s="22" t="inlineStr">
@@ -40291,7 +40291,7 @@
           <t>J | 414呎 (2房)
 $731万
 $17,657/呎
-(26年-01月-07日)</t>
+(26年-01月)</t>
         </is>
       </c>
       <c r="K33" s="22" t="inlineStr">
@@ -40322,7 +40322,7 @@
           <t>B | 454呎 (2房)
 $919万
 $20,240/呎
-(26年-05月-17日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="D34" s="20" t="inlineStr">
@@ -40330,7 +40330,7 @@
           <t>C | 329呎 (1房)
 $594万
 $18,061/呎
-(26年-05月-18日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="E34" s="22" t="inlineStr">
@@ -40346,7 +40346,7 @@
           <t>E | 320呎 (1房)
 $546万
 $17,075/呎
-(26年-01月-14日)</t>
+(26年-01月)</t>
         </is>
       </c>
       <c r="G34" s="24" t="inlineStr">
@@ -40362,7 +40362,7 @@
           <t>G | 250呎 (开放式)
 $450万
 $18,000/呎
-(26年-05月-17日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="I34" s="22" t="inlineStr">
@@ -40378,7 +40378,7 @@
           <t>J | 414呎 (2房)
 $782万
 $18,877/呎
-(26年-05月-17日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="K34" s="22" t="inlineStr">

--- a/files/九龙-启德-Double Coast III.xlsx
+++ b/files/九龙-启德-Double Coast III.xlsx
@@ -35838,7 +35838,7 @@
           <t>A | 1378呎 (4+房)
 $4668万
 $33,877/呎
-(26年-04月)</t>
+(26年-04月-07日)</t>
         </is>
       </c>
       <c r="C5" s="21" t="inlineStr"/>
@@ -36256,7 +36256,7 @@
           <t>F | 431呎 (2房)
 $791万
 $18,346/呎
-(26年-05月)</t>
+(26年-05月-05日)</t>
         </is>
       </c>
     </row>
@@ -36279,7 +36279,7 @@
           <t>B | 695呎 (3房)
 $1631万
 $23,471/呎
-(26年-04月)</t>
+(26年-04月-26日)</t>
         </is>
       </c>
       <c r="D13" s="22" t="inlineStr">
@@ -36311,7 +36311,7 @@
           <t>F | 431呎 (2房)
 $789万
 $18,302/呎
-(26年-05月)</t>
+(26年-05月-06日)</t>
         </is>
       </c>
     </row>
@@ -36358,7 +36358,7 @@
           <t>E | 429呎 (2房)
 $800万
 $18,653/呎
-(26年-05月)</t>
+(26年-05月-05日)</t>
         </is>
       </c>
       <c r="G14" s="20" t="inlineStr">
@@ -36366,7 +36366,7 @@
           <t>F | 431呎 (2房)
 $796万
 $18,459/呎
-(26年-05月)</t>
+(26年-05月-06日)</t>
         </is>
       </c>
     </row>
@@ -36468,7 +36468,7 @@
           <t>E | 429呎 (2房)
 $794万
 $18,513/呎
-(26年-05月)</t>
+(26年-05月-07日)</t>
         </is>
       </c>
       <c r="G16" s="20" t="inlineStr">
@@ -36476,7 +36476,7 @@
           <t>F | 431呎 (2房)
 $790万
 $18,323/呎
-(26年-05月)</t>
+(26年-05月-06日)</t>
         </is>
       </c>
     </row>
@@ -36499,7 +36499,7 @@
           <t>B | 695呎 (3房)
 $1558万
 $22,416/呎
-(26年-01月)</t>
+(26年-01月-29日)</t>
         </is>
       </c>
       <c r="D17" s="22" t="inlineStr">
@@ -36523,7 +36523,7 @@
           <t>E | 429呎 (2房)
 $792万
 $18,466/呎
-(26年-05月)</t>
+(26年-05月-06日)</t>
         </is>
       </c>
       <c r="G17" s="20" t="inlineStr">
@@ -36531,7 +36531,7 @@
           <t>F | 431呎 (2房)
 $788万
 $18,276/呎
-(26年-05月)</t>
+(26年-05月-05日)</t>
         </is>
       </c>
     </row>
@@ -36578,7 +36578,7 @@
           <t>E | 429呎 (2房)
 $790万
 $18,420/呎
-(26年-05月)</t>
+(26年-05月-06日)</t>
         </is>
       </c>
       <c r="G18" s="20" t="inlineStr">
@@ -36586,7 +36586,7 @@
           <t>F | 431呎 (2房)
 $786万
 $18,230/呎
-(26年-05月)</t>
+(26年-05月-17日)</t>
         </is>
       </c>
     </row>
@@ -36609,7 +36609,7 @@
           <t>B | 695呎 (3房)
 $1550万
 $22,304/呎
-(26年-02月)</t>
+(26年-02月-09日)</t>
         </is>
       </c>
       <c r="D19" s="22" t="inlineStr">
@@ -36633,7 +36633,7 @@
           <t>E | 429呎 (2房)
 $788万
 $18,373/呎
-(26年-05月)</t>
+(26年-05月-06日)</t>
         </is>
       </c>
       <c r="G19" s="20" t="inlineStr">
@@ -36641,7 +36641,7 @@
           <t>F | 431呎 (2房)
 $792万
 $18,387/呎
-(26年-05月)</t>
+(26年-05月-14日)</t>
         </is>
       </c>
     </row>
@@ -36664,7 +36664,7 @@
           <t>B | 695呎 (3房)
 $1546万
 $22,249/呎
-(26年-02月)</t>
+(26年-02月-25日)</t>
         </is>
       </c>
       <c r="D20" s="22" t="inlineStr">
@@ -36688,7 +36688,7 @@
           <t>E | 429呎 (2房)
 $786万
 $18,329/呎
-(26年-05月)</t>
+(26年-05月-06日)</t>
         </is>
       </c>
       <c r="G20" s="20" t="inlineStr">
@@ -36696,7 +36696,7 @@
           <t>F | 431呎 (2房)
 $782万
 $18,139/呎
-(26年-05月)</t>
+(26年-05月-05日)</t>
         </is>
       </c>
     </row>
@@ -36711,7 +36711,7 @@
           <t>A | 640呎 (3房)
 $1444万
 $22,564/呎
-(26年-05月)</t>
+(26年-05月-18日)</t>
         </is>
       </c>
       <c r="C21" s="20" t="inlineStr">
@@ -36719,7 +36719,7 @@
           <t>B | 695呎 (3房)
 $1542万
 $22,193/呎
-(26年-03月)</t>
+(26年-03月-02日)</t>
         </is>
       </c>
       <c r="D21" s="22" t="inlineStr">
@@ -36743,7 +36743,7 @@
           <t>E | 429呎 (2房)
 $784万
 $18,282/呎
-(26年-05月)</t>
+(26年-05月-06日)</t>
         </is>
       </c>
       <c r="G21" s="20" t="inlineStr">
@@ -36751,7 +36751,7 @@
           <t>F | 431呎 (2房)
 $780万
 $18,095/呎
-(26年-05月)</t>
+(26年-05月-05日)</t>
         </is>
       </c>
     </row>
@@ -36766,7 +36766,7 @@
           <t>A | 640呎 (3房)
 $1432万
 $22,383/呎
-(26年-05月)</t>
+(26年-05月-05日)</t>
         </is>
       </c>
       <c r="C22" s="20" t="inlineStr">
@@ -36774,7 +36774,7 @@
           <t>B | 695呎 (3房)
 $1556万
 $22,388/呎
-(26年-01月)</t>
+(26年-01月-20日)</t>
         </is>
       </c>
       <c r="D22" s="22" t="inlineStr">
@@ -36798,7 +36798,7 @@
           <t>E | 429呎 (2房)
 $782万
 $18,238/呎
-(26年-05月)</t>
+(26年-05月-06日)</t>
         </is>
       </c>
       <c r="G22" s="20" t="inlineStr">
@@ -36806,7 +36806,7 @@
           <t>F | 431呎 (2房)
 $769万
 $17,849/呎
-(26年-05月)</t>
+(26年-05月-05日)</t>
         </is>
       </c>
     </row>
@@ -36821,7 +36821,7 @@
           <t>A | 640呎 (3房)
 $1429万
 $22,327/呎
-(26年-05月)</t>
+(26年-05月-06日)</t>
         </is>
       </c>
       <c r="C23" s="20" t="inlineStr">
@@ -36829,7 +36829,7 @@
           <t>B | 695呎 (3房)
 $1604万
 $23,085/呎
-(26年-01月)</t>
+(26年-01月-07日)</t>
         </is>
       </c>
       <c r="D23" s="22" t="inlineStr">
@@ -36853,7 +36853,7 @@
           <t>E | 429呎 (2房)
 $780万
 $18,191/呎
-(26年-05月)</t>
+(26年-05月-11日)</t>
         </is>
       </c>
       <c r="G23" s="20" t="inlineStr">
@@ -36861,7 +36861,7 @@
           <t>F | 431呎 (2房)
 $776万
 $18,005/呎
-(26年-05月)</t>
+(26年-05月-12日)</t>
         </is>
       </c>
     </row>
@@ -36876,7 +36876,7 @@
           <t>A | 640呎 (3房)
 $1433万
 $22,397/呎
-(26年-05月)</t>
+(26年-05月-20日)</t>
         </is>
       </c>
       <c r="C24" s="20" t="inlineStr">
@@ -36884,7 +36884,7 @@
           <t>B | 695呎 (3房)
 $1531万
 $22,027/呎
-(26年-03月)</t>
+(26年-03月-03日)</t>
         </is>
       </c>
       <c r="D24" s="22" t="inlineStr">
@@ -36908,7 +36908,7 @@
           <t>E | 429呎 (2房)
 $787万
 $18,350/呎
-(26年-05月)</t>
+(26年-05月-17日)</t>
         </is>
       </c>
       <c r="G24" s="20" t="inlineStr">
@@ -36916,7 +36916,7 @@
           <t>F | 431呎 (2房)
 $729万
 $16,914/呎
-(26年-01月)</t>
+(26年-01月-05日)</t>
         </is>
       </c>
     </row>
@@ -36931,7 +36931,7 @@
           <t>A | 640呎 (3房)
 $1426万
 $22,284/呎
-(26年-05月)</t>
+(26年-05月-17日)</t>
         </is>
       </c>
       <c r="C25" s="20" t="inlineStr">
@@ -36939,7 +36939,7 @@
           <t>B | 695呎 (3房)
 $1523万
 $21,917/呎
-(26年-02月)</t>
+(26年-02月-22日)</t>
         </is>
       </c>
       <c r="D25" s="22" t="inlineStr">
@@ -36963,7 +36963,7 @@
           <t>E | 429呎 (2房)
 $783万
 $18,259/呎
-(26年-05月)</t>
+(26年-05月-14日)</t>
         </is>
       </c>
       <c r="G25" s="20" t="inlineStr">
@@ -36971,7 +36971,7 @@
           <t>F | 431呎 (2房)
 $725万
 $16,828/呎
-(26年-01月)</t>
+(26年-01月-07日)</t>
         </is>
       </c>
     </row>
@@ -36986,7 +36986,7 @@
           <t>A | 640呎 (3房)
 $1415万
 $22,105/呎
-(26年-05月)</t>
+(26年-05月-06日)</t>
         </is>
       </c>
       <c r="C26" s="20" t="inlineStr">
@@ -36994,7 +36994,7 @@
           <t>B | 695呎 (3房)
 $1520万
 $21,863/呎
-(26年-03月)</t>
+(26年-03月-01日)</t>
         </is>
       </c>
       <c r="D26" s="22" t="inlineStr">
@@ -37018,7 +37018,7 @@
           <t>E | 429呎 (2房)
 $773万
 $18,012/呎
-(26年-05月)</t>
+(26年-05月-07日)</t>
         </is>
       </c>
       <c r="G26" s="20" t="inlineStr">
@@ -37026,7 +37026,7 @@
           <t>F | 431呎 (2房)
 $724万
 $16,789/呎
-(26年-01月)</t>
+(26年-01月-07日)</t>
         </is>
       </c>
     </row>
@@ -37041,7 +37041,7 @@
           <t>A | 640呎 (3房)
 $1357万
 $21,202/呎
-(26年-01月)</t>
+(26年-01月-13日)</t>
         </is>
       </c>
       <c r="C27" s="20" t="inlineStr">
@@ -37049,7 +37049,7 @@
           <t>B | 695呎 (3房)
 $1516万
 $21,809/呎
-(26年-01月)</t>
+(26年-01月-08日)</t>
         </is>
       </c>
       <c r="D27" s="22" t="inlineStr">
@@ -37073,7 +37073,7 @@
           <t>E | 429呎 (2房)
 $771万
 $17,967/呎
-(26年-05月)</t>
+(26年-05月-07日)</t>
         </is>
       </c>
       <c r="G27" s="20" t="inlineStr">
@@ -37081,7 +37081,7 @@
           <t>F | 431呎 (2房)
 $722万
 $16,745/呎
-(26年-01月)</t>
+(26年-01月-05日)</t>
         </is>
       </c>
     </row>
@@ -37096,7 +37096,7 @@
           <t>A | 640呎 (3房)
 $1416万
 $22,119/呎
-(26年-05月)</t>
+(26年-05月-20日)</t>
         </is>
       </c>
       <c r="C28" s="20" t="inlineStr">
@@ -37104,7 +37104,7 @@
           <t>B | 695呎 (3房)
 $1512万
 $21,754/呎
-(26年-01月)</t>
+(26年-01月-08日)</t>
         </is>
       </c>
       <c r="D28" s="22" t="inlineStr">
@@ -37128,7 +37128,7 @@
           <t>E | 429呎 (2房)
 $740万
 $17,261/呎
-(26年-01月)</t>
+(26年-01月-07日)</t>
         </is>
       </c>
       <c r="G28" s="20" t="inlineStr">
@@ -37136,7 +37136,7 @@
           <t>F | 431呎 (2房)
 $720万
 $16,705/呎
-(26年-01月)</t>
+(26年-01月-06日)</t>
         </is>
       </c>
     </row>
@@ -37151,7 +37151,7 @@
           <t>A | 640呎 (3房)
 $1404万
 $21,941/呎
-(26年-05月)</t>
+(26年-05月-07日)</t>
         </is>
       </c>
       <c r="C29" s="20" t="inlineStr">
@@ -37159,7 +37159,7 @@
           <t>B | 695呎 (3房)
 $1508万
 $21,699/呎
-(26年-02月)</t>
+(26年-02月-24日)</t>
         </is>
       </c>
       <c r="D29" s="22" t="inlineStr">
@@ -37183,7 +37183,7 @@
           <t>E | 429呎 (2房)
 $730万
 $17,026/呎
-(26年-01月)</t>
+(26年-01月-08日)</t>
         </is>
       </c>
       <c r="G29" s="20" t="inlineStr">
@@ -37191,7 +37191,7 @@
           <t>F | 431呎 (2房)
 $718万
 $16,661/呎
-(26年-01月)</t>
+(26年-01月-01日)</t>
         </is>
       </c>
     </row>
@@ -37206,7 +37206,7 @@
           <t>A | 640呎 (3房)
 $1401万
 $21,884/呎
-(26年-05月)</t>
+(26年-05月-12日)</t>
         </is>
       </c>
       <c r="C30" s="20" t="inlineStr">
@@ -37214,7 +37214,7 @@
           <t>B | 695呎 (3房)
 $1522万
 $21,892/呎
-(26年-02月)</t>
+(26年-02月-25日)</t>
         </is>
       </c>
       <c r="D30" s="22" t="inlineStr">
@@ -37238,7 +37238,7 @@
           <t>E | 429呎 (2房)
 $729万
 $16,984/呎
-(26年-01月)</t>
+(26年-01月-11日)</t>
         </is>
       </c>
       <c r="G30" s="20" t="inlineStr">
@@ -37246,7 +37246,7 @@
           <t>F | 431呎 (2房)
 $716万
 $16,622/呎
-(26年-01月)</t>
+(26年-01月-06日)</t>
         </is>
       </c>
     </row>
@@ -37261,7 +37261,7 @@
           <t>A | 640呎 (3房)
 $1397万
 $21,831/呎
-(26年-05月)</t>
+(26年-05月-05日)</t>
         </is>
       </c>
       <c r="C31" s="20" t="inlineStr">
@@ -37269,7 +37269,7 @@
           <t>B | 695呎 (3房)
 $1501万
 $21,591/呎
-(26年-01月)</t>
+(26年-01月-13日)</t>
         </is>
       </c>
       <c r="D31" s="22" t="inlineStr">
@@ -37293,7 +37293,7 @@
           <t>E | 429呎 (2房)
 $727万
 $16,942/呎
-(26年-01月)</t>
+(26年-01月-12日)</t>
         </is>
       </c>
       <c r="G31" s="20" t="inlineStr">
@@ -37301,7 +37301,7 @@
           <t>F | 431呎 (2房)
 $750万
 $17,408/呎
-(26年-05月)</t>
+(26年-05月-18日)</t>
         </is>
       </c>
     </row>
@@ -37316,7 +37316,7 @@
           <t>A | 640呎 (3房)
 $1340万
 $20,939/呎
-(26年-01月)</t>
+(26年-01月-14日)</t>
         </is>
       </c>
       <c r="C32" s="20" t="inlineStr">
@@ -37324,7 +37324,7 @@
           <t>B | 695呎 (3房)
 $1497万
 $21,538/呎
-(26年-01月)</t>
+(26年-01月-15日)</t>
         </is>
       </c>
       <c r="D32" s="22" t="inlineStr">
@@ -37348,7 +37348,7 @@
           <t>E | 429呎 (2房)
 $725万
 $16,897/呎
-(26年-01月)</t>
+(26年-01月-11日)</t>
         </is>
       </c>
       <c r="G32" s="20" t="inlineStr">
@@ -37356,7 +37356,7 @@
           <t>F | 431呎 (2房)
 $748万
 $17,367/呎
-(26年-05月)</t>
+(26年-05月-13日)</t>
         </is>
       </c>
     </row>
@@ -37379,7 +37379,7 @@
           <t>B | 695呎 (3房)
 $1557万
 $22,404/呎
-(26年-04月)</t>
+(26年-04月-21日)</t>
         </is>
       </c>
       <c r="D33" s="22" t="inlineStr">
@@ -37403,7 +37403,7 @@
           <t>E | 429呎 (2房)
 $766万
 $17,853/呎
-(26年-05月)</t>
+(26年-05月-19日)</t>
         </is>
       </c>
       <c r="G33" s="20" t="inlineStr">
@@ -37411,7 +37411,7 @@
           <t>F | 431呎 (2房)
 $753万
 $17,473/呎
-(26年-05月)</t>
+(26年-05月-18日)</t>
         </is>
       </c>
     </row>
@@ -37458,7 +37458,7 @@
           <t>E | 429呎 (2房)
 $756万
 $17,611/呎
-(26年-05月)</t>
+(26年-05月-11日)</t>
         </is>
       </c>
       <c r="G34" s="20" t="inlineStr">
@@ -37466,7 +37466,7 @@
           <t>F | 431呎 (2房)
 $743万
 $17,234/呎
-(26年-05月)</t>
+(26年-05月-14日)</t>
         </is>
       </c>
     </row>
@@ -38068,7 +38068,7 @@
           <t>C | 329呎 (1房)
 $639万
 $19,416/呎
-(26年-05月)</t>
+(26年-05月-18日)</t>
         </is>
       </c>
       <c r="E8" s="22" t="inlineStr">
@@ -38084,7 +38084,7 @@
           <t>E | 320呎 (1房)
 $622万
 $19,431/呎
-(26年-05月)</t>
+(26年-05月-14日)</t>
         </is>
       </c>
       <c r="G8" s="20" t="inlineStr">
@@ -38092,7 +38092,7 @@
           <t>F | 320呎 (1房)
 $620万
 $19,369/呎
-(26年-05月)</t>
+(26年-05月-05日)</t>
         </is>
       </c>
       <c r="H8" s="20" t="inlineStr">
@@ -38100,7 +38100,7 @@
           <t>G | 250呎 (开放式)
 $478万
 $19,136/呎
-(26年-05月)</t>
+(26年-05月-10日)</t>
         </is>
       </c>
       <c r="I8" s="22" t="inlineStr">
@@ -38155,7 +38155,7 @@
           <t>C | 329呎 (1房)
 $637万
 $19,368/呎
-(26年-05月)</t>
+(26年-05月-20日)</t>
         </is>
       </c>
       <c r="E9" s="22" t="inlineStr">
@@ -38171,7 +38171,7 @@
           <t>E | 320呎 (1房)
 $620万
 $19,384/呎
-(26年-05月)</t>
+(26年-05月-18日)</t>
         </is>
       </c>
       <c r="G9" s="20" t="inlineStr">
@@ -38179,7 +38179,7 @@
           <t>F | 320呎 (1房)
 $618万
 $19,319/呎
-(26年-05月)</t>
+(26年-05月-06日)</t>
         </is>
       </c>
       <c r="H9" s="20" t="inlineStr">
@@ -38187,7 +38187,7 @@
           <t>G | 250呎 (开放式)
 $477万
 $19,092/呎
-(26年-05月)</t>
+(26年-05月-10日)</t>
         </is>
       </c>
       <c r="I9" s="22" t="inlineStr">
@@ -38203,7 +38203,7 @@
           <t>J | 414呎 (2房)
 $829万
 $20,019/呎
-(26年-05月)</t>
+(26年-05月-12日)</t>
         </is>
       </c>
       <c r="K9" s="22" t="inlineStr">
@@ -38242,7 +38242,7 @@
           <t>C | 329呎 (1房)
 $643万
 $19,535/呎
-(26年-05月)</t>
+(26年-05月-20日)</t>
         </is>
       </c>
       <c r="E10" s="22" t="inlineStr">
@@ -38258,7 +38258,7 @@
           <t>E | 320呎 (1房)
 $619万
 $19,338/呎
-(26年-05月)</t>
+(26年-05月-18日)</t>
         </is>
       </c>
       <c r="G10" s="20" t="inlineStr">
@@ -38266,7 +38266,7 @@
           <t>F | 320呎 (1房)
 $622万
 $19,431/呎
-(26年-05月)</t>
+(26年-05月-14日)</t>
         </is>
       </c>
       <c r="H10" s="20" t="inlineStr">
@@ -38274,7 +38274,7 @@
           <t>G | 250呎 (开放式)
 $482万
 $19,260/呎
-(26年-05月)</t>
+(26年-05月-19日)</t>
         </is>
       </c>
       <c r="I10" s="22" t="inlineStr">
@@ -38290,7 +38290,7 @@
           <t>J | 414呎 (2房)
 $836万
 $20,196/呎
-(26年-05月)</t>
+(26年-05月-20日)</t>
         </is>
       </c>
       <c r="K10" s="22" t="inlineStr">
@@ -38329,7 +38329,7 @@
           <t>C | 329呎 (1房)
 $629万
 $19,109/呎
-(26年-05月)</t>
+(26年-05月-06日)</t>
         </is>
       </c>
       <c r="E11" s="22" t="inlineStr">
@@ -38345,7 +38345,7 @@
           <t>E | 320呎 (1房)
 $617万
 $19,291/呎
-(26年-05月)</t>
+(26年-05月-18日)</t>
         </is>
       </c>
       <c r="G11" s="20" t="inlineStr">
@@ -38353,7 +38353,7 @@
           <t>F | 320呎 (1房)
 $622万
 $19,438/呎
-(26年-04月)</t>
+(26年-04月-09日)</t>
         </is>
       </c>
       <c r="H11" s="20" t="inlineStr">
@@ -38361,7 +38361,7 @@
           <t>G | 250呎 (开放式)
 $475万
 $18,996/呎
-(26年-05月)</t>
+(26年-05月-06日)</t>
         </is>
       </c>
       <c r="I11" s="22" t="inlineStr">
@@ -38377,7 +38377,7 @@
           <t>J | 414呎 (2房)
 $825万
 $19,920/呎
-(26年-05月)</t>
+(26年-05月-07日)</t>
         </is>
       </c>
       <c r="K11" s="22" t="inlineStr">
@@ -38416,7 +38416,7 @@
           <t>C | 329呎 (1房)
 $627万
 $19,061/呎
-(26年-05月)</t>
+(26年-05月-07日)</t>
         </is>
       </c>
       <c r="E12" s="22" t="inlineStr">
@@ -38432,7 +38432,7 @@
           <t>E | 320呎 (1房)
 $616万
 $19,241/呎
-(26年-05月)</t>
+(26年-05月-18日)</t>
         </is>
       </c>
       <c r="G12" s="20" t="inlineStr">
@@ -38440,7 +38440,7 @@
           <t>F | 320呎 (1房)
 $614万
 $19,175/呎
-(26年-05月)</t>
+(26年-05月-05日)</t>
         </is>
       </c>
       <c r="H12" s="20" t="inlineStr">
@@ -38448,7 +38448,7 @@
           <t>G | 250呎 (开放式)
 $474万
 $18,948/呎
-(26年-05月)</t>
+(26年-05月-06日)</t>
         </is>
       </c>
       <c r="I12" s="22" t="inlineStr">
@@ -38464,7 +38464,7 @@
           <t>J | 414呎 (2房)
 $823万
 $19,872/呎
-(26年-05月)</t>
+(26年-05月-06日)</t>
         </is>
       </c>
       <c r="K12" s="22" t="inlineStr">
@@ -38503,7 +38503,7 @@
           <t>C | 329呎 (1房)
 $626万
 $19,015/呎
-(26年-05月)</t>
+(26年-05月-07日)</t>
         </is>
       </c>
       <c r="E13" s="22" t="inlineStr">
@@ -38519,7 +38519,7 @@
           <t>E | 320呎 (1房)
 $613万
 $19,156/呎
-(26年-04月)</t>
+(26年-04月-28日)</t>
         </is>
       </c>
       <c r="G13" s="20" t="inlineStr">
@@ -38527,7 +38527,7 @@
           <t>F | 320呎 (1房)
 $583万
 $18,219/呎
-(26年-03月)</t>
+(26年-03月-01日)</t>
         </is>
       </c>
       <c r="H13" s="20" t="inlineStr">
@@ -38535,7 +38535,7 @@
           <t>G | 250呎 (开放式)
 $473万
 $18,904/呎
-(26年-05月)</t>
+(26年-05月-06日)</t>
         </is>
       </c>
       <c r="I13" s="22" t="inlineStr">
@@ -38551,7 +38551,7 @@
           <t>J | 414呎 (2房)
 $820万
 $19,819/呎
-(26年-05月)</t>
+(26年-05月-06日)</t>
         </is>
       </c>
       <c r="K13" s="22" t="inlineStr">
@@ -38582,7 +38582,7 @@
           <t>B | 454呎 (2房)
 $962万
 $21,198/呎
-(26年-05月)</t>
+(26年-05月-06日)</t>
         </is>
       </c>
       <c r="D14" s="20" t="inlineStr">
@@ -38590,7 +38590,7 @@
           <t>C | 329呎 (1房)
 $624万
 $18,967/呎
-(26年-05月)</t>
+(26年-05月-06日)</t>
         </is>
       </c>
       <c r="E14" s="22" t="inlineStr">
@@ -38606,7 +38606,7 @@
           <t>E | 320呎 (1房)
 $611万
 $19,106/呎
-(26年-05月)</t>
+(26年-05月-03日)</t>
         </is>
       </c>
       <c r="G14" s="20" t="inlineStr">
@@ -38614,7 +38614,7 @@
           <t>F | 320呎 (1房)
 $582万
 $18,172/呎
-(26年-02月)</t>
+(26年-02月-22日)</t>
         </is>
       </c>
       <c r="H14" s="20" t="inlineStr">
@@ -38622,7 +38622,7 @@
           <t>G | 250呎 (开放式)
 $471万
 $18,852/呎
-(26年-05月)</t>
+(26年-05月-07日)</t>
         </is>
       </c>
       <c r="I14" s="22" t="inlineStr">
@@ -38638,7 +38638,7 @@
           <t>J | 414呎 (2房)
 $818万
 $19,771/呎
-(26年-05月)</t>
+(26年-05月-11日)</t>
         </is>
       </c>
       <c r="K14" s="22" t="inlineStr">
@@ -38756,7 +38756,7 @@
           <t>B | 454呎 (2房)
 $955万
 $21,040/呎
-(26年-05月)</t>
+(26年-05月-07日)</t>
         </is>
       </c>
       <c r="D16" s="20" t="inlineStr">
@@ -38764,7 +38764,7 @@
           <t>C | 329呎 (1房)
 $619万
 $18,827/呎
-(26年-05月)</t>
+(26年-05月-06日)</t>
         </is>
       </c>
       <c r="E16" s="22" t="inlineStr">
@@ -38780,7 +38780,7 @@
           <t>E | 320呎 (1房)
 $607万
 $18,966/呎
-(26年-05月)</t>
+(26年-05月-03日)</t>
         </is>
       </c>
       <c r="G16" s="20" t="inlineStr">
@@ -38788,7 +38788,7 @@
           <t>F | 320呎 (1房)
 $577万
 $18,038/呎
-(26年-02月)</t>
+(26年-02月-25日)</t>
         </is>
       </c>
       <c r="H16" s="20" t="inlineStr">
@@ -38796,7 +38796,7 @@
           <t>G | 250呎 (开放式)
 $468万
 $18,712/呎
-(26年-05月)</t>
+(26年-05月-11日)</t>
         </is>
       </c>
       <c r="I16" s="22" t="inlineStr">
@@ -38812,7 +38812,7 @@
           <t>J | 414呎 (2房)
 $812万
 $19,623/呎
-(26年-05月)</t>
+(26年-05月-06日)</t>
         </is>
       </c>
       <c r="K16" s="22" t="inlineStr">
@@ -38843,7 +38843,7 @@
           <t>B | 454呎 (2房)
 $953万
 $20,987/呎
-(26年-05月)</t>
+(26年-05月-12日)</t>
         </is>
       </c>
       <c r="D17" s="20" t="inlineStr">
@@ -38851,7 +38851,7 @@
           <t>C | 329呎 (1房)
 $618万
 $18,781/呎
-(26年-05月)</t>
+(26年-05月-06日)</t>
         </is>
       </c>
       <c r="E17" s="22" t="inlineStr">
@@ -38867,7 +38867,7 @@
           <t>E | 320呎 (1房)
 $579万
 $18,106/呎
-(26年-02月)</t>
+(26年-02月-23日)</t>
         </is>
       </c>
       <c r="G17" s="20" t="inlineStr">
@@ -38875,7 +38875,7 @@
           <t>F | 320呎 (1房)
 $576万
 $17,991/呎
-(26年-02月)</t>
+(26年-02月-24日)</t>
         </is>
       </c>
       <c r="H17" s="20" t="inlineStr">
@@ -38883,7 +38883,7 @@
           <t>G | 250呎 (开放式)
 $467万
 $18,668/呎
-(26年-05月)</t>
+(26年-05月-17日)</t>
         </is>
       </c>
       <c r="I17" s="22" t="inlineStr">
@@ -38899,7 +38899,7 @@
           <t>J | 414呎 (2房)
 $810万
 $19,575/呎
-(26年-05月)</t>
+(26年-05月-06日)</t>
         </is>
       </c>
       <c r="K17" s="22" t="inlineStr">
@@ -38930,7 +38930,7 @@
           <t>B | 454呎 (2房)
 $961万
 $21,172/呎
-(26年-05月)</t>
+(26年-05月-18日)</t>
         </is>
       </c>
       <c r="D18" s="20" t="inlineStr">
@@ -38938,7 +38938,7 @@
           <t>C | 329呎 (1房)
 $616万
 $18,733/呎
-(26年-05月)</t>
+(26年-05月-06日)</t>
         </is>
       </c>
       <c r="E18" s="22" t="inlineStr">
@@ -38954,7 +38954,7 @@
           <t>E | 320呎 (1房)
 $604万
 $18,872/呎
-(26年-04月)</t>
+(26年-04月-28日)</t>
         </is>
       </c>
       <c r="G18" s="20" t="inlineStr">
@@ -38962,7 +38962,7 @@
           <t>F | 320呎 (1房)
 $574万
 $17,944/呎
-(26年-02月)</t>
+(26年-02月-12日)</t>
         </is>
       </c>
       <c r="H18" s="20" t="inlineStr">
@@ -38970,7 +38970,7 @@
           <t>G | 250呎 (开放式)
 $471万
 $18,828/呎
-(26年-05月)</t>
+(26年-05月-14日)</t>
         </is>
       </c>
       <c r="I18" s="22" t="inlineStr">
@@ -38986,7 +38986,7 @@
           <t>J | 414呎 (2房)
 $817万
 $19,744/呎
-(26年-05月)</t>
+(26年-05月-11日)</t>
         </is>
       </c>
       <c r="K18" s="22" t="inlineStr">
@@ -39017,7 +39017,7 @@
           <t>B | 454呎 (2房)
 $959万
 $21,117/呎
-(26年-05月)</t>
+(26年-05月-17日)</t>
         </is>
       </c>
       <c r="D19" s="20" t="inlineStr">
@@ -39025,7 +39025,7 @@
           <t>C | 329呎 (1房)
 $615万
 $18,687/呎
-(26年-05月)</t>
+(26年-05月-06日)</t>
         </is>
       </c>
       <c r="E19" s="22" t="inlineStr">
@@ -39041,7 +39041,7 @@
           <t>E | 320呎 (1房)
 $602万
 $18,825/呎
-(26年-05月)</t>
+(26年-05月-03日)</t>
         </is>
       </c>
       <c r="G19" s="20" t="inlineStr">
@@ -39049,7 +39049,7 @@
           <t>F | 320呎 (1房)
 $573万
 $17,900/呎
-(26年-02月)</t>
+(26年-02月-04日)</t>
         </is>
       </c>
       <c r="H19" s="20" t="inlineStr">
@@ -39057,7 +39057,7 @@
           <t>G | 250呎 (开放式)
 $475万
 $18,992/呎
-(26年-05月)</t>
+(26年-05月-18日)</t>
         </is>
       </c>
       <c r="I19" s="22" t="inlineStr">
@@ -39073,7 +39073,7 @@
           <t>J | 414呎 (2房)
 $815万
 $19,696/呎
-(26年-05月)</t>
+(26年-05月-18日)</t>
         </is>
       </c>
       <c r="K19" s="22" t="inlineStr">
@@ -39104,7 +39104,7 @@
           <t>B | 454呎 (2房)
 $946万
 $20,830/呎
-(26年-05月)</t>
+(26年-05月-07日)</t>
         </is>
       </c>
       <c r="D20" s="20" t="inlineStr">
@@ -39112,7 +39112,7 @@
           <t>C | 329呎 (1房)
 $613万
 $18,641/呎
-(26年-05月)</t>
+(26年-05月-06日)</t>
         </is>
       </c>
       <c r="E20" s="22" t="inlineStr">
@@ -39128,7 +39128,7 @@
           <t>E | 320呎 (1房)
 $601万
 $18,775/呎
-(26年-05月)</t>
+(26年-05月-03日)</t>
         </is>
       </c>
       <c r="G20" s="20" t="inlineStr">
@@ -39136,7 +39136,7 @@
           <t>F | 320呎 (1房)
 $571万
 $17,856/呎
-(26年-02月)</t>
+(26年-02月-01日)</t>
         </is>
       </c>
       <c r="H20" s="20" t="inlineStr">
@@ -39144,7 +39144,7 @@
           <t>G | 250呎 (开放式)
 $468万
 $18,736/呎
-(26年-05月)</t>
+(26年-05月-07日)</t>
         </is>
       </c>
       <c r="I20" s="22" t="inlineStr">
@@ -39160,7 +39160,7 @@
           <t>J | 414呎 (2房)
 $804万
 $19,428/呎
-(26年-05月)</t>
+(26年-05月-07日)</t>
         </is>
       </c>
       <c r="K20" s="22" t="inlineStr">
@@ -39191,7 +39191,7 @@
           <t>B | 454呎 (2房)
 $943万
 $20,780/呎
-(26年-05月)</t>
+(26年-05月-07日)</t>
         </is>
       </c>
       <c r="D21" s="20" t="inlineStr">
@@ -39199,7 +39199,7 @@
           <t>C | 329呎 (1房)
 $612万
 $18,593/呎
-(26年-05月)</t>
+(26年-05月-06日)</t>
         </is>
       </c>
       <c r="E21" s="22" t="inlineStr">
@@ -39215,7 +39215,7 @@
           <t>E | 320呎 (1房)
 $599万
 $18,728/呎
-(26年-05月)</t>
+(26年-05月-03日)</t>
         </is>
       </c>
       <c r="G21" s="20" t="inlineStr">
@@ -39223,7 +39223,7 @@
           <t>F | 320呎 (1房)
 $570万
 $17,812/呎
-(26年-01月)</t>
+(26年-01月-22日)</t>
         </is>
       </c>
       <c r="H21" s="20" t="inlineStr">
@@ -39231,7 +39231,7 @@
           <t>G | 250呎 (开放式)
 $462万
 $18,480/呎
-(26年-05月)</t>
+(26年-05月-10日)</t>
         </is>
       </c>
       <c r="I21" s="22" t="inlineStr">
@@ -39247,7 +39247,7 @@
           <t>J | 414呎 (2房)
 $811万
 $19,599/呎
-(26年-05月)</t>
+(26年-05月-12日)</t>
         </is>
       </c>
       <c r="K21" s="22" t="inlineStr">
@@ -39278,7 +39278,7 @@
           <t>B | 454呎 (2房)
 $923万
 $20,322/呎
-(26年-03月)</t>
+(26年-03月-02日)</t>
         </is>
       </c>
       <c r="D22" s="20" t="inlineStr">
@@ -39286,7 +39286,7 @@
           <t>C | 329呎 (1房)
 $610万
 $18,547/呎
-(26年-05月)</t>
+(26年-05月-06日)</t>
         </is>
       </c>
       <c r="E22" s="22" t="inlineStr">
@@ -39302,7 +39302,7 @@
           <t>E | 320呎 (1房)
 $566万
 $17,678/呎
-(26年-02月)</t>
+(26年-02月-12日)</t>
         </is>
       </c>
       <c r="G22" s="20" t="inlineStr">
@@ -39310,7 +39310,7 @@
           <t>F | 320呎 (1房)
 $568万
 $17,766/呎
-(26年-02月)</t>
+(26年-02月-03日)</t>
         </is>
       </c>
       <c r="H22" s="20" t="inlineStr">
@@ -39318,7 +39318,7 @@
           <t>G | 250呎 (开放式)
 $461万
 $18,436/呎
-(26年-05月)</t>
+(26年-05月-07日)</t>
         </is>
       </c>
       <c r="I22" s="22" t="inlineStr">
@@ -39334,7 +39334,7 @@
           <t>J | 414呎 (2房)
 $800万
 $19,331/呎
-(26年-05月)</t>
+(26年-05月-10日)</t>
         </is>
       </c>
       <c r="K22" s="22" t="inlineStr">
@@ -39365,7 +39365,7 @@
           <t>B | 454呎 (2房)
 $931万
 $20,500/呎
-(26年-03月)</t>
+(26年-03月-04日)</t>
         </is>
       </c>
       <c r="D23" s="20" t="inlineStr">
@@ -39373,7 +39373,7 @@
           <t>C | 329呎 (1房)
 $609万
 $18,498/呎
-(26年-05月)</t>
+(26年-05月-06日)</t>
         </is>
       </c>
       <c r="E23" s="22" t="inlineStr">
@@ -39389,7 +39389,7 @@
           <t>E | 320呎 (1房)
 $564万
 $17,634/呎
-(26年-01月)</t>
+(26年-01月-07日)</t>
         </is>
       </c>
       <c r="G23" s="20" t="inlineStr">
@@ -39397,7 +39397,7 @@
           <t>F | 320呎 (1房)
 $567万
 $17,722/呎
-(26年-02月)</t>
+(26年-02月-05日)</t>
         </is>
       </c>
       <c r="H23" s="20" t="inlineStr">
@@ -39405,7 +39405,7 @@
           <t>G | 250呎 (开放式)
 $465万
 $18,596/呎
-(26年-05月)</t>
+(26年-05月-06日)</t>
         </is>
       </c>
       <c r="I23" s="22" t="inlineStr">
@@ -39421,7 +39421,7 @@
           <t>J | 414呎 (2房)
 $798万
 $19,285/呎
-(26年-05月)</t>
+(26年-05月-05日)</t>
         </is>
       </c>
       <c r="K23" s="22" t="inlineStr">
@@ -39452,7 +39452,7 @@
           <t>B | 454呎 (2房)
 $918万
 $20,220/呎
-(26年-02月)</t>
+(26年-02月-25日)</t>
         </is>
       </c>
       <c r="D24" s="20" t="inlineStr">
@@ -39460,7 +39460,7 @@
           <t>C | 329呎 (1房)
 $607万
 $18,453/呎
-(26年-05月)</t>
+(26年-05月-05日)</t>
         </is>
       </c>
       <c r="E24" s="22" t="inlineStr">
@@ -39476,7 +39476,7 @@
           <t>E | 320呎 (1房)
 $563万
 $17,591/呎
-(26年-01月)</t>
+(26年-01月-12日)</t>
         </is>
       </c>
       <c r="G24" s="20" t="inlineStr">
@@ -39484,7 +39484,7 @@
           <t>F | 320呎 (1房)
 $566万
 $17,678/呎
-(26年-02月)</t>
+(26年-02月-05日)</t>
         </is>
       </c>
       <c r="H24" s="20" t="inlineStr">
@@ -39492,7 +39492,7 @@
           <t>G | 250呎 (开放式)
 $459万
 $18,344/呎
-(26年-05月)</t>
+(26年-05月-05日)</t>
         </is>
       </c>
       <c r="I24" s="22" t="inlineStr">
@@ -39508,7 +39508,7 @@
           <t>J | 414呎 (2房)
 $796万
 $19,234/呎
-(26年-05月)</t>
+(26年-05月-14日)</t>
         </is>
       </c>
       <c r="K24" s="22" t="inlineStr">
@@ -39539,7 +39539,7 @@
           <t>B | 454呎 (2房)
 $913万
 $20,119/呎
-(26年-03月)</t>
+(26年-03月-01日)</t>
         </is>
       </c>
       <c r="D25" s="20" t="inlineStr">
@@ -39547,7 +39547,7 @@
           <t>C | 329呎 (1房)
 $604万
 $18,362/呎
-(26年-05月)</t>
+(26年-05月-06日)</t>
         </is>
       </c>
       <c r="E25" s="22" t="inlineStr">
@@ -39563,7 +39563,7 @@
           <t>E | 320呎 (1房)
 $560万
 $17,503/呎
-(26年-01月)</t>
+(26年-01月-08日)</t>
         </is>
       </c>
       <c r="G25" s="20" t="inlineStr">
@@ -39571,7 +39571,7 @@
           <t>F | 320呎 (1房)
 $563万
 $17,591/呎
-(26年-02月)</t>
+(26年-02月-15日)</t>
         </is>
       </c>
       <c r="H25" s="20" t="inlineStr">
@@ -39579,7 +39579,7 @@
           <t>G | 250呎 (开放式)
 $426万
 $17,056/呎
-(26年-01月)</t>
+(26年-01月-08日)</t>
         </is>
       </c>
       <c r="I25" s="22" t="inlineStr">
@@ -39595,7 +39595,7 @@
           <t>J | 414呎 (2房)
 $792万
 $19,140/呎
-(26年-05月)</t>
+(26年-05月-07日)</t>
         </is>
       </c>
       <c r="K25" s="22" t="inlineStr">
@@ -39626,7 +39626,7 @@
           <t>B | 454呎 (2房)
 $911万
 $20,068/呎
-(26年-02月)</t>
+(26年-02月-10日)</t>
         </is>
       </c>
       <c r="D26" s="20" t="inlineStr">
@@ -39634,7 +39634,7 @@
           <t>C | 329呎 (1房)
 $603万
 $18,319/呎
-(26年-05月)</t>
+(26年-05月-06日)</t>
         </is>
       </c>
       <c r="E26" s="22" t="inlineStr">
@@ -39650,7 +39650,7 @@
           <t>E | 320呎 (1房)
 $559万
 $17,462/呎
-(26年-01月)</t>
+(26年-01月-08日)</t>
         </is>
       </c>
       <c r="G26" s="20" t="inlineStr">
@@ -39658,7 +39658,7 @@
           <t>F | 320呎 (1房)
 $562万
 $17,547/呎
-(26年-02月)</t>
+(26年-02月-05日)</t>
         </is>
       </c>
       <c r="H26" s="20" t="inlineStr">
@@ -39666,7 +39666,7 @@
           <t>G | 250呎 (开放式)
 $425万
 $17,016/呎
-(26年-01月)</t>
+(26年-01月-08日)</t>
         </is>
       </c>
       <c r="I26" s="22" t="inlineStr">
@@ -39682,7 +39682,7 @@
           <t>J | 414呎 (2房)
 $790万
 $19,094/呎
-(26年-05月)</t>
+(26年-05月-05日)</t>
         </is>
       </c>
       <c r="K26" s="22" t="inlineStr">
@@ -39713,7 +39713,7 @@
           <t>B | 454呎 (2房)
 $909万
 $20,018/呎
-(26年-02月)</t>
+(26年-02月-04日)</t>
         </is>
       </c>
       <c r="D27" s="20" t="inlineStr">
@@ -39721,7 +39721,7 @@
           <t>C | 329呎 (1房)
 $601万
 $18,274/呎
-(26年-05月)</t>
+(26年-05月-06日)</t>
         </is>
       </c>
       <c r="E27" s="22" t="inlineStr">
@@ -39737,7 +39737,7 @@
           <t>E | 320呎 (1房)
 $557万
 $17,419/呎
-(26年-01月)</t>
+(26年-01月-08日)</t>
         </is>
       </c>
       <c r="G27" s="20" t="inlineStr">
@@ -39745,7 +39745,7 @@
           <t>F | 320呎 (1房)
 $560万
 $17,503/呎
-(26年-01月)</t>
+(26年-01月-25日)</t>
         </is>
       </c>
       <c r="H27" s="20" t="inlineStr">
@@ -39753,7 +39753,7 @@
           <t>G | 250呎 (开放式)
 $424万
 $16,972/呎
-(26年-01月)</t>
+(26年-01月-13日)</t>
         </is>
       </c>
       <c r="I27" s="22" t="inlineStr">
@@ -39769,7 +39769,7 @@
           <t>J | 414呎 (2房)
 $744万
 $17,966/呎
-(26年-01月)</t>
+(26年-01月-13日)</t>
         </is>
       </c>
       <c r="K27" s="22" t="inlineStr">
@@ -39800,7 +39800,7 @@
           <t>B | 454呎 (2房)
 $906万
 $19,967/呎
-(26年-03月)</t>
+(26年-03月-01日)</t>
         </is>
       </c>
       <c r="D28" s="20" t="inlineStr">
@@ -39808,7 +39808,7 @@
           <t>C | 329呎 (1房)
 $606万
 $18,432/呎
-(26年-05月)</t>
+(26年-05月-07日)</t>
         </is>
       </c>
       <c r="E28" s="22" t="inlineStr">
@@ -39824,7 +39824,7 @@
           <t>E | 320呎 (1房)
 $556万
 $17,372/呎
-(26年-01月)</t>
+(26年-01月-11日)</t>
         </is>
       </c>
       <c r="G28" s="20" t="inlineStr">
@@ -39832,7 +39832,7 @@
           <t>F | 320呎 (1房)
 $559万
 $17,459/呎
-(26年-02月)</t>
+(26年-02月-12日)</t>
         </is>
       </c>
       <c r="H28" s="20" t="inlineStr">
@@ -39840,7 +39840,7 @@
           <t>G | 250呎 (开放式)
 $442万
 $17,700/呎
-(26年-01月)</t>
+(26年-01月-08日)</t>
         </is>
       </c>
       <c r="I28" s="22" t="inlineStr">
@@ -39856,7 +39856,7 @@
           <t>J | 414呎 (2房)
 $776万
 $18,737/呎
-(26年-01月)</t>
+(26年-01月-08日)</t>
         </is>
       </c>
       <c r="K28" s="22" t="inlineStr">
@@ -39887,7 +39887,7 @@
           <t>B | 454呎 (2房)
 $904万
 $19,919/呎
-(26年-03月)</t>
+(26年-03月-01日)</t>
         </is>
       </c>
       <c r="D29" s="20" t="inlineStr">
@@ -39895,7 +39895,7 @@
           <t>C | 329呎 (1房)
 $598万
 $18,179/呎
-(26年-05月)</t>
+(26年-05月-06日)</t>
         </is>
       </c>
       <c r="E29" s="22" t="inlineStr">
@@ -39911,7 +39911,7 @@
           <t>E | 320呎 (1房)
 $554万
 $17,328/呎
-(26年-01月)</t>
+(26年-01月-08日)</t>
         </is>
       </c>
       <c r="G29" s="20" t="inlineStr">
@@ -39919,7 +39919,7 @@
           <t>F | 320呎 (1房)
 $557万
 $17,419/呎
-(26年-02月)</t>
+(26年-02月-12日)</t>
         </is>
       </c>
       <c r="H29" s="20" t="inlineStr">
@@ -39927,7 +39927,7 @@
           <t>G | 250呎 (开放式)
 $422万
 $16,888/呎
-(26年-01月)</t>
+(26年-01月-08日)</t>
         </is>
       </c>
       <c r="I29" s="22" t="inlineStr">
@@ -39943,7 +39943,7 @@
           <t>J | 414呎 (2房)
 $774万
 $18,691/呎
-(26年-01月)</t>
+(26年-01月-08日)</t>
         </is>
       </c>
       <c r="K29" s="22" t="inlineStr">
@@ -39974,7 +39974,7 @@
           <t>B | 454呎 (2房)
 $902万
 $19,868/呎
-(26年-01月)</t>
+(26年-01月-13日)</t>
         </is>
       </c>
       <c r="D30" s="20" t="inlineStr">
@@ -39982,7 +39982,7 @@
           <t>C | 329呎 (1房)
 $597万
 $18,134/呎
-(26年-05月)</t>
+(26年-05月-05日)</t>
         </is>
       </c>
       <c r="E30" s="22" t="inlineStr">
@@ -39998,7 +39998,7 @@
           <t>E | 320呎 (1房)
 $553万
 $17,284/呎
-(26年-01月)</t>
+(26年-01月-18日)</t>
         </is>
       </c>
       <c r="G30" s="20" t="inlineStr">
@@ -40006,7 +40006,7 @@
           <t>F | 320呎 (1房)
 $556万
 $17,372/呎
-(26年-02月)</t>
+(26年-02月-23日)</t>
         </is>
       </c>
       <c r="H30" s="20" t="inlineStr">
@@ -40014,7 +40014,7 @@
           <t>G | 250呎 (开放式)
 $421万
 $16,844/呎
-(26年-01月)</t>
+(26年-01月-07日)</t>
         </is>
       </c>
       <c r="I30" s="22" t="inlineStr">
@@ -40030,7 +40030,7 @@
           <t>J | 414呎 (2房)
 $738万
 $17,833/呎
-(26年-01月)</t>
+(26年-01月-06日)</t>
         </is>
       </c>
       <c r="K30" s="22" t="inlineStr">
@@ -40061,7 +40061,7 @@
           <t>B | 454呎 (2房)
 $900万
 $19,819/呎
-(26年-02月)</t>
+(26年-02月-25日)</t>
         </is>
       </c>
       <c r="D31" s="20" t="inlineStr">
@@ -40069,7 +40069,7 @@
           <t>C | 329呎 (1房)
 $595万
 $18,091/呎
-(26年-05月)</t>
+(26年-05月-05日)</t>
         </is>
       </c>
       <c r="E31" s="22" t="inlineStr">
@@ -40085,7 +40085,7 @@
           <t>E | 320呎 (1房)
 $577万
 $18,028/呎
-(26年-01月)</t>
+(26年-01月-12日)</t>
         </is>
       </c>
       <c r="G31" s="20" t="inlineStr">
@@ -40093,7 +40093,7 @@
           <t>F | 320呎 (1房)
 $561万
 $17,525/呎
-(26年-01月)</t>
+(26年-01月-25日)</t>
         </is>
       </c>
       <c r="H31" s="20" t="inlineStr">
@@ -40101,7 +40101,7 @@
           <t>G | 250呎 (开放式)
 $420万
 $16,804/呎
-(26年-01月)</t>
+(26年-01月-08日)</t>
         </is>
       </c>
       <c r="I31" s="22" t="inlineStr">
@@ -40117,7 +40117,7 @@
           <t>J | 414呎 (2房)
 $736万
 $17,787/呎
-(25年-12月)</t>
+(25年-12月-13日)</t>
         </is>
       </c>
       <c r="K31" s="22" t="inlineStr">
@@ -40148,7 +40148,7 @@
           <t>B | 454呎 (2房)
 $908万
 $19,996/呎
-(26年-03月)</t>
+(26年-03月-15日)</t>
         </is>
       </c>
       <c r="D32" s="20" t="inlineStr">
@@ -40156,7 +40156,7 @@
           <t>C | 329呎 (1房)
 $594万
 $18,046/呎
-(26年-05月)</t>
+(26年-05月-06日)</t>
         </is>
       </c>
       <c r="E32" s="22" t="inlineStr">
@@ -40172,7 +40172,7 @@
           <t>E | 320呎 (1房)
 $582万
 $18,178/呎
-(26年-04月)</t>
+(26年-04月-22日)</t>
         </is>
       </c>
       <c r="G32" s="20" t="inlineStr">
@@ -40180,7 +40180,7 @@
           <t>F | 320呎 (1房)
 $553万
 $17,284/呎
-(26年-02月)</t>
+(26年-02月-10日)</t>
         </is>
       </c>
       <c r="H32" s="20" t="inlineStr">
@@ -40188,7 +40188,7 @@
           <t>G | 250呎 (开放式)
 $419万
 $16,764/呎
-(26年-01月)</t>
+(26年-01月-13日)</t>
         </is>
       </c>
       <c r="I32" s="22" t="inlineStr">
@@ -40204,7 +40204,7 @@
           <t>J | 414呎 (2房)
 $735万
 $17,744/呎
-(26年-01月)</t>
+(26年-01月-06日)</t>
         </is>
       </c>
       <c r="K32" s="22" t="inlineStr">
@@ -40235,7 +40235,7 @@
           <t>B | 454呎 (2房)
 $903万
 $19,894/呎
-(26年-03月)</t>
+(26年-03月-16日)</t>
         </is>
       </c>
       <c r="D33" s="20" t="inlineStr">
@@ -40243,7 +40243,7 @@
           <t>C | 329呎 (1房)
 $596万
 $18,106/呎
-(26年-05月)</t>
+(26年-05月-18日)</t>
         </is>
       </c>
       <c r="E33" s="22" t="inlineStr">
@@ -40267,7 +40267,7 @@
           <t>F | 320呎 (1房)
 $548万
 $17,116/呎
-(26年-02月)</t>
+(26年-02月-24日)</t>
         </is>
       </c>
       <c r="H33" s="20" t="inlineStr">
@@ -40275,7 +40275,7 @@
           <t>G | 250呎 (开放式)
 $451万
 $18,044/呎
-(26年-05月)</t>
+(26年-05月-14日)</t>
         </is>
       </c>
       <c r="I33" s="22" t="inlineStr">
@@ -40291,7 +40291,7 @@
           <t>J | 414呎 (2房)
 $731万
 $17,657/呎
-(26年-01月)</t>
+(26年-01月-07日)</t>
         </is>
       </c>
       <c r="K33" s="22" t="inlineStr">
@@ -40322,7 +40322,7 @@
           <t>B | 454呎 (2房)
 $919万
 $20,240/呎
-(26年-05月)</t>
+(26年-05月-17日)</t>
         </is>
       </c>
       <c r="D34" s="20" t="inlineStr">
@@ -40330,7 +40330,7 @@
           <t>C | 329呎 (1房)
 $594万
 $18,061/呎
-(26年-05月)</t>
+(26年-05月-18日)</t>
         </is>
       </c>
       <c r="E34" s="22" t="inlineStr">
@@ -40346,7 +40346,7 @@
           <t>E | 320呎 (1房)
 $546万
 $17,075/呎
-(26年-01月)</t>
+(26年-01月-14日)</t>
         </is>
       </c>
       <c r="G34" s="24" t="inlineStr">
@@ -40362,7 +40362,7 @@
           <t>G | 250呎 (开放式)
 $450万
 $18,000/呎
-(26年-05月)</t>
+(26年-05月-17日)</t>
         </is>
       </c>
       <c r="I34" s="22" t="inlineStr">
@@ -40378,7 +40378,7 @@
           <t>J | 414呎 (2房)
 $782万
 $18,877/呎
-(26年-05月)</t>
+(26年-05月-17日)</t>
         </is>
       </c>
       <c r="K34" s="22" t="inlineStr">

--- a/files/九龙-启德-Double Coast III.xlsx
+++ b/files/九龙-启德-Double Coast III.xlsx
@@ -32656,7 +32656,7 @@
       </c>
       <c r="J483" s="3" t="inlineStr">
         <is>
-          <t>7.0%</t>
+          <t>7%</t>
         </is>
       </c>
       <c r="K483" s="5" t="n">
@@ -33246,7 +33246,7 @@
       </c>
       <c r="J492" s="3" t="inlineStr">
         <is>
-          <t>7.0%</t>
+          <t>7%</t>
         </is>
       </c>
       <c r="K492" s="5" t="n">
